--- a/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_CENTRO_pgto_05-10-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_CENTRO_pgto_05-10-2026.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HOLERITE SET.26'!$A$4:$I$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$153</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'GANHOS DO COLABORADOR'!$A$1:$D$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PONTO SET.26'!$A$4:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PONTO SET.26'!$A$4:$I$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'FOLGUISTAS'!$A$4:$H$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -836,7 +836,7 @@
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>GENECIR: voltou das férias, salário integral em setembro.</t>
+          <t>GENECIR: voltou das férias, salário integral em setembro. Trabalhou os feriados de 07/09 e 08/09 (R$ 108,06), recebeu adiantamento de R$ 500,00 em 09/09 e R$ 270,00 de vale-transporte.</t>
         </is>
       </c>
     </row>
@@ -935,25 +935,34 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>OBSERVAÇÃO TÉCNICA</t>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>08/09 foi tratado como feriado (GENECIR). Se for feriado municipal, somar 1 em 'Domingos + feriados' na aba PARÂMETROS das 3 lojas: o fator do DSR passa de 0,20 (5/25) para 0,25 (6/24).</t>
         </is>
       </c>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="4" t="inlineStr"/>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>As células de total e de cálculo são fórmulas. Ao abrir no Excel ou no Google Planilhas elas aparecem calculadas; em visualizadores simples podem aparecer em branco até o arquivo ser aberto.</t>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Feriado trabalhado está a 1 salário-dia (R$ 54,03). Em agosto a Betel lançou o feriado como 4h53 de hora extra a 50% (R$ 53,97) — alinhar o critério.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>ABAS DO ARQUIVO</t>
+          <t>OBSERVAÇÃO TÉCNICA</t>
         </is>
       </c>
     </row>
@@ -961,15 +970,14 @@
       <c r="A36" s="4" t="inlineStr"/>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>HOLERITE SET.26 — relatório principal da competência setembro/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="4" t="inlineStr"/>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>GANHOS DO COLABORADOR — demonstrativo individual, pronto para imprimir/mandar.</t>
+          <t>As células de total e de cálculo são fórmulas. Ao abrir no Excel ou no Google Planilhas elas aparecem calculadas; em visualizadores simples podem aparecer em branco até o arquivo ser aberto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>ABAS DO ARQUIVO</t>
         </is>
       </c>
     </row>
@@ -977,7 +985,7 @@
       <c r="A38" s="4" t="inlineStr"/>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista.</t>
+          <t>HOLERITE SET.26 — relatório principal da competência setembro/2026.</t>
         </is>
       </c>
     </row>
@@ -985,7 +993,7 @@
       <c r="A39" s="4" t="inlineStr"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>BASE INOVAFARMA SET.26 — apuração de comissões e incentivos por vendedor.</t>
+          <t>GANHOS DO COLABORADOR — demonstrativo individual, pronto para imprimir/mandar.</t>
         </is>
       </c>
     </row>
@@ -993,7 +1001,7 @@
       <c r="A40" s="4" t="inlineStr"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
+          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista.</t>
         </is>
       </c>
     </row>
@@ -1001,13 +1009,29 @@
       <c r="A41" s="4" t="inlineStr"/>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>PONTO SET.26 — horas extras, adicional noturno e feriado trabalhado; alimenta o holerite.</t>
+          <t>BASE INOVAFARMA SET.26 — apuração de comissões e incentivos por vendedor.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="4" t="inlineStr"/>
       <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="4" t="inlineStr"/>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>PONTO SET.26 — horas extras, adicional noturno e feriado trabalhado; alimenta o holerite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="4" t="inlineStr"/>
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>FOLGUISTAS — diárias de SERGIO e ANA CELIA para o contas a pagar (fora do holerite).</t>
         </is>
@@ -1019,8 +1043,8 @@
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A33:B33"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A35:B35"/>
@@ -1978,27 +2002,27 @@
         </is>
       </c>
       <c r="B7" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,B$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,B$4,'PONTO SET.26'!$H$5:$H$15,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="C7" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,C$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,C$4,'PONTO SET.26'!$H$5:$H$15,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="D7" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,D$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,D$4,'PONTO SET.26'!$H$5:$H$15,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="E7" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,E$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,E$4,'PONTO SET.26'!$H$5:$H$15,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="F7" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,F$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,F$4,'PONTO SET.26'!$H$5:$H$15,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="G7" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,G$4,'PONTO SET.26'!$H$5:$H$14,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,G$4,'PONTO SET.26'!$H$5:$H$15,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="H7" s="20">
@@ -2018,27 +2042,27 @@
         </is>
       </c>
       <c r="B8" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,B$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,B$4,'PONTO SET.26'!$H$5:$H$15,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="C8" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,C$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,C$4,'PONTO SET.26'!$H$5:$H$15,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="D8" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,D$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,D$4,'PONTO SET.26'!$H$5:$H$15,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="E8" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,E$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,E$4,'PONTO SET.26'!$H$5:$H$15,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="F8" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,F$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,F$4,'PONTO SET.26'!$H$5:$H$15,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="G8" s="34">
-        <f>SUMIFS('PONTO SET.26'!$G$5:$G$14,'PONTO SET.26'!$A$5:$A$14,G$4,'PONTO SET.26'!$H$5:$H$14,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,G$4,'PONTO SET.26'!$H$5:$H$15,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="H8" s="20">
@@ -2506,7 +2530,9 @@
       </c>
       <c r="B24" s="35" t="n"/>
       <c r="C24" s="35" t="n"/>
-      <c r="D24" s="35" t="n"/>
+      <c r="D24" s="35" t="n">
+        <v>-500</v>
+      </c>
       <c r="E24" s="35" t="n"/>
       <c r="F24" s="35" t="n"/>
       <c r="G24" s="35" t="n"/>
@@ -2516,7 +2542,7 @@
       </c>
       <c r="I24" s="33" t="inlineStr">
         <is>
-          <t>PREENCHER com os vales adiantados durante setembro.</t>
+          <t>PREENCHER com os vales adiantados durante setembro. GENECIR: adiantamento de R$ 500,00 em 09/09/2026.</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2816,9 @@
       </c>
       <c r="B35" s="35" t="n"/>
       <c r="C35" s="35" t="n"/>
-      <c r="D35" s="35" t="n"/>
+      <c r="D35" s="35" t="n">
+        <v>270</v>
+      </c>
       <c r="E35" s="35" t="n"/>
       <c r="F35" s="35" t="n"/>
       <c r="G35" s="35" t="n"/>
@@ -2800,7 +2828,7 @@
       </c>
       <c r="I35" s="33" t="inlineStr">
         <is>
-          <t>PREENCHER com as passagens compradas para outubro/2026.</t>
+          <t>PREENCHER com as passagens compradas. GENECIR: R$ 270,00 de vale-transporte.</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6714,16 +6742,16 @@
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>RENALDO</t>
+          <t>GENECIR</t>
         </is>
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>Registro informativo</t>
+          <t>Feriado trabalhado (dobra)</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
@@ -6734,8 +6762,9 @@
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A6,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F6" s="36" t="n">
-        <v>0</v>
+      <c r="F6" s="36">
+        <f>ROUND(E6/PARÂMETROS!$B$19,2)</f>
+        <v/>
       </c>
       <c r="G6" s="20">
         <f>ROUND(C6*F6,2)</f>
@@ -6743,31 +6772,55 @@
       </c>
       <c r="H6" s="51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HORAS EXTRAS</t>
         </is>
       </c>
       <c r="I6" s="33" t="inlineStr">
         <is>
-          <t>Férias de 01 a 30/09/2026 — mês inteiro. Salário zerado no holerite; férias e 1/3 vão em recibo próprio.</t>
+          <t>Feriados de 07/09 e 08/09/2026 trabalhados, sem folga compensatória — 1 salário-dia a mais por feriado.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="52" t="n"/>
-      <c r="B7" s="52" t="n"/>
-      <c r="C7" s="52" t="n"/>
-      <c r="D7" s="52" t="n"/>
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Registro informativo</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>dias</t>
+        </is>
+      </c>
       <c r="E7" s="34">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A7,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F7" s="35" t="n"/>
+      <c r="F7" s="36" t="n">
+        <v>0</v>
+      </c>
       <c r="G7" s="20">
         <f>ROUND(C7*F7,2)</f>
         <v/>
       </c>
-      <c r="H7" s="52" t="n"/>
-      <c r="I7" s="52" t="n"/>
+      <c r="H7" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="33" t="inlineStr">
+        <is>
+          <t>Férias de 01 a 30/09/2026 — mês inteiro. Salário zerado no holerite; férias e 1/3 vão em recibo próprio.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="52" t="n"/>
@@ -6889,60 +6942,77 @@
       <c r="I14" s="52" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n"/>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="A15" s="52" t="n"/>
+      <c r="B15" s="52" t="n"/>
+      <c r="C15" s="52" t="n"/>
+      <c r="D15" s="52" t="n"/>
+      <c r="E15" s="34">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A15,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F15" s="35" t="n"/>
+      <c r="G15" s="20">
+        <f>ROUND(C15*F15,2)</f>
+        <v/>
+      </c>
+      <c r="H15" s="52" t="n"/>
+      <c r="I15" s="52" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="n"/>
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="18" t="n"/>
-      <c r="E15" s="18" t="n"/>
-      <c r="F15" s="18" t="n"/>
-      <c r="G15" s="20">
-        <f>SUM(G5:G14)</f>
-        <v/>
-      </c>
-      <c r="H15" s="18" t="n"/>
-      <c r="I15" s="18" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Salário-hora = salário base ÷ 220. Hora extra = salário-hora × 1,5. Adicional noturno = salário-hora × 20%. Feriado trabalhado sem folga = 1 salário-dia a mais (salário base ÷ 30).</t>
-        </is>
-      </c>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="20">
+        <f>SUM(G5:G15)</f>
+        <v/>
+      </c>
+      <c r="H16" s="18" t="n"/>
+      <c r="I16" s="18" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>No salário de R$ 1.621,00: 40 horas extras dão R$ 442,09 e 24 horas dão R$ 265,25 — é a mesma conta usada na planilha de julho.</t>
+          <t>Salário-hora = salário base ÷ 220. Hora extra = salário-hora × 1,5. Adicional noturno = salário-hora × 20%. Feriado trabalhado sem folga = 1 salário-dia a mais (salário base ÷ 30).</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>As linhas em branco são para acrescentar ocorrências: preencha funcionário, ocorrência, quantidade, valor unitário e a rubrica de destino (HORAS EXTRAS ou ADICIONAL NOTURNO).</t>
+          <t>No salário de R$ 1.621,00: 40 horas extras dão R$ 442,09 e 24 horas dão R$ 265,25 — é a mesma conta usada na planilha de julho.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
+          <t>As linhas em branco são para acrescentar ocorrências: preencha funcionário, ocorrência, quantidade, valor unitário e a rubrica de destino (HORAS EXTRAS ou ADICIONAL NOTURNO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
           <t>Os totais desta aba entram sozinhos nas linhas HORAS EXTRAS e ADICIONAL NOTURNO da aba HOLERITE SET.26.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I14"/>
+  <autoFilter ref="A4:I15"/>
   <mergeCells count="6">
     <mergeCell ref="A19:I19"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A17:I17"/>
     <mergeCell ref="A18:I18"/>
     <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:I21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_CENTRO_pgto_05-10-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_CENTRO_pgto_05-10-2026.xlsx
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -813,7 +813,7 @@
       <c r="A20" s="4" t="inlineStr"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>DSR de setembro/2026: 4 domingos + o feriado de 07/09 ÷ 25 dias úteis = fator 0,200000</t>
+          <t>DSR de setembro/2026: 4 domingos + os feriados de 07/09 e 08/09 (municipal) = 6 ÷ 24 dias úteis = fator 0,250000</t>
         </is>
       </c>
     </row>
@@ -943,41 +943,37 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>08/09 foi tratado como feriado (GENECIR). Se for feriado municipal, somar 1 em 'Domingos + feriados' na aba PARÂMETROS das 3 lojas: o fator do DSR passa de 0,20 (5/25) para 0,25 (6/24).</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
           <t>Feriado trabalhado está a 1 salário-dia (R$ 54,03). Em agosto a Betel lançou o feriado como 4h53 de hora extra a 50% (R$ 53,97) — alinhar o critério.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO TÉCNICA</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="4" t="inlineStr"/>
-      <c r="B36" s="5" t="inlineStr">
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="4" t="inlineStr"/>
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>As células de total e de cálculo são fórmulas. Ao abrir no Excel ou no Google Planilhas elas aparecem calculadas; em visualizadores simples podem aparecer em branco até o arquivo ser aberto.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>ABAS DO ARQUIVO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="4" t="inlineStr"/>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>HOLERITE SET.26 — relatório principal da competência setembro/2026.</t>
         </is>
       </c>
     </row>
@@ -985,7 +981,7 @@
       <c r="A38" s="4" t="inlineStr"/>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>HOLERITE SET.26 — relatório principal da competência setembro/2026.</t>
+          <t>GANHOS DO COLABORADOR — demonstrativo individual, pronto para imprimir/mandar.</t>
         </is>
       </c>
     </row>
@@ -993,7 +989,7 @@
       <c r="A39" s="4" t="inlineStr"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>GANHOS DO COLABORADOR — demonstrativo individual, pronto para imprimir/mandar.</t>
+          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista.</t>
         </is>
       </c>
     </row>
@@ -1001,7 +997,7 @@
       <c r="A40" s="4" t="inlineStr"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista.</t>
+          <t>BASE INOVAFARMA SET.26 — apuração de comissões e incentivos por vendedor.</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1005,7 @@
       <c r="A41" s="4" t="inlineStr"/>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>BASE INOVAFARMA SET.26 — apuração de comissões e incentivos por vendedor.</t>
+          <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
         </is>
       </c>
     </row>
@@ -1017,21 +1013,13 @@
       <c r="A42" s="4" t="inlineStr"/>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
+          <t>PONTO SET.26 — horas extras, adicional noturno e feriado trabalhado; alimenta o holerite.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="4" t="inlineStr"/>
       <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>PONTO SET.26 — horas extras, adicional noturno e feriado trabalhado; alimenta o holerite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="4" t="inlineStr"/>
-      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>FOLGUISTAS — diárias de SERGIO e ANA CELIA para o contas a pagar (fora do holerite).</t>
         </is>
@@ -1044,10 +1032,10 @@
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1168,11 +1156,11 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Domingos: 06, 13, 20 e 27/09/2026, mais o feriado de 07/09 (segunda-feira). CONFERIR feriados municipais.</t>
+          <t>Domingos: 06, 13, 20 e 27/09/2026, mais os feriados de 07/09 (Independência, segunda) e 08/09 (municipal, terça).</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2199,7 @@
       </c>
       <c r="I12" s="33" t="inlineStr">
         <is>
-          <t>Cálculo: (comissão total + horas extras) × (4 domingos + feriado 07/09) ÷ 25 dias úteis de setembro/2026.</t>
+          <t>Cálculo: (comissão total + horas extras) × (4 domingos + feriados de 07/09 e 08/09) ÷ 24 dias úteis de setembro/2026.</t>
         </is>
       </c>
     </row>

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_CENTRO_pgto_05-10-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_CENTRO_pgto_05-10-2026.xlsx
@@ -1971,7 +1971,7 @@
         <v>1621</v>
       </c>
       <c r="G6" s="31" t="n">
-        <v>1621</v>
+        <v>4000</v>
       </c>
       <c r="H6" s="32">
         <f>SUM(B6:G6)</f>

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_CENTRO_pgto_05-10-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_CENTRO_pgto_05-10-2026.xlsx
@@ -667,7 +667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -836,7 +836,7 @@
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>GENECIR: voltou das férias, salário integral em setembro. Trabalhou os feriados de 07/09 e 08/09 (R$ 108,06), recebeu adiantamento de R$ 500,00 em 09/09 e R$ 270,00 de vale-transporte.</t>
+          <t>PEDRO: registrado na empresa matriz; salário de R$ 4.000,00 a partir de setembro/2026.</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       <c r="A24" s="4" t="inlineStr"/>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>RENALDO: férias de 01 a 30/09/2026 (mês inteiro) — salário zerado e sem desconto de vale-transporte; férias e 1/3 em recibo próprio.</t>
+          <t>GENECIR: voltou das férias, salário integral em setembro. Trabalhou os feriados de 07/09 e 08/09 (R$ 108,06), recebeu adiantamento de R$ 500,00 em 09/09 e R$ 270,00 de vale-transporte.</t>
         </is>
       </c>
     </row>
@@ -852,26 +852,22 @@
       <c r="A25" s="4" t="inlineStr"/>
       <c r="B25" s="5" t="inlineStr">
         <is>
+          <t>RENALDO: férias de 01 a 30/09/2026 (mês inteiro) — salário zerado e sem desconto de vale-transporte; férias e 1/3 em recibo próprio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="4" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
           <t>SERGIO e ANA CELIA seguem como folguistas (diária de R$ 150,00 e R$ 100,00), na aba FOLGUISTAS.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>PENDÊNCIAS — CONFIRMAR ANTES DE ENVIAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Horas extras, adicional noturno e feriados trabalhados de setembro — lançar na aba PONTO SET.26.</t>
         </is>
       </c>
     </row>
@@ -883,7 +879,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Prêmio cota geral e prêmio pré-vencidos, conforme a tabela de metas da loja.</t>
+          <t>Horas extras, adicional noturno e feriados trabalhados de setembro — lançar na aba PONTO SET.26.</t>
         </is>
       </c>
     </row>
@@ -895,7 +891,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Vales adiantados, convênio e faltas de agosto.</t>
+          <t>Prêmio cota geral e prêmio pré-vencidos, conforme a tabela de metas da loja.</t>
         </is>
       </c>
     </row>
@@ -907,7 +903,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Férias, afastamentos e admissões que mudem o salário do mês.</t>
+          <t>Vales adiantados, convênio e faltas de agosto.</t>
         </is>
       </c>
     </row>
@@ -919,7 +915,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Extrair o relatório de comissões de setembro no InovaFarma e preencher a aba BASE INOVAFARMA SET.26.</t>
+          <t>Férias, afastamentos e admissões que mudem o salário do mês.</t>
         </is>
       </c>
     </row>
@@ -931,7 +927,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Preencher a quantidade de diárias de SERGIO e ANA CELIA.</t>
+          <t>Extrair o relatório de comissões de setembro no InovaFarma e preencher a aba BASE INOVAFARMA SET.26.</t>
         </is>
       </c>
     </row>
@@ -943,37 +939,41 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
+          <t>Preencher a quantidade de diárias de SERGIO e ANA CELIA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
           <t>Feriado trabalhado está a 1 salário-dia (R$ 54,03). Em agosto a Betel lançou o feriado como 4h53 de hora extra a 50% (R$ 53,97) — alinhar o critério.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO TÉCNICA</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="4" t="inlineStr"/>
-      <c r="B35" s="5" t="inlineStr">
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="4" t="inlineStr"/>
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>As células de total e de cálculo são fórmulas. Ao abrir no Excel ou no Google Planilhas elas aparecem calculadas; em visualizadores simples podem aparecer em branco até o arquivo ser aberto.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>ABAS DO ARQUIVO</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="4" t="inlineStr"/>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>HOLERITE SET.26 — relatório principal da competência setembro/2026.</t>
         </is>
       </c>
     </row>
@@ -981,7 +981,7 @@
       <c r="A38" s="4" t="inlineStr"/>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>GANHOS DO COLABORADOR — demonstrativo individual, pronto para imprimir/mandar.</t>
+          <t>HOLERITE SET.26 — relatório principal da competência setembro/2026.</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       <c r="A39" s="4" t="inlineStr"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista.</t>
+          <t>GANHOS DO COLABORADOR — demonstrativo individual, pronto para imprimir/mandar.</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       <c r="A40" s="4" t="inlineStr"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>BASE INOVAFARMA SET.26 — apuração de comissões e incentivos por vendedor.</t>
+          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista.</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       <c r="A41" s="4" t="inlineStr"/>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
+          <t>BASE INOVAFARMA SET.26 — apuração de comissões e incentivos por vendedor.</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       <c r="A42" s="4" t="inlineStr"/>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>PONTO SET.26 — horas extras, adicional noturno e feriado trabalhado; alimenta o holerite.</t>
+          <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
         </is>
       </c>
     </row>
@@ -1021,6 +1021,14 @@
       <c r="A43" s="4" t="inlineStr"/>
       <c r="B43" s="5" t="inlineStr">
         <is>
+          <t>PONTO SET.26 — horas extras, adicional noturno e feriado trabalhado; alimenta o holerite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="4" t="inlineStr"/>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
           <t>FOLGUISTAS — diárias de SERGIO e ANA CELIA para o contas a pagar (fora do holerite).</t>
         </is>
       </c>
@@ -1028,14 +1036,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_CENTRO_pgto_05-10-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_CENTRO_pgto_05-10-2026.xlsx
@@ -10,19 +10,21 @@
     <sheet name="CAPA" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="PARÂMETROS" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="BASE INOVAFARMA SET.26" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="HOLERITE SET.26" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="LISTA CONTABILIDADE" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="GANHOS DO COLABORADOR" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="PONTO SET.26" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="FOLGUISTAS" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="METAS SET.26" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="HOLERITE SET.26" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="LISTA CONTABILIDADE" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="GANHOS DO COLABORADOR" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PONTO SET.26" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="FOLGUISTAS" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BASE INOVAFARMA SET.26'!$A$4:$J$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HOLERITE SET.26'!$A$4:$I$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$153</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'GANHOS DO COLABORADOR'!$A$1:$D$44</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PONTO SET.26'!$A$4:$I$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'FOLGUISTAS'!$A$4:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'METAS SET.26'!$A$11:$T$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'HOLERITE SET.26'!$A$4:$I$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$165</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'GANHOS DO COLABORADOR'!$A$1:$D$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'PONTO SET.26'!$A$4:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'FOLGUISTAS'!$A$4:$H$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,11 +32,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00;-R$ #,##0.00;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -93,6 +96,18 @@
       <name val="Arial"/>
       <color rgb="00000000"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -175,12 +190,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6E0B4"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -215,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -224,11 +239,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -269,39 +284,59 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="18" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -667,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -836,7 +871,7 @@
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>PEDRO: registrado na empresa matriz; salário de R$ 4.000,00 a partir de setembro/2026.</t>
+          <t>PEDRO: registrado na empresa matriz. Nesta folha (pagamento 05/10) segue com R$ 1.621,00; o salário de R$ 4.000,00 começa na competência de outubro (pagamento 05/11/2026).</t>
         </is>
       </c>
     </row>
@@ -891,7 +926,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Prêmio cota geral e prêmio pré-vencidos, conforme a tabela de metas da loja.</t>
+          <t>Prêmios do programa de metas: lançar na aba METAS SET.26 a venda realizada, os dias trabalhados, o pré-vencido vendido, a Meta 2 e a perfumaria da loja.</t>
         </is>
       </c>
     </row>
@@ -1021,13 +1056,21 @@
       <c r="A43" s="4" t="inlineStr"/>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>PONTO SET.26 — horas extras, adicional noturno e feriado trabalhado; alimenta o holerite.</t>
+          <t>METAS SET.26 — programa de metas de setembro (4 metas), com o prêmio de cada um calculado e ligado ao holerite.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="4" t="inlineStr"/>
       <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>PONTO SET.26 — horas extras, adicional noturno e feriado trabalhado; alimenta o holerite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="4" t="inlineStr"/>
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>FOLGUISTAS — diárias de SERGIO e ANA CELIA para o contas a pagar (fora do holerite).</t>
         </is>
@@ -1867,7 +1910,708 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:T26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="52" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PROGRAMA DE METAS E PREMIAÇÃO — SETEMBRO/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Loja CENTRO · as 4 metas somam · pagamento junto com o holerite de 05/10/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>META 4 — PERFUMARIA DA LOJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>Média mensal (mar-ago/26)</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="n">
+        <v>9455.09</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>Meta = 130% da média</t>
+        </is>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>12300</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>Perfumaria vendida no mês</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>Zerou o estoque? (SIM/NÃO)</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>A LOJA BATEU A META 4?</t>
+        </is>
+      </c>
+      <c r="C9" s="31">
+        <f>IF(OR(AND(C7&lt;&gt;"",C7&gt;=C6),UPPER(C8)="SIM"),"SIM","NÃO")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>FUNCIONÁRIO</t>
+        </is>
+      </c>
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>FAIXA</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>META CHEIA</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>DIAS TRAB.</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>META AJUSTADA</t>
+        </is>
+      </c>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>VENDA REALIZADA</t>
+        </is>
+      </c>
+      <c r="G11" s="32" t="inlineStr">
+        <is>
+          <t>% DA META</t>
+        </is>
+      </c>
+      <c r="H11" s="32" t="inlineStr">
+        <is>
+          <t>PRÊMIO 80%</t>
+        </is>
+      </c>
+      <c r="I11" s="32" t="inlineStr">
+        <is>
+          <t>PRÊMIO 100%</t>
+        </is>
+      </c>
+      <c r="J11" s="32" t="inlineStr">
+        <is>
+          <t>PRÊMIO 120%</t>
+        </is>
+      </c>
+      <c r="K11" s="32" t="inlineStr">
+        <is>
+          <t>META 1 VOLUME</t>
+        </is>
+      </c>
+      <c r="L11" s="32" t="inlineStr">
+        <is>
+          <t>META 2 PROD. FOCO</t>
+        </is>
+      </c>
+      <c r="M11" s="32" t="inlineStr">
+        <is>
+          <t>PRÉ-VENC. VENDIDO</t>
+        </is>
+      </c>
+      <c r="N11" s="32" t="inlineStr">
+        <is>
+          <t>META PRÉ-V. FARMAC.</t>
+        </is>
+      </c>
+      <c r="O11" s="32" t="inlineStr">
+        <is>
+          <t>META 3 PRÉ-VENC.</t>
+        </is>
+      </c>
+      <c r="P11" s="32" t="inlineStr">
+        <is>
+          <t>META 4?</t>
+        </is>
+      </c>
+      <c r="Q11" s="32" t="inlineStr">
+        <is>
+          <t>COMISSÃO PERFUMARIA</t>
+        </is>
+      </c>
+      <c r="R11" s="32" t="inlineStr">
+        <is>
+          <t>META 4 PERFUM.</t>
+        </is>
+      </c>
+      <c r="S11" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL PRÊMIOS</t>
+        </is>
+      </c>
+      <c r="T11" s="32" t="inlineStr">
+        <is>
+          <t>OBSERVAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>A - Vendedor pleno</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="n">
+        <v>43000</v>
+      </c>
+      <c r="D12" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" s="28">
+        <f>ROUND(C12*IF(D12="",0,D12)/30,2)</f>
+        <v/>
+      </c>
+      <c r="F12" s="29" t="n"/>
+      <c r="G12" s="34">
+        <f>IF(E12&gt;0,IF(F12="",0,F12)/E12,0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="I12" s="28" t="n">
+        <v>250</v>
+      </c>
+      <c r="J12" s="28" t="n">
+        <v>500</v>
+      </c>
+      <c r="K12" s="35">
+        <f>IF(G12&gt;=1.2,J12,IF(G12&gt;=1,I12,IF(G12&gt;=0.8,H12,0)))</f>
+        <v/>
+      </c>
+      <c r="L12" s="29" t="n"/>
+      <c r="M12" s="29" t="n"/>
+      <c r="N12" s="28" t="n"/>
+      <c r="O12" s="35">
+        <f>IF(M12&gt;=3000,300,IF(M12&gt;=2000,200,IF(M12&gt;=1000,100,0)))</f>
+        <v/>
+      </c>
+      <c r="P12" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q12" s="29" t="n"/>
+      <c r="R12" s="35">
+        <f>IF(AND(P12="SIM",$C$9="SIM"),IF(Q12="",0,Q12)+50,0)</f>
+        <v/>
+      </c>
+      <c r="S12" s="36">
+        <f>ROUND(K12+IF(L12="",0,L12)+O12+R12,2)</f>
+        <v/>
+      </c>
+      <c r="T12" s="37" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>A - Vendedor pleno</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="n">
+        <v>31000</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="28">
+        <f>ROUND(C13*IF(D13="",0,D13)/30,2)</f>
+        <v/>
+      </c>
+      <c r="F13" s="29" t="n"/>
+      <c r="G13" s="34">
+        <f>IF(E13&gt;0,IF(F13="",0,F13)/E13,0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="I13" s="28" t="n">
+        <v>250</v>
+      </c>
+      <c r="J13" s="28" t="n">
+        <v>500</v>
+      </c>
+      <c r="K13" s="35">
+        <f>IF(G13&gt;=1.2,J13,IF(G13&gt;=1,I13,IF(G13&gt;=0.8,H13,0)))</f>
+        <v/>
+      </c>
+      <c r="L13" s="29" t="n"/>
+      <c r="M13" s="29" t="n"/>
+      <c r="N13" s="28" t="n"/>
+      <c r="O13" s="35">
+        <f>IF(M13&gt;=3000,300,IF(M13&gt;=2000,200,IF(M13&gt;=1000,100,0)))</f>
+        <v/>
+      </c>
+      <c r="P13" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q13" s="29" t="n"/>
+      <c r="R13" s="35">
+        <f>IF(AND(P13="SIM",$C$9="SIM"),IF(Q13="",0,Q13)+50,0)</f>
+        <v/>
+      </c>
+      <c r="S13" s="36">
+        <f>ROUND(K13+IF(L13="",0,L13)+O13+R13,2)</f>
+        <v/>
+      </c>
+      <c r="T13" s="37" t="inlineStr">
+        <is>
+          <t>Férias de 01 a 30/09: sem dias trabalhados, fica fora da apuração.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>ARIANE</t>
+        </is>
+      </c>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>B - Meia jornada</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" s="28">
+        <f>ROUND(C14*IF(D14="",0,D14)/30,2)</f>
+        <v/>
+      </c>
+      <c r="F14" s="29" t="n"/>
+      <c r="G14" s="34">
+        <f>IF(E14&gt;0,IF(F14="",0,F14)/E14,0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="I14" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="J14" s="28" t="n">
+        <v>300</v>
+      </c>
+      <c r="K14" s="35">
+        <f>IF(G14&gt;=1.2,J14,IF(G14&gt;=1,I14,IF(G14&gt;=0.8,H14,0)))</f>
+        <v/>
+      </c>
+      <c r="L14" s="29" t="n"/>
+      <c r="M14" s="29" t="n"/>
+      <c r="N14" s="28" t="n">
+        <v>1040</v>
+      </c>
+      <c r="O14" s="35">
+        <f>IF(AND(M14&lt;&gt;"",M14&gt;=N14),150,0)</f>
+        <v/>
+      </c>
+      <c r="P14" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q14" s="29" t="n"/>
+      <c r="R14" s="35">
+        <f>IF(AND(P14="SIM",$C$9="SIM"),IF(Q14="",0,Q14)+50,0)</f>
+        <v/>
+      </c>
+      <c r="S14" s="36">
+        <f>ROUND(K14+IF(L14="",0,L14)+O14+R14,2)</f>
+        <v/>
+      </c>
+      <c r="T14" s="37" t="inlineStr">
+        <is>
+          <t>Farmacêutica: na Meta 3 vale a regra própria (equipe + 30%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B15" s="33" t="inlineStr">
+        <is>
+          <t>B - Meia jornada</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="E15" s="28">
+        <f>ROUND(C15*IF(D15="",0,D15)/30,2)</f>
+        <v/>
+      </c>
+      <c r="F15" s="29" t="n"/>
+      <c r="G15" s="34">
+        <f>IF(E15&gt;0,IF(F15="",0,F15)/E15,0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="I15" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="J15" s="28" t="n">
+        <v>300</v>
+      </c>
+      <c r="K15" s="35">
+        <f>IF(G15&gt;=1.2,J15,IF(G15&gt;=1,I15,IF(G15&gt;=0.8,H15,0)))</f>
+        <v/>
+      </c>
+      <c r="L15" s="29" t="n"/>
+      <c r="M15" s="29" t="n"/>
+      <c r="N15" s="28" t="n"/>
+      <c r="O15" s="35">
+        <f>IF(M15&gt;=3000,300,IF(M15&gt;=2000,200,IF(M15&gt;=1000,100,0)))</f>
+        <v/>
+      </c>
+      <c r="P15" s="33" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="Q15" s="29" t="n"/>
+      <c r="R15" s="35">
+        <f>IF(AND(P15="SIM",$C$9="SIM"),IF(Q15="",0,Q15)+50,0)</f>
+        <v/>
+      </c>
+      <c r="S15" s="36">
+        <f>ROUND(K15+IF(L15="",0,L15)+O15+R15,2)</f>
+        <v/>
+      </c>
+      <c r="T15" s="37" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>C - Apoio / balcão</t>
+        </is>
+      </c>
+      <c r="C16" s="28" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D16" s="30" t="n">
+        <v>30</v>
+      </c>
+      <c r="E16" s="28">
+        <f>ROUND(C16*IF(D16="",0,D16)/30,2)</f>
+        <v/>
+      </c>
+      <c r="F16" s="29" t="n"/>
+      <c r="G16" s="34">
+        <f>IF(E16&gt;0,IF(F16="",0,F16)/E16,0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="I16" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="J16" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="K16" s="35">
+        <f>IF(G16&gt;=1.2,J16,IF(G16&gt;=1,I16,IF(G16&gt;=0.8,H16,0)))</f>
+        <v/>
+      </c>
+      <c r="L16" s="29" t="n"/>
+      <c r="M16" s="29" t="n"/>
+      <c r="N16" s="28" t="n"/>
+      <c r="O16" s="35">
+        <f>IF(M16&gt;=3000,300,IF(M16&gt;=2000,200,IF(M16&gt;=1000,100,0)))</f>
+        <v/>
+      </c>
+      <c r="P16" s="33" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="Q16" s="29" t="n"/>
+      <c r="R16" s="35">
+        <f>IF(AND(P16="SIM",$C$9="SIM"),IF(Q16="",0,Q16)+50,0)</f>
+        <v/>
+      </c>
+      <c r="S16" s="36">
+        <f>ROUND(K16+IF(L16="",0,L16)+O16+R16,2)</f>
+        <v/>
+      </c>
+      <c r="T16" s="37" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>SERGIO</t>
+        </is>
+      </c>
+      <c r="B17" s="33" t="inlineStr">
+        <is>
+          <t>D - Folguista</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D17" s="30" t="n"/>
+      <c r="E17" s="28">
+        <f>ROUND(C17*IF(D17="",0,D17)/30,2)</f>
+        <v/>
+      </c>
+      <c r="F17" s="29" t="n"/>
+      <c r="G17" s="34">
+        <f>IF(E17&gt;0,IF(F17="",0,F17)/E17,0)</f>
+        <v/>
+      </c>
+      <c r="H17" s="28" t="n">
+        <v>50</v>
+      </c>
+      <c r="I17" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="J17" s="28" t="n">
+        <v>150</v>
+      </c>
+      <c r="K17" s="35">
+        <f>IF(G17&gt;=1.2,J17,IF(G17&gt;=1,I17,IF(G17&gt;=0.8,H17,0)))</f>
+        <v/>
+      </c>
+      <c r="L17" s="29" t="n"/>
+      <c r="M17" s="29" t="n"/>
+      <c r="N17" s="28" t="n"/>
+      <c r="O17" s="35">
+        <f>IF(M17&gt;=3000,300,IF(M17&gt;=2000,200,IF(M17&gt;=1000,100,0)))</f>
+        <v/>
+      </c>
+      <c r="P17" s="33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q17" s="29" t="n"/>
+      <c r="R17" s="35">
+        <f>IF(AND(P17="SIM",$C$9="SIM"),IF(Q17="",0,Q17)+50,0)</f>
+        <v/>
+      </c>
+      <c r="S17" s="36">
+        <f>ROUND(K17+IF(L17="",0,L17)+O17+R17,2)</f>
+        <v/>
+      </c>
+      <c r="T17" s="37" t="inlineStr">
+        <is>
+          <t>Folguista: meta proporcional aos dias trabalhados — preencher os dias. Prêmio vai para o contas a pagar, fora do holerite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="18" t="n"/>
+      <c r="I18" s="18" t="n"/>
+      <c r="J18" s="18" t="n"/>
+      <c r="K18" s="20">
+        <f>SUM(K12:K17)</f>
+        <v/>
+      </c>
+      <c r="L18" s="20">
+        <f>SUM(L12:L17)</f>
+        <v/>
+      </c>
+      <c r="M18" s="18" t="n"/>
+      <c r="N18" s="18" t="n"/>
+      <c r="O18" s="20">
+        <f>SUM(O12:O17)</f>
+        <v/>
+      </c>
+      <c r="P18" s="18" t="n"/>
+      <c r="Q18" s="18" t="n"/>
+      <c r="R18" s="20">
+        <f>SUM(R12:R17)</f>
+        <v/>
+      </c>
+      <c r="S18" s="20">
+        <f>SUM(S12:S17)</f>
+        <v/>
+      </c>
+      <c r="T18" s="18" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="38" t="inlineStr">
+        <is>
+          <t>COMO PREENCHER (células amarelas):</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="39" t="inlineStr">
+        <is>
+          <t>VENDA REALIZADA: total vendido no mês pelo código do vendedor (InovaFarma, venda líquida). DIAS TRAB.: dias efetivamente trabalhados — a meta cai na mesma proporção.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="39" t="inlineStr">
+        <is>
+          <t>META 1 — VOLUME: meta = média dos 3 últimos meses + 8%. 80% da meta paga o prêmio de 80%, 100% paga o de 100% e 120% paga o de 120%, conforme a faixa (A 150/250/500 · B 100/150/300 · C e D 50/80/150).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="39" t="inlineStr">
+        <is>
+          <t>META 2 — PRODUTOS FOCO: lançar o valor apurado na semana (vitaminas da campanha, packs, injetáveis, coquetel, brinco, kit ressaca). ATENÇÃO: se o incentivo já vier no relatório do InovaFarma (linhas INCENTIVO do holerite), não lançar de novo aqui.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="39" t="inlineStr">
+        <is>
+          <t>META 3 — PRÉ-VENCIDOS: escada mensal por vendedor (acima de R$ 1.000 = 100 · R$ 2.000 = 200 · R$ 3.000 = 300). Farmacêuticos têm regra própria: bateu a meta da coluna META PRÉ-V. FARMAC., recebe R$ 150.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="39" t="inlineStr">
+        <is>
+          <t>META 4 — PERFUMARIA 130%: meta da LOJA (bloco no topo). Se a loja bater 130% da média ou zerar o estoque, cada vendedora marcada recebe a comissão de perfumaria do mês mais R$ 50 fixos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="39" t="inlineStr">
+        <is>
+          <t>Os prêmios entram sozinhos nas linhas PRÊMIO META 1 a 4 do holerite. Fonte: planilha Metas_Equipe_Set2026_v2.xlsx.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A11:T17"/>
+  <mergeCells count="14">
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A23:T23"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A22:T22"/>
+    <mergeCell ref="A26:T26"/>
+    <mergeCell ref="A21:T21"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A25:T25"/>
+    <mergeCell ref="A20:T20"/>
+    <mergeCell ref="A24:T24"/>
+    <mergeCell ref="A2:T2"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A6:B6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1896,47 +2640,47 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" s="40" t="inlineStr">
         <is>
           <t>RUBRICA</t>
         </is>
       </c>
-      <c r="B4" s="28" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="C4" s="28" t="inlineStr">
+      <c r="C4" s="41" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="D4" s="28" t="inlineStr">
+      <c r="D4" s="41" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="E4" s="28" t="inlineStr">
+      <c r="E4" s="41" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="F4" s="28" t="inlineStr">
+      <c r="F4" s="41" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="G4" s="28" t="inlineStr">
+      <c r="G4" s="41" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="H4" s="28" t="inlineStr">
+      <c r="H4" s="41" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="I4" s="27" t="inlineStr">
+      <c r="I4" s="40" t="inlineStr">
         <is>
           <t>ORIGEM / OBSERVAÇÃO</t>
         </is>
@@ -1948,76 +2692,76 @@
           <t>PROVENTOS</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n"/>
-      <c r="C5" s="29" t="n"/>
-      <c r="D5" s="29" t="n"/>
-      <c r="E5" s="29" t="n"/>
-      <c r="F5" s="29" t="n"/>
-      <c r="G5" s="29" t="n"/>
-      <c r="H5" s="29" t="n"/>
-      <c r="I5" s="29" t="n"/>
+      <c r="B5" s="42" t="n"/>
+      <c r="C5" s="42" t="n"/>
+      <c r="D5" s="42" t="n"/>
+      <c r="E5" s="42" t="n"/>
+      <c r="F5" s="42" t="n"/>
+      <c r="G5" s="42" t="n"/>
+      <c r="H5" s="42" t="n"/>
+      <c r="I5" s="42" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="44" t="n">
         <v>5648.41</v>
       </c>
-      <c r="C6" s="31" t="n">
+      <c r="C6" s="44" t="n">
         <v>1621</v>
       </c>
-      <c r="D6" s="31" t="n">
+      <c r="D6" s="44" t="n">
         <v>1621</v>
       </c>
-      <c r="E6" s="31" t="n">
+      <c r="E6" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="31" t="n">
+      <c r="F6" s="44" t="n">
         <v>1621</v>
       </c>
-      <c r="G6" s="31" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H6" s="32">
+      <c r="G6" s="44" t="n">
+        <v>1621</v>
+      </c>
+      <c r="H6" s="45">
         <f>SUM(B6:G6)</f>
         <v/>
       </c>
-      <c r="I6" s="33" t="inlineStr">
+      <c r="I6" s="46" t="inlineStr">
         <is>
           <t>Piso 2026 R$ 1.621,00; gerente conforme ago/2026. CONFERIR admissões, afastamentos e férias do mês.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="47">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,B$4,'PONTO SET.26'!$H$5:$H$15,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="47">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,C$4,'PONTO SET.26'!$H$5:$H$15,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
-      <c r="D7" s="34">
+      <c r="D7" s="47">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,D$4,'PONTO SET.26'!$H$5:$H$15,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
-      <c r="E7" s="34">
+      <c r="E7" s="47">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,E$4,'PONTO SET.26'!$H$5:$H$15,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
-      <c r="F7" s="34">
+      <c r="F7" s="47">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,F$4,'PONTO SET.26'!$H$5:$H$15,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
-      <c r="G7" s="34">
+      <c r="G7" s="47">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,G$4,'PONTO SET.26'!$H$5:$H$15,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
@@ -2025,39 +2769,39 @@
         <f>SUM(B7:G7)</f>
         <v/>
       </c>
-      <c r="I7" s="33" t="inlineStr">
+      <c r="I7" s="46" t="inlineStr">
         <is>
           <t>Somado automaticamente da aba PONTO SET.26 (apontamento de setembro/2026). Para mudar, edite lá.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="47">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,B$4,'PONTO SET.26'!$H$5:$H$15,"HORAS EXTRAS")</f>
         <v/>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="47">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,C$4,'PONTO SET.26'!$H$5:$H$15,"HORAS EXTRAS")</f>
         <v/>
       </c>
-      <c r="D8" s="34">
+      <c r="D8" s="47">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,D$4,'PONTO SET.26'!$H$5:$H$15,"HORAS EXTRAS")</f>
         <v/>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="47">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,E$4,'PONTO SET.26'!$H$5:$H$15,"HORAS EXTRAS")</f>
         <v/>
       </c>
-      <c r="F8" s="34">
+      <c r="F8" s="47">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,F$4,'PONTO SET.26'!$H$5:$H$15,"HORAS EXTRAS")</f>
         <v/>
       </c>
-      <c r="G8" s="34">
+      <c r="G8" s="47">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,G$4,'PONTO SET.26'!$H$5:$H$15,"HORAS EXTRAS")</f>
         <v/>
       </c>
@@ -2065,67 +2809,67 @@
         <f>SUM(B8:G8)</f>
         <v/>
       </c>
-      <c r="I8" s="33" t="inlineStr">
+      <c r="I8" s="46" t="inlineStr">
         <is>
           <t>Somado automaticamente da aba PONTO SET.26 (apontamento de setembro/2026). Para mudar, edite lá.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="43" t="inlineStr">
         <is>
           <t>COMISSÃO PRODUTOS (INOVAFARMA)</t>
         </is>
       </c>
-      <c r="B9" s="34" t="n">
+      <c r="B9" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="47">
         <f>ROUND('BASE INOVAFARMA SET.26'!F6*PARÂMETROS!$B$20,2)</f>
         <v/>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="47">
         <f>ROUND('BASE INOVAFARMA SET.26'!F7*PARÂMETROS!$B$20,2)</f>
         <v/>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="47">
         <f>ROUND('BASE INOVAFARMA SET.26'!F8*PARÂMETROS!$B$20,2)</f>
         <v/>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="47">
         <f>ROUND('BASE INOVAFARMA SET.26'!F9*PARÂMETROS!$B$20,2)</f>
         <v/>
       </c>
-      <c r="G9" s="34" t="n">
+      <c r="G9" s="47" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="20">
         <f>SUM(B9:G9)</f>
         <v/>
       </c>
-      <c r="I9" s="33" t="inlineStr">
+      <c r="I9" s="46" t="inlineStr">
         <is>
           <t>Apurado no InovaFarma (aba BASE INOVAFARMA SET.26). ARIANE e PEDRO não recebe(m) comissão — lançado zero.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>COMPLEMENTO / COMISSÃO PDV</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n"/>
-      <c r="C10" s="35" t="n"/>
-      <c r="D10" s="35" t="n"/>
-      <c r="E10" s="35" t="n"/>
-      <c r="F10" s="35" t="n"/>
-      <c r="G10" s="35" t="n"/>
+      <c r="B10" s="29" t="n"/>
+      <c r="C10" s="29" t="n"/>
+      <c r="D10" s="29" t="n"/>
+      <c r="E10" s="29" t="n"/>
+      <c r="F10" s="29" t="n"/>
+      <c r="G10" s="29" t="n"/>
       <c r="H10" s="20">
         <f>SUM(B10:G10)</f>
         <v/>
       </c>
-      <c r="I10" s="33" t="inlineStr">
+      <c r="I10" s="46" t="inlineStr">
         <is>
           <t>PREENCHER: PDV antigos e complementos de comissão acordados, se houver.</t>
         </is>
@@ -2165,39 +2909,39 @@
         <f>SUM(B11:G11)</f>
         <v/>
       </c>
-      <c r="I11" s="33" t="inlineStr">
+      <c r="I11" s="46" t="inlineStr">
         <is>
           <t>Base do DSR junto com as horas extras.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="43" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="B12" s="36">
+      <c r="B12" s="48">
         <f>ROUND((B11+B8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="48">
         <f>ROUND((C11+C8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="48">
         <f>ROUND((D11+D8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
-      <c r="E12" s="36">
+      <c r="E12" s="48">
         <f>ROUND((E11+E8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="48">
         <f>ROUND((F11+F8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="48">
         <f>ROUND((G11+G8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
@@ -2205,539 +2949,597 @@
         <f>SUM(B12:G12)</f>
         <v/>
       </c>
-      <c r="I12" s="33" t="inlineStr">
+      <c r="I12" s="46" t="inlineStr">
         <is>
           <t>Cálculo: (comissão total + horas extras) × (4 domingos + feriados de 07/09 e 08/09) ÷ 24 dias úteis de setembro/2026.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="43" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n"/>
+      <c r="B13" s="29" t="n"/>
+      <c r="C13" s="29" t="n"/>
+      <c r="D13" s="29" t="n"/>
+      <c r="E13" s="29" t="n"/>
+      <c r="F13" s="29" t="n"/>
+      <c r="G13" s="29" t="n"/>
       <c r="H13" s="20">
         <f>SUM(B13:G13)</f>
         <v/>
       </c>
-      <c r="I13" s="33" t="inlineStr">
+      <c r="I13" s="46" t="inlineStr">
         <is>
           <t>Conforme acordo da loja.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="A14" s="43" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n"/>
-      <c r="C14" s="35" t="n"/>
-      <c r="D14" s="35" t="n"/>
-      <c r="E14" s="35" t="n"/>
-      <c r="F14" s="35" t="n"/>
-      <c r="G14" s="35" t="n"/>
+      <c r="B14" s="29" t="n"/>
+      <c r="C14" s="29" t="n"/>
+      <c r="D14" s="29" t="n"/>
+      <c r="E14" s="29" t="n"/>
+      <c r="F14" s="29" t="n"/>
+      <c r="G14" s="29" t="n"/>
       <c r="H14" s="20">
         <f>SUM(B14:G14)</f>
         <v/>
       </c>
-      <c r="I14" s="33" t="inlineStr">
+      <c r="I14" s="46" t="inlineStr">
         <is>
           <t>Conforme apuração do caixa.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="inlineStr">
-        <is>
-          <t>PRÊMIO COTA GERAL</t>
-        </is>
-      </c>
-      <c r="B15" s="35" t="n"/>
-      <c r="C15" s="35" t="n"/>
-      <c r="D15" s="35" t="n"/>
-      <c r="E15" s="35" t="n"/>
-      <c r="F15" s="35" t="n"/>
-      <c r="G15" s="35" t="n"/>
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 1 — VOLUME</t>
+        </is>
+      </c>
+      <c r="B15" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$17,MATCH(B$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="C15" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$17,MATCH(C$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$17,MATCH(D$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="E15" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$17,MATCH(E$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F15" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$17,MATCH(F$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$17,MATCH(G$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
       <c r="H15" s="20">
         <f>SUM(B15:G15)</f>
         <v/>
       </c>
-      <c r="I15" s="33" t="inlineStr">
-        <is>
-          <t>PREENCHER conforme a tabela de metas da loja (aba METAS da planilha original).</t>
+      <c r="I15" s="46" t="inlineStr">
+        <is>
+          <t>Da aba METAS SET.26: venda do mês contra a meta individual (80% / 100% / 120%).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="inlineStr">
-        <is>
-          <t>PRÊMIO PRÉ-VENCIDOS</t>
-        </is>
-      </c>
-      <c r="B16" s="35" t="n"/>
-      <c r="C16" s="35" t="n"/>
-      <c r="D16" s="35" t="n"/>
-      <c r="E16" s="35" t="n"/>
-      <c r="F16" s="35" t="n"/>
-      <c r="G16" s="35" t="n"/>
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
+        </is>
+      </c>
+      <c r="B16" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$17,MATCH(B$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="C16" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$17,MATCH(C$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$17,MATCH(D$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="E16" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$17,MATCH(E$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F16" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$17,MATCH(F$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$17,MATCH(G$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
       <c r="H16" s="20">
         <f>SUM(B16:G16)</f>
         <v/>
       </c>
-      <c r="I16" s="33" t="inlineStr">
-        <is>
-          <t>PREENCHER conforme a apuração de pré-vencidos de setembro.</t>
+      <c r="I16" s="46" t="inlineStr">
+        <is>
+          <t>Da aba METAS SET.26: vitaminas, packs, injetáveis, coquetel, brinco e kit ressaca.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="inlineStr">
-        <is>
-          <t>FÉRIAS (DIAS GOZADOS)</t>
-        </is>
-      </c>
-      <c r="B17" s="35" t="n"/>
-      <c r="C17" s="35" t="n"/>
-      <c r="D17" s="35" t="n"/>
-      <c r="E17" s="35" t="n"/>
-      <c r="F17" s="35" t="n"/>
-      <c r="G17" s="35" t="n"/>
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
+        </is>
+      </c>
+      <c r="B17" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$17,MATCH(B$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="C17" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$17,MATCH(C$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$17,MATCH(D$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="E17" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$17,MATCH(E$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F17" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$17,MATCH(F$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$17,MATCH(G$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
       <c r="H17" s="20">
         <f>SUM(B17:G17)</f>
         <v/>
       </c>
-      <c r="I17" s="33" t="inlineStr">
-        <is>
-          <t>PREENCHER se houve férias no mês; informar o período.</t>
+      <c r="I17" s="46" t="inlineStr">
+        <is>
+          <t>Da aba METAS SET.26: escada de pré-vencidos (farmacêuticos com regra própria).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
-        </is>
-      </c>
-      <c r="B18" s="35" t="n"/>
-      <c r="C18" s="35" t="n"/>
-      <c r="D18" s="35" t="n"/>
-      <c r="E18" s="35" t="n"/>
-      <c r="F18" s="35" t="n"/>
-      <c r="G18" s="35" t="n"/>
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
+        </is>
+      </c>
+      <c r="B18" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$17,MATCH(B$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="C18" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$17,MATCH(C$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="D18" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$17,MATCH(D$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="E18" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$17,MATCH(E$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F18" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$17,MATCH(F$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="G18" s="47">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$17,MATCH(G$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
       <c r="H18" s="20">
         <f>SUM(B18:G18)</f>
         <v/>
       </c>
-      <c r="I18" s="33" t="inlineStr">
-        <is>
-          <t>Calculado pela contabilidade sobre o valor das férias.</t>
+      <c r="I18" s="46" t="inlineStr">
+        <is>
+          <t>Da aba METAS SET.26: se a loja bateu, comissão de perfumaria em dobro + R$ 50 fixos.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="inlineStr">
-        <is>
-          <t>INCENTIVO APLICAÇÕES</t>
-        </is>
-      </c>
-      <c r="B19" s="34">
-        <f>'BASE INOVAFARMA SET.26'!G5</f>
-        <v/>
-      </c>
-      <c r="C19" s="34">
-        <f>'BASE INOVAFARMA SET.26'!G6</f>
-        <v/>
-      </c>
-      <c r="D19" s="34">
-        <f>'BASE INOVAFARMA SET.26'!G7</f>
-        <v/>
-      </c>
-      <c r="E19" s="34">
-        <f>'BASE INOVAFARMA SET.26'!G8</f>
-        <v/>
-      </c>
-      <c r="F19" s="34">
-        <f>'BASE INOVAFARMA SET.26'!G9</f>
-        <v/>
-      </c>
-      <c r="G19" s="34">
-        <f>'BASE INOVAFARMA SET.26'!G10</f>
-        <v/>
-      </c>
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>FÉRIAS (DIAS GOZADOS)</t>
+        </is>
+      </c>
+      <c r="B19" s="29" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="29" t="n"/>
+      <c r="G19" s="29" t="n"/>
       <c r="H19" s="20">
         <f>SUM(B19:G19)</f>
         <v/>
       </c>
-      <c r="I19" s="33" t="inlineStr">
-        <is>
-          <t>Incentivo de injetáveis apurado no InovaFarma.</t>
+      <c r="I19" s="46" t="inlineStr">
+        <is>
+          <t>PREENCHER se houve férias no mês; informar o período.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>INCENTIVO VITAMINAS</t>
-        </is>
-      </c>
-      <c r="B20" s="34">
-        <f>'BASE INOVAFARMA SET.26'!H5</f>
-        <v/>
-      </c>
-      <c r="C20" s="34">
-        <f>'BASE INOVAFARMA SET.26'!H6</f>
-        <v/>
-      </c>
-      <c r="D20" s="34">
-        <f>'BASE INOVAFARMA SET.26'!H7</f>
-        <v/>
-      </c>
-      <c r="E20" s="34">
-        <f>'BASE INOVAFARMA SET.26'!H8</f>
-        <v/>
-      </c>
-      <c r="F20" s="34">
-        <f>'BASE INOVAFARMA SET.26'!H9</f>
-        <v/>
-      </c>
-      <c r="G20" s="34">
-        <f>'BASE INOVAFARMA SET.26'!H10</f>
-        <v/>
-      </c>
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
+        </is>
+      </c>
+      <c r="B20" s="29" t="n"/>
+      <c r="C20" s="29" t="n"/>
+      <c r="D20" s="29" t="n"/>
+      <c r="E20" s="29" t="n"/>
+      <c r="F20" s="29" t="n"/>
+      <c r="G20" s="29" t="n"/>
       <c r="H20" s="20">
         <f>SUM(B20:G20)</f>
         <v/>
       </c>
-      <c r="I20" s="33" t="inlineStr">
-        <is>
-          <t>Grupo APLICAÇÃO E VITAMINAS INCENTIVO no InovaFarma.</t>
+      <c r="I20" s="46" t="inlineStr">
+        <is>
+          <t>Calculado pela contabilidade sobre o valor das férias.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="inlineStr">
-        <is>
-          <t>OUTROS INCENTIVOS</t>
-        </is>
-      </c>
-      <c r="B21" s="34">
-        <f>'BASE INOVAFARMA SET.26'!I5</f>
-        <v/>
-      </c>
-      <c r="C21" s="34">
-        <f>'BASE INOVAFARMA SET.26'!I6</f>
-        <v/>
-      </c>
-      <c r="D21" s="34">
-        <f>'BASE INOVAFARMA SET.26'!I7</f>
-        <v/>
-      </c>
-      <c r="E21" s="34">
-        <f>'BASE INOVAFARMA SET.26'!I8</f>
-        <v/>
-      </c>
-      <c r="F21" s="34">
-        <f>'BASE INOVAFARMA SET.26'!I9</f>
-        <v/>
-      </c>
-      <c r="G21" s="34">
-        <f>'BASE INOVAFARMA SET.26'!I10</f>
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t>INCENTIVO APLICAÇÕES</t>
+        </is>
+      </c>
+      <c r="B21" s="47">
+        <f>'BASE INOVAFARMA SET.26'!G5</f>
+        <v/>
+      </c>
+      <c r="C21" s="47">
+        <f>'BASE INOVAFARMA SET.26'!G6</f>
+        <v/>
+      </c>
+      <c r="D21" s="47">
+        <f>'BASE INOVAFARMA SET.26'!G7</f>
+        <v/>
+      </c>
+      <c r="E21" s="47">
+        <f>'BASE INOVAFARMA SET.26'!G8</f>
+        <v/>
+      </c>
+      <c r="F21" s="47">
+        <f>'BASE INOVAFARMA SET.26'!G9</f>
+        <v/>
+      </c>
+      <c r="G21" s="47">
+        <f>'BASE INOVAFARMA SET.26'!G10</f>
         <v/>
       </c>
       <c r="H21" s="20">
         <f>SUM(B21:G21)</f>
         <v/>
       </c>
-      <c r="I21" s="33" t="inlineStr">
-        <is>
-          <t>Populares, oficinais e similar normal.</t>
+      <c r="I21" s="46" t="inlineStr">
+        <is>
+          <t>Incentivo de injetáveis apurado no InovaFarma.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL DE PROVENTOS</t>
-        </is>
-      </c>
-      <c r="B22" s="20">
-        <f>SUM(B6:B21)-B9-B10</f>
-        <v/>
-      </c>
-      <c r="C22" s="20">
-        <f>SUM(C6:C21)-C9-C10</f>
-        <v/>
-      </c>
-      <c r="D22" s="20">
-        <f>SUM(D6:D21)-D9-D10</f>
-        <v/>
-      </c>
-      <c r="E22" s="20">
-        <f>SUM(E6:E21)-E9-E10</f>
-        <v/>
-      </c>
-      <c r="F22" s="20">
-        <f>SUM(F6:F21)-F9-F10</f>
-        <v/>
-      </c>
-      <c r="G22" s="20">
-        <f>SUM(G6:G21)-G9-G10</f>
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>INCENTIVO VITAMINAS</t>
+        </is>
+      </c>
+      <c r="B22" s="47">
+        <f>'BASE INOVAFARMA SET.26'!H5</f>
+        <v/>
+      </c>
+      <c r="C22" s="47">
+        <f>'BASE INOVAFARMA SET.26'!H6</f>
+        <v/>
+      </c>
+      <c r="D22" s="47">
+        <f>'BASE INOVAFARMA SET.26'!H7</f>
+        <v/>
+      </c>
+      <c r="E22" s="47">
+        <f>'BASE INOVAFARMA SET.26'!H8</f>
+        <v/>
+      </c>
+      <c r="F22" s="47">
+        <f>'BASE INOVAFARMA SET.26'!H9</f>
+        <v/>
+      </c>
+      <c r="G22" s="47">
+        <f>'BASE INOVAFARMA SET.26'!H10</f>
         <v/>
       </c>
       <c r="H22" s="20">
         <f>SUM(B22:G22)</f>
         <v/>
       </c>
-      <c r="I22" s="33" t="inlineStr">
-        <is>
-          <t>Soma das rubricas acima (a linha COMISSÃO TOTAL já engloba a comissão do InovaFarma e o complemento).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>DESCONTOS  (lançar com sinal negativo)</t>
-        </is>
-      </c>
-      <c r="B23" s="29" t="n"/>
-      <c r="C23" s="29" t="n"/>
-      <c r="D23" s="29" t="n"/>
-      <c r="E23" s="29" t="n"/>
-      <c r="F23" s="29" t="n"/>
-      <c r="G23" s="29" t="n"/>
-      <c r="H23" s="29" t="n"/>
-      <c r="I23" s="29" t="n"/>
+      <c r="I22" s="46" t="inlineStr">
+        <is>
+          <t>Grupo APLICAÇÃO E VITAMINAS INCENTIVO no InovaFarma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="43" t="inlineStr">
+        <is>
+          <t>OUTROS INCENTIVOS</t>
+        </is>
+      </c>
+      <c r="B23" s="47">
+        <f>'BASE INOVAFARMA SET.26'!I5</f>
+        <v/>
+      </c>
+      <c r="C23" s="47">
+        <f>'BASE INOVAFARMA SET.26'!I6</f>
+        <v/>
+      </c>
+      <c r="D23" s="47">
+        <f>'BASE INOVAFARMA SET.26'!I7</f>
+        <v/>
+      </c>
+      <c r="E23" s="47">
+        <f>'BASE INOVAFARMA SET.26'!I8</f>
+        <v/>
+      </c>
+      <c r="F23" s="47">
+        <f>'BASE INOVAFARMA SET.26'!I9</f>
+        <v/>
+      </c>
+      <c r="G23" s="47">
+        <f>'BASE INOVAFARMA SET.26'!I10</f>
+        <v/>
+      </c>
+      <c r="H23" s="20">
+        <f>SUM(B23:G23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="46" t="inlineStr">
+        <is>
+          <t>Populares, oficinais e similar normal.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="inlineStr">
-        <is>
-          <t>ADIANTAMENTO SALARIAL / VALES</t>
-        </is>
-      </c>
-      <c r="B24" s="35" t="n"/>
-      <c r="C24" s="35" t="n"/>
-      <c r="D24" s="35" t="n">
-        <v>-500</v>
-      </c>
-      <c r="E24" s="35" t="n"/>
-      <c r="F24" s="35" t="n"/>
-      <c r="G24" s="35" t="n"/>
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL DE PROVENTOS</t>
+        </is>
+      </c>
+      <c r="B24" s="20">
+        <f>SUM(B6:B23)-B9-B10</f>
+        <v/>
+      </c>
+      <c r="C24" s="20">
+        <f>SUM(C6:C23)-C9-C10</f>
+        <v/>
+      </c>
+      <c r="D24" s="20">
+        <f>SUM(D6:D23)-D9-D10</f>
+        <v/>
+      </c>
+      <c r="E24" s="20">
+        <f>SUM(E6:E23)-E9-E10</f>
+        <v/>
+      </c>
+      <c r="F24" s="20">
+        <f>SUM(F6:F23)-F9-F10</f>
+        <v/>
+      </c>
+      <c r="G24" s="20">
+        <f>SUM(G6:G23)-G9-G10</f>
+        <v/>
+      </c>
       <c r="H24" s="20">
         <f>SUM(B24:G24)</f>
         <v/>
       </c>
-      <c r="I24" s="33" t="inlineStr">
-        <is>
-          <t>PREENCHER com os vales adiantados durante setembro. GENECIR: adiantamento de R$ 500,00 em 09/09/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="30" t="inlineStr">
-        <is>
-          <t>ADIANT. VALES INCENT. E APLIC.</t>
-        </is>
-      </c>
-      <c r="B25" s="37">
-        <f>-(B19+B20+B21)</f>
-        <v/>
-      </c>
-      <c r="C25" s="37">
-        <f>-(C19+C20+C21)</f>
-        <v/>
-      </c>
-      <c r="D25" s="37">
-        <f>-(D19+D20+D21)</f>
-        <v/>
-      </c>
-      <c r="E25" s="37">
-        <f>-(E19+E20+E21)</f>
-        <v/>
-      </c>
-      <c r="F25" s="37">
-        <f>-(F19+F20+F21)</f>
-        <v/>
-      </c>
-      <c r="G25" s="37">
-        <f>-(G19+G20+G21)</f>
-        <v/>
-      </c>
-      <c r="H25" s="32">
-        <f>SUM(B25:G25)</f>
-        <v/>
-      </c>
-      <c r="I25" s="33" t="inlineStr">
-        <is>
-          <t>Estorno dos incentivos já adiantados em dinheiro no mês. AJUSTAR se algum incentivo não foi adiantado.</t>
-        </is>
-      </c>
+      <c r="I24" s="46" t="inlineStr">
+        <is>
+          <t>Soma das rubricas acima (a linha COMISSÃO TOTAL já engloba a comissão do InovaFarma e o complemento).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>DESCONTOS  (lançar com sinal negativo)</t>
+        </is>
+      </c>
+      <c r="B25" s="42" t="n"/>
+      <c r="C25" s="42" t="n"/>
+      <c r="D25" s="42" t="n"/>
+      <c r="E25" s="42" t="n"/>
+      <c r="F25" s="42" t="n"/>
+      <c r="G25" s="42" t="n"/>
+      <c r="H25" s="42" t="n"/>
+      <c r="I25" s="42" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="inlineStr">
-        <is>
-          <t>CONVÊNIO</t>
-        </is>
-      </c>
-      <c r="B26" s="35" t="n"/>
-      <c r="C26" s="35" t="n"/>
-      <c r="D26" s="35" t="n"/>
-      <c r="E26" s="35" t="n"/>
-      <c r="F26" s="35" t="n"/>
-      <c r="G26" s="35" t="n"/>
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
+        </is>
+      </c>
+      <c r="B26" s="29" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="29" t="n">
+        <v>-500</v>
+      </c>
+      <c r="E26" s="29" t="n"/>
+      <c r="F26" s="29" t="n"/>
+      <c r="G26" s="29" t="n"/>
       <c r="H26" s="20">
         <f>SUM(B26:G26)</f>
         <v/>
       </c>
-      <c r="I26" s="33" t="inlineStr">
+      <c r="I26" s="46" t="inlineStr">
+        <is>
+          <t>PREENCHER com os vales adiantados durante setembro. GENECIR: adiantamento de R$ 500,00 em 09/09/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="inlineStr">
+        <is>
+          <t>ADIANT. VALES INCENT. E APLIC.</t>
+        </is>
+      </c>
+      <c r="B27" s="49">
+        <f>-(B21+B22+B23)</f>
+        <v/>
+      </c>
+      <c r="C27" s="49">
+        <f>-(C21+C22+C23)</f>
+        <v/>
+      </c>
+      <c r="D27" s="49">
+        <f>-(D21+D22+D23)</f>
+        <v/>
+      </c>
+      <c r="E27" s="49">
+        <f>-(E21+E22+E23)</f>
+        <v/>
+      </c>
+      <c r="F27" s="49">
+        <f>-(F21+F22+F23)</f>
+        <v/>
+      </c>
+      <c r="G27" s="49">
+        <f>-(G21+G22+G23)</f>
+        <v/>
+      </c>
+      <c r="H27" s="45">
+        <f>SUM(B27:G27)</f>
+        <v/>
+      </c>
+      <c r="I27" s="46" t="inlineStr">
+        <is>
+          <t>Estorno dos incentivos já adiantados em dinheiro no mês. AJUSTAR se algum incentivo não foi adiantado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="inlineStr">
+        <is>
+          <t>CONVÊNIO</t>
+        </is>
+      </c>
+      <c r="B28" s="29" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="29" t="n"/>
+      <c r="E28" s="29" t="n"/>
+      <c r="F28" s="29" t="n"/>
+      <c r="G28" s="29" t="n"/>
+      <c r="H28" s="20">
+        <f>SUM(B28:G28)</f>
+        <v/>
+      </c>
+      <c r="I28" s="46" t="inlineStr">
         <is>
           <t>PREENCHER conforme o convênio de setembro.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="30" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="43" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="B27" s="35" t="n"/>
-      <c r="C27" s="35" t="n"/>
-      <c r="D27" s="35" t="n"/>
-      <c r="E27" s="35" t="n"/>
-      <c r="F27" s="35" t="n"/>
-      <c r="G27" s="35" t="n"/>
-      <c r="H27" s="20">
-        <f>SUM(B27:G27)</f>
-        <v/>
-      </c>
-      <c r="I27" s="33" t="inlineStr">
-        <is>
-          <t>PREENCHER conforme o ponto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="30" t="inlineStr">
-        <is>
-          <t>DESCONTO VALE TRANSPORTE 6%</t>
-        </is>
-      </c>
-      <c r="B28" s="31" t="n"/>
-      <c r="C28" s="31" t="n">
-        <v>-84.29000000000001</v>
-      </c>
-      <c r="D28" s="31" t="n">
-        <v>-84.29000000000001</v>
-      </c>
-      <c r="E28" s="31" t="n"/>
-      <c r="F28" s="31" t="n">
-        <v>-84.29000000000001</v>
-      </c>
-      <c r="G28" s="31" t="n"/>
-      <c r="H28" s="32">
-        <f>SUM(B28:G28)</f>
-        <v/>
-      </c>
-      <c r="I28" s="33" t="inlineStr">
-        <is>
-          <t>Valores praticados em ago/26. 6% sobre R$ 1.621,00 seria R$ 97,26 — CONFERIR a base usada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>DESCONTO INSS</t>
-        </is>
-      </c>
-      <c r="B29" s="35" t="n"/>
-      <c r="C29" s="35" t="n"/>
-      <c r="D29" s="35" t="n"/>
-      <c r="E29" s="35" t="n"/>
-      <c r="F29" s="35" t="n"/>
-      <c r="G29" s="35" t="n"/>
+      <c r="B29" s="29" t="n"/>
+      <c r="C29" s="29" t="n"/>
+      <c r="D29" s="29" t="n"/>
+      <c r="E29" s="29" t="n"/>
+      <c r="F29" s="29" t="n"/>
+      <c r="G29" s="29" t="n"/>
       <c r="H29" s="20">
         <f>SUM(B29:G29)</f>
         <v/>
       </c>
-      <c r="I29" s="33" t="inlineStr">
-        <is>
-          <t>A CALCULAR PELA CONTABILIDADE sobre o total de proventos.</t>
+      <c r="I29" s="46" t="inlineStr">
+        <is>
+          <t>PREENCHER conforme o ponto.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="inlineStr">
-        <is>
-          <t>DESCONTO IRRF</t>
-        </is>
-      </c>
-      <c r="B30" s="35" t="n"/>
-      <c r="C30" s="35" t="n"/>
-      <c r="D30" s="35" t="n"/>
-      <c r="E30" s="35" t="n"/>
-      <c r="F30" s="35" t="n"/>
-      <c r="G30" s="35" t="n"/>
-      <c r="H30" s="20">
+      <c r="A30" s="43" t="inlineStr">
+        <is>
+          <t>DESCONTO VALE TRANSPORTE 6%</t>
+        </is>
+      </c>
+      <c r="B30" s="44" t="n"/>
+      <c r="C30" s="44" t="n">
+        <v>-84.29000000000001</v>
+      </c>
+      <c r="D30" s="44" t="n">
+        <v>-84.29000000000001</v>
+      </c>
+      <c r="E30" s="44" t="n"/>
+      <c r="F30" s="44" t="n">
+        <v>-84.29000000000001</v>
+      </c>
+      <c r="G30" s="44" t="n"/>
+      <c r="H30" s="45">
         <f>SUM(B30:G30)</f>
         <v/>
       </c>
-      <c r="I30" s="33" t="inlineStr">
-        <is>
-          <t>A CALCULAR PELA CONTABILIDADE.</t>
+      <c r="I30" s="46" t="inlineStr">
+        <is>
+          <t>Valores praticados em ago/26. 6% sobre R$ 1.621,00 seria R$ 97,26 — CONFERIR a base usada.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL DE DESCONTOS</t>
-        </is>
-      </c>
-      <c r="B31" s="20">
-        <f>SUM(B24:B30)</f>
-        <v/>
-      </c>
-      <c r="C31" s="20">
-        <f>SUM(C24:C30)</f>
-        <v/>
-      </c>
-      <c r="D31" s="20">
-        <f>SUM(D24:D30)</f>
-        <v/>
-      </c>
-      <c r="E31" s="20">
-        <f>SUM(E24:E30)</f>
-        <v/>
-      </c>
-      <c r="F31" s="20">
-        <f>SUM(F24:F30)</f>
-        <v/>
-      </c>
-      <c r="G31" s="20">
-        <f>SUM(G24:G30)</f>
-        <v/>
-      </c>
+      <c r="A31" s="43" t="inlineStr">
+        <is>
+          <t>DESCONTO INSS</t>
+        </is>
+      </c>
+      <c r="B31" s="29" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="29" t="n"/>
+      <c r="F31" s="29" t="n"/>
+      <c r="G31" s="29" t="n"/>
       <c r="H31" s="20">
         <f>SUM(B31:G31)</f>
         <v/>
       </c>
-      <c r="I31" s="33" t="inlineStr"/>
-    </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>LÍQUIDO</t>
+      <c r="I31" s="46" t="inlineStr">
+        <is>
+          <t>A CALCULAR PELA CONTABILIDADE sobre o total de proventos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>DESCONTO IRRF</t>
         </is>
       </c>
       <c r="B32" s="29" t="n"/>
@@ -2746,210 +3548,268 @@
       <c r="E32" s="29" t="n"/>
       <c r="F32" s="29" t="n"/>
       <c r="G32" s="29" t="n"/>
-      <c r="H32" s="29" t="n"/>
-      <c r="I32" s="29" t="n"/>
+      <c r="H32" s="20">
+        <f>SUM(B32:G32)</f>
+        <v/>
+      </c>
+      <c r="I32" s="46" t="inlineStr">
+        <is>
+          <t>A CALCULAR PELA CONTABILIDADE.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="15" t="inlineStr">
         <is>
-          <t>LÍQUIDO A RECEBER (05/10/2026)</t>
-        </is>
-      </c>
-      <c r="B33" s="38">
-        <f>B22+B31</f>
-        <v/>
-      </c>
-      <c r="C33" s="38">
-        <f>C22+C31</f>
-        <v/>
-      </c>
-      <c r="D33" s="38">
-        <f>D22+D31</f>
-        <v/>
-      </c>
-      <c r="E33" s="38">
-        <f>E22+E31</f>
-        <v/>
-      </c>
-      <c r="F33" s="38">
-        <f>F22+F31</f>
-        <v/>
-      </c>
-      <c r="G33" s="38">
-        <f>G22+G31</f>
-        <v/>
-      </c>
-      <c r="H33" s="38">
+          <t>TOTAL DE DESCONTOS</t>
+        </is>
+      </c>
+      <c r="B33" s="20">
+        <f>SUM(B26:B32)</f>
+        <v/>
+      </c>
+      <c r="C33" s="20">
+        <f>SUM(C26:C32)</f>
+        <v/>
+      </c>
+      <c r="D33" s="20">
+        <f>SUM(D26:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="20">
+        <f>SUM(E26:E32)</f>
+        <v/>
+      </c>
+      <c r="F33" s="20">
+        <f>SUM(F26:F32)</f>
+        <v/>
+      </c>
+      <c r="G33" s="20">
+        <f>SUM(G26:G32)</f>
+        <v/>
+      </c>
+      <c r="H33" s="20">
         <f>SUM(B33:G33)</f>
         <v/>
       </c>
-      <c r="I33" s="33" t="inlineStr">
-        <is>
-          <t>Total de proventos menos descontos. Só fica definitivo depois do INSS/IRRF da contabilidade.</t>
-        </is>
-      </c>
+      <c r="I33" s="46" t="inlineStr"/>
     </row>
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t>LÍQUIDO</t>
+        </is>
+      </c>
+      <c r="B34" s="42" t="n"/>
+      <c r="C34" s="42" t="n"/>
+      <c r="D34" s="42" t="n"/>
+      <c r="E34" s="42" t="n"/>
+      <c r="F34" s="42" t="n"/>
+      <c r="G34" s="42" t="n"/>
+      <c r="H34" s="42" t="n"/>
+      <c r="I34" s="42" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>LÍQUIDO A RECEBER (05/10/2026)</t>
+        </is>
+      </c>
+      <c r="B35" s="36">
+        <f>B24+B33</f>
+        <v/>
+      </c>
+      <c r="C35" s="36">
+        <f>C24+C33</f>
+        <v/>
+      </c>
+      <c r="D35" s="36">
+        <f>D24+D33</f>
+        <v/>
+      </c>
+      <c r="E35" s="36">
+        <f>E24+E33</f>
+        <v/>
+      </c>
+      <c r="F35" s="36">
+        <f>F24+F33</f>
+        <v/>
+      </c>
+      <c r="G35" s="36">
+        <f>G24+G33</f>
+        <v/>
+      </c>
+      <c r="H35" s="36">
+        <f>SUM(B35:G35)</f>
+        <v/>
+      </c>
+      <c r="I35" s="46" t="inlineStr">
+        <is>
+          <t>Total de proventos menos descontos. Só fica definitivo depois do INSS/IRRF da contabilidade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
           <t>INFORMATIVO — PAGO PELA EMPRESA, NÃO ENTRA NO HOLERITE</t>
         </is>
       </c>
-      <c r="B34" s="29" t="n"/>
-      <c r="C34" s="29" t="n"/>
-      <c r="D34" s="29" t="n"/>
-      <c r="E34" s="29" t="n"/>
-      <c r="F34" s="29" t="n"/>
-      <c r="G34" s="29" t="n"/>
-      <c r="H34" s="29" t="n"/>
-      <c r="I34" s="29" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="30" t="inlineStr">
+      <c r="B36" s="42" t="n"/>
+      <c r="C36" s="42" t="n"/>
+      <c r="D36" s="42" t="n"/>
+      <c r="E36" s="42" t="n"/>
+      <c r="F36" s="42" t="n"/>
+      <c r="G36" s="42" t="n"/>
+      <c r="H36" s="42" t="n"/>
+      <c r="I36" s="42" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="43" t="inlineStr">
         <is>
           <t>VALE TRANSPORTE (compra out/26)</t>
         </is>
       </c>
-      <c r="B35" s="35" t="n"/>
-      <c r="C35" s="35" t="n"/>
-      <c r="D35" s="35" t="n">
+      <c r="B37" s="29" t="n"/>
+      <c r="C37" s="29" t="n"/>
+      <c r="D37" s="29" t="n">
         <v>270</v>
       </c>
-      <c r="E35" s="35" t="n"/>
-      <c r="F35" s="35" t="n"/>
-      <c r="G35" s="35" t="n"/>
-      <c r="H35" s="20">
-        <f>SUM(B35:G35)</f>
-        <v/>
-      </c>
-      <c r="I35" s="33" t="inlineStr">
+      <c r="E37" s="29" t="n"/>
+      <c r="F37" s="29" t="n"/>
+      <c r="G37" s="29" t="n"/>
+      <c r="H37" s="20">
+        <f>SUM(B37:G37)</f>
+        <v/>
+      </c>
+      <c r="I37" s="46" t="inlineStr">
         <is>
           <t>PREENCHER com as passagens compradas. GENECIR: R$ 270,00 de vale-transporte.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="30" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="43" t="inlineStr">
         <is>
           <t>VALE ALIMENTAÇÃO FERIADOS E DOMINGOS</t>
         </is>
       </c>
-      <c r="B36" s="35" t="n"/>
-      <c r="C36" s="35" t="n"/>
-      <c r="D36" s="35" t="n"/>
-      <c r="E36" s="35" t="n"/>
-      <c r="F36" s="35" t="n"/>
-      <c r="G36" s="35" t="n"/>
-      <c r="H36" s="20">
-        <f>SUM(B36:G36)</f>
-        <v/>
-      </c>
-      <c r="I36" s="33" t="inlineStr">
+      <c r="B38" s="29" t="n"/>
+      <c r="C38" s="29" t="n"/>
+      <c r="D38" s="29" t="n"/>
+      <c r="E38" s="29" t="n"/>
+      <c r="F38" s="29" t="n"/>
+      <c r="G38" s="29" t="n"/>
+      <c r="H38" s="20">
+        <f>SUM(B38:G38)</f>
+        <v/>
+      </c>
+      <c r="I38" s="46" t="inlineStr">
         <is>
           <t>PREENCHER conforme escala de domingos e feriados.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="30" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="43" t="inlineStr">
         <is>
           <t>FÉRIAS PAGAS À PARTE (CONTAS A PAGAR)</t>
         </is>
       </c>
-      <c r="B37" s="31" t="n"/>
-      <c r="C37" s="31" t="n"/>
-      <c r="D37" s="31" t="n"/>
-      <c r="E37" s="31" t="n"/>
-      <c r="F37" s="31" t="n"/>
-      <c r="G37" s="31" t="n"/>
-      <c r="H37" s="32">
-        <f>SUM(B37:G37)</f>
-        <v/>
-      </c>
-      <c r="I37" s="33" t="inlineStr">
+      <c r="B39" s="44" t="n"/>
+      <c r="C39" s="44" t="n"/>
+      <c r="D39" s="44" t="n"/>
+      <c r="E39" s="44" t="n"/>
+      <c r="F39" s="44" t="n"/>
+      <c r="G39" s="44" t="n"/>
+      <c r="H39" s="45">
+        <f>SUM(B39:G39)</f>
+        <v/>
+      </c>
+      <c r="I39" s="46" t="inlineStr">
         <is>
           <t>Recibo de férias pago fora do holerite — lembrete para o contas a pagar. RENALDO: férias de 01 a 30/09/2026 — informar o valor do recibo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="21" t="inlineStr">
-        <is>
-          <t>LEGENDA</t>
-        </is>
-      </c>
-      <c r="B39" s="22" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="21" t="inlineStr">
-        <is>
-          <t>Célula amarela, texto azul</t>
-        </is>
-      </c>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
-          <t>Célula laranja</t>
-        </is>
-      </c>
-      <c r="B41" s="22" t="inlineStr">
-        <is>
-          <t>valor repetido de agosto/2026 — CONFERIR se continua válido em setembro.</t>
-        </is>
-      </c>
+          <t>LEGENDA</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="21" t="inlineStr">
         <is>
-          <t>Texto verde</t>
+          <t>Célula amarela, texto azul</t>
         </is>
       </c>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>valor puxado da aba BASE INOVAFARMA SET.26 (não digitar por cima).</t>
+          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="inlineStr">
         <is>
+          <t>Célula laranja</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>valor repetido de agosto/2026 — CONFERIR se continua válido em setembro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="inlineStr">
+        <is>
+          <t>Texto verde</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>valor puxado da aba BASE INOVAFARMA SET.26 (não digitar por cima).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
           <t>Texto preto em célula verde</t>
         </is>
       </c>
-      <c r="B43" s="22" t="inlineStr">
+      <c r="B45" s="22" t="inlineStr">
         <is>
           <t>resultado de fórmula — não alterar.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I37"/>
+  <autoFilter ref="A4:I39"/>
   <mergeCells count="7">
+    <mergeCell ref="B44:I44"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="B39:I39"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B42:I42"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="B41:I41"/>
     <mergeCell ref="B43:I43"/>
-    <mergeCell ref="B41:I41"/>
-    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E153"/>
+  <dimension ref="A1:E165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2974,3202 +3834,3466 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" s="40" t="inlineStr">
         <is>
           <t>FUNCIONÁRIO</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>RUBRICA</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="D4" s="27" t="inlineStr">
+      <c r="D4" s="40" t="inlineStr">
         <is>
           <t>VALOR</t>
         </is>
       </c>
-      <c r="E4" s="27" t="inlineStr">
+      <c r="E4" s="40" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C5" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D5" s="34">
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D5" s="47">
         <f>'HOLERITE SET.26'!B6</f>
         <v/>
       </c>
-      <c r="E5" s="39" t="n"/>
+      <c r="E5" s="50" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C6" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D6" s="34">
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D6" s="47">
         <f>'HOLERITE SET.26'!B7</f>
         <v/>
       </c>
-      <c r="E6" s="39" t="n"/>
+      <c r="E6" s="50" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="inlineStr">
+      <c r="A7" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C7" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D7" s="34">
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D7" s="47">
         <f>'HOLERITE SET.26'!B8</f>
         <v/>
       </c>
-      <c r="E7" s="39" t="n"/>
+      <c r="E7" s="50" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="43" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D8" s="34">
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D8" s="47">
         <f>'HOLERITE SET.26'!B11</f>
         <v/>
       </c>
-      <c r="E8" s="39" t="n"/>
+      <c r="E8" s="50" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="inlineStr">
+      <c r="A9" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="43" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C9" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D9" s="34">
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D9" s="47">
         <f>'HOLERITE SET.26'!B12</f>
         <v/>
       </c>
-      <c r="E9" s="39" t="n"/>
+      <c r="E9" s="50" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="43" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C10" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D10" s="34">
+      <c r="C10" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D10" s="47">
         <f>'HOLERITE SET.26'!B13</f>
         <v/>
       </c>
-      <c r="E10" s="39" t="n"/>
+      <c r="E10" s="50" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="inlineStr">
+      <c r="A11" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="43" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C11" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D11" s="34">
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D11" s="47">
         <f>'HOLERITE SET.26'!B14</f>
         <v/>
       </c>
-      <c r="E11" s="39" t="n"/>
+      <c r="E11" s="50" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>PRÊMIO COTA GERAL</t>
-        </is>
-      </c>
-      <c r="C12" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D12" s="34">
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 1 — VOLUME</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D12" s="47">
         <f>'HOLERITE SET.26'!B15</f>
         <v/>
       </c>
-      <c r="E12" s="39" t="n"/>
+      <c r="E12" s="50" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="inlineStr">
+      <c r="A13" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B13" s="30" t="inlineStr">
-        <is>
-          <t>PRÊMIO PRÉ-VENCIDOS</t>
-        </is>
-      </c>
-      <c r="C13" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D13" s="34">
+      <c r="B13" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D13" s="47">
         <f>'HOLERITE SET.26'!B16</f>
         <v/>
       </c>
-      <c r="E13" s="39" t="n"/>
+      <c r="E13" s="50" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="A14" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D14" s="47">
+        <f>'HOLERITE SET.26'!B17</f>
+        <v/>
+      </c>
+      <c r="E14" s="50" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>ARIANE</t>
+        </is>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D15" s="47">
+        <f>'HOLERITE SET.26'!B18</f>
+        <v/>
+      </c>
+      <c r="E15" s="50" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>ARIANE</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C14" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D14" s="34">
-        <f>'HOLERITE SET.26'!B17</f>
-        <v/>
-      </c>
-      <c r="E14" s="39" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D16" s="47">
+        <f>'HOLERITE SET.26'!B19</f>
+        <v/>
+      </c>
+      <c r="E16" s="50" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B15" s="30" t="inlineStr">
+      <c r="B17" s="43" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C15" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D15" s="34">
-        <f>'HOLERITE SET.26'!B18</f>
-        <v/>
-      </c>
-      <c r="E15" s="39" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="C17" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D17" s="47">
+        <f>'HOLERITE SET.26'!B20</f>
+        <v/>
+      </c>
+      <c r="E17" s="50" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B18" s="43" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C16" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D16" s="34">
-        <f>'HOLERITE SET.26'!B19</f>
-        <v/>
-      </c>
-      <c r="E16" s="39" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="30" t="inlineStr">
+      <c r="C18" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D18" s="47">
+        <f>'HOLERITE SET.26'!B21</f>
+        <v/>
+      </c>
+      <c r="E18" s="50" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B17" s="30" t="inlineStr">
+      <c r="B19" s="43" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C17" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D17" s="34">
-        <f>'HOLERITE SET.26'!B20</f>
-        <v/>
-      </c>
-      <c r="E17" s="39" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="C19" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D19" s="47">
+        <f>'HOLERITE SET.26'!B22</f>
+        <v/>
+      </c>
+      <c r="E19" s="50" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B18" s="30" t="inlineStr">
+      <c r="B20" s="43" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C18" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D18" s="34">
-        <f>'HOLERITE SET.26'!B21</f>
-        <v/>
-      </c>
-      <c r="E18" s="39" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="40" t="inlineStr">
+      <c r="C20" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D20" s="47">
+        <f>'HOLERITE SET.26'!B23</f>
+        <v/>
+      </c>
+      <c r="E20" s="50" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="51" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B19" s="40" t="inlineStr">
+      <c r="B21" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C19" s="40" t="inlineStr">
+      <c r="C21" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D19" s="41">
-        <f>'HOLERITE SET.26'!B22</f>
-        <v/>
-      </c>
-      <c r="E19" s="18" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="D21" s="52">
+        <f>'HOLERITE SET.26'!B24</f>
+        <v/>
+      </c>
+      <c r="E21" s="18" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
+      <c r="B22" s="43" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C20" s="30" t="inlineStr">
+      <c r="C22" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D20" s="34">
-        <f>'HOLERITE SET.26'!B24</f>
-        <v/>
-      </c>
-      <c r="E20" s="39" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="D22" s="47">
+        <f>'HOLERITE SET.26'!B26</f>
+        <v/>
+      </c>
+      <c r="E22" s="50" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B21" s="30" t="inlineStr">
+      <c r="B23" s="43" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C21" s="30" t="inlineStr">
+      <c r="C23" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D21" s="34">
-        <f>'HOLERITE SET.26'!B25</f>
-        <v/>
-      </c>
-      <c r="E21" s="39" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="30" t="inlineStr">
+      <c r="D23" s="47">
+        <f>'HOLERITE SET.26'!B27</f>
+        <v/>
+      </c>
+      <c r="E23" s="50" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B24" s="43" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C22" s="30" t="inlineStr">
+      <c r="C24" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D22" s="34">
-        <f>'HOLERITE SET.26'!B26</f>
-        <v/>
-      </c>
-      <c r="E22" s="39" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="D24" s="47">
+        <f>'HOLERITE SET.26'!B28</f>
+        <v/>
+      </c>
+      <c r="E24" s="50" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B23" s="30" t="inlineStr">
+      <c r="B25" s="43" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C23" s="30" t="inlineStr">
+      <c r="C25" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D23" s="34">
-        <f>'HOLERITE SET.26'!B27</f>
-        <v/>
-      </c>
-      <c r="E23" s="39" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="D25" s="47">
+        <f>'HOLERITE SET.26'!B29</f>
+        <v/>
+      </c>
+      <c r="E25" s="50" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B26" s="43" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C24" s="30" t="inlineStr">
+      <c r="C26" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D24" s="34">
-        <f>'HOLERITE SET.26'!B28</f>
-        <v/>
-      </c>
-      <c r="E24" s="39" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="30" t="inlineStr">
+      <c r="D26" s="47">
+        <f>'HOLERITE SET.26'!B30</f>
+        <v/>
+      </c>
+      <c r="E26" s="50" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B25" s="30" t="inlineStr">
+      <c r="B27" s="43" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C25" s="30" t="inlineStr">
+      <c r="C27" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D25" s="34">
-        <f>'HOLERITE SET.26'!B29</f>
-        <v/>
-      </c>
-      <c r="E25" s="39" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="30" t="inlineStr">
+      <c r="D27" s="47">
+        <f>'HOLERITE SET.26'!B31</f>
+        <v/>
+      </c>
+      <c r="E27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="43" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B28" s="43" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C26" s="30" t="inlineStr">
+      <c r="C28" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D26" s="34">
-        <f>'HOLERITE SET.26'!B30</f>
-        <v/>
-      </c>
-      <c r="E26" s="39" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="40" t="inlineStr">
+      <c r="D28" s="47">
+        <f>'HOLERITE SET.26'!B32</f>
+        <v/>
+      </c>
+      <c r="E28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="51" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B27" s="40" t="inlineStr">
+      <c r="B29" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C27" s="40" t="inlineStr">
+      <c r="C29" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D27" s="41">
-        <f>'HOLERITE SET.26'!B31</f>
-        <v/>
-      </c>
-      <c r="E27" s="18" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="42" t="inlineStr">
+      <c r="D29" s="52">
+        <f>'HOLERITE SET.26'!B33</f>
+        <v/>
+      </c>
+      <c r="E29" s="18" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="53" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B28" s="43" t="inlineStr">
+      <c r="B30" s="54" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C28" s="43" t="inlineStr">
+      <c r="C30" s="54" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D28" s="44">
-        <f>'HOLERITE SET.26'!B33</f>
-        <v/>
-      </c>
-      <c r="E28" s="45" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="30" t="inlineStr">
+      <c r="D30" s="55">
+        <f>'HOLERITE SET.26'!B35</f>
+        <v/>
+      </c>
+      <c r="E30" s="56" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B32" s="43" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C30" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D30" s="34">
+      <c r="C32" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D32" s="47">
         <f>'HOLERITE SET.26'!C6</f>
         <v/>
       </c>
-      <c r="E30" s="39" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="30" t="inlineStr">
+      <c r="E32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B31" s="30" t="inlineStr">
+      <c r="B33" s="43" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C31" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D31" s="34">
+      <c r="C33" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D33" s="47">
         <f>'HOLERITE SET.26'!C7</f>
         <v/>
       </c>
-      <c r="E31" s="39" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="30" t="inlineStr">
+      <c r="E33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B32" s="30" t="inlineStr">
+      <c r="B34" s="43" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C32" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D32" s="34">
+      <c r="C34" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D34" s="47">
         <f>'HOLERITE SET.26'!C8</f>
         <v/>
       </c>
-      <c r="E32" s="39" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="30" t="inlineStr">
+      <c r="E34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B33" s="30" t="inlineStr">
+      <c r="B35" s="43" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C33" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D33" s="34">
+      <c r="C35" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D35" s="47">
         <f>'HOLERITE SET.26'!C11</f>
         <v/>
       </c>
-      <c r="E33" s="39" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="30" t="inlineStr">
+      <c r="E35" s="50" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B34" s="30" t="inlineStr">
+      <c r="B36" s="43" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C34" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D34" s="34">
+      <c r="C36" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D36" s="47">
         <f>'HOLERITE SET.26'!C12</f>
         <v/>
       </c>
-      <c r="E34" s="39" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="30" t="inlineStr">
+      <c r="E36" s="50" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B35" s="30" t="inlineStr">
+      <c r="B37" s="43" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C35" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D35" s="34">
+      <c r="C37" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D37" s="47">
         <f>'HOLERITE SET.26'!C13</f>
         <v/>
       </c>
-      <c r="E35" s="39" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="30" t="inlineStr">
+      <c r="E37" s="50" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B36" s="30" t="inlineStr">
+      <c r="B38" s="43" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C36" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D36" s="34">
+      <c r="C38" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D38" s="47">
         <f>'HOLERITE SET.26'!C14</f>
         <v/>
       </c>
-      <c r="E36" s="39" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="30" t="inlineStr">
+      <c r="E38" s="50" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B37" s="30" t="inlineStr">
-        <is>
-          <t>PRÊMIO COTA GERAL</t>
-        </is>
-      </c>
-      <c r="C37" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D37" s="34">
+      <c r="B39" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 1 — VOLUME</t>
+        </is>
+      </c>
+      <c r="C39" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D39" s="47">
         <f>'HOLERITE SET.26'!C15</f>
         <v/>
       </c>
-      <c r="E37" s="39" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="30" t="inlineStr">
+      <c r="E39" s="50" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B38" s="30" t="inlineStr">
-        <is>
-          <t>PRÊMIO PRÉ-VENCIDOS</t>
-        </is>
-      </c>
-      <c r="C38" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D38" s="34">
+      <c r="B40" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
+        </is>
+      </c>
+      <c r="C40" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D40" s="47">
         <f>'HOLERITE SET.26'!C16</f>
         <v/>
       </c>
-      <c r="E38" s="39" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="30" t="inlineStr">
+      <c r="E40" s="50" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B39" s="30" t="inlineStr">
+      <c r="B41" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
+        </is>
+      </c>
+      <c r="C41" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D41" s="47">
+        <f>'HOLERITE SET.26'!C17</f>
+        <v/>
+      </c>
+      <c r="E41" s="50" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="43" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B42" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
+        </is>
+      </c>
+      <c r="C42" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D42" s="47">
+        <f>'HOLERITE SET.26'!C18</f>
+        <v/>
+      </c>
+      <c r="E42" s="50" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="43" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B43" s="43" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C39" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D39" s="34">
-        <f>'HOLERITE SET.26'!C17</f>
-        <v/>
-      </c>
-      <c r="E39" s="39" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="30" t="inlineStr">
+      <c r="C43" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D43" s="47">
+        <f>'HOLERITE SET.26'!C19</f>
+        <v/>
+      </c>
+      <c r="E43" s="50" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B40" s="30" t="inlineStr">
+      <c r="B44" s="43" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C40" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D40" s="34">
-        <f>'HOLERITE SET.26'!C18</f>
-        <v/>
-      </c>
-      <c r="E40" s="39" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="30" t="inlineStr">
+      <c r="C44" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D44" s="47">
+        <f>'HOLERITE SET.26'!C20</f>
+        <v/>
+      </c>
+      <c r="E44" s="50" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B41" s="30" t="inlineStr">
+      <c r="B45" s="43" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C41" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D41" s="34">
-        <f>'HOLERITE SET.26'!C19</f>
-        <v/>
-      </c>
-      <c r="E41" s="39" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="30" t="inlineStr">
+      <c r="C45" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D45" s="47">
+        <f>'HOLERITE SET.26'!C21</f>
+        <v/>
+      </c>
+      <c r="E45" s="50" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B42" s="30" t="inlineStr">
+      <c r="B46" s="43" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C42" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D42" s="34">
-        <f>'HOLERITE SET.26'!C20</f>
-        <v/>
-      </c>
-      <c r="E42" s="39" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="30" t="inlineStr">
+      <c r="C46" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D46" s="47">
+        <f>'HOLERITE SET.26'!C22</f>
+        <v/>
+      </c>
+      <c r="E46" s="50" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B43" s="30" t="inlineStr">
+      <c r="B47" s="43" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C43" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D43" s="34">
-        <f>'HOLERITE SET.26'!C21</f>
-        <v/>
-      </c>
-      <c r="E43" s="39" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="40" t="inlineStr">
+      <c r="C47" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D47" s="47">
+        <f>'HOLERITE SET.26'!C23</f>
+        <v/>
+      </c>
+      <c r="E47" s="50" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="51" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B44" s="40" t="inlineStr">
+      <c r="B48" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C44" s="40" t="inlineStr">
+      <c r="C48" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D44" s="41">
-        <f>'HOLERITE SET.26'!C22</f>
-        <v/>
-      </c>
-      <c r="E44" s="18" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="30" t="inlineStr">
+      <c r="D48" s="52">
+        <f>'HOLERITE SET.26'!C24</f>
+        <v/>
+      </c>
+      <c r="E48" s="18" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B45" s="30" t="inlineStr">
+      <c r="B49" s="43" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C45" s="30" t="inlineStr">
+      <c r="C49" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D45" s="34">
-        <f>'HOLERITE SET.26'!C24</f>
-        <v/>
-      </c>
-      <c r="E45" s="39" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="30" t="inlineStr">
+      <c r="D49" s="47">
+        <f>'HOLERITE SET.26'!C26</f>
+        <v/>
+      </c>
+      <c r="E49" s="50" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B46" s="30" t="inlineStr">
+      <c r="B50" s="43" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C46" s="30" t="inlineStr">
+      <c r="C50" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D46" s="34">
-        <f>'HOLERITE SET.26'!C25</f>
-        <v/>
-      </c>
-      <c r="E46" s="39" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="30" t="inlineStr">
+      <c r="D50" s="47">
+        <f>'HOLERITE SET.26'!C27</f>
+        <v/>
+      </c>
+      <c r="E50" s="50" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B47" s="30" t="inlineStr">
+      <c r="B51" s="43" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C47" s="30" t="inlineStr">
+      <c r="C51" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D47" s="34">
-        <f>'HOLERITE SET.26'!C26</f>
-        <v/>
-      </c>
-      <c r="E47" s="39" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="30" t="inlineStr">
+      <c r="D51" s="47">
+        <f>'HOLERITE SET.26'!C28</f>
+        <v/>
+      </c>
+      <c r="E51" s="50" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B48" s="30" t="inlineStr">
+      <c r="B52" s="43" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C48" s="30" t="inlineStr">
+      <c r="C52" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D48" s="34">
-        <f>'HOLERITE SET.26'!C27</f>
-        <v/>
-      </c>
-      <c r="E48" s="39" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="30" t="inlineStr">
+      <c r="D52" s="47">
+        <f>'HOLERITE SET.26'!C29</f>
+        <v/>
+      </c>
+      <c r="E52" s="50" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B49" s="30" t="inlineStr">
+      <c r="B53" s="43" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C49" s="30" t="inlineStr">
+      <c r="C53" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D49" s="34">
-        <f>'HOLERITE SET.26'!C28</f>
-        <v/>
-      </c>
-      <c r="E49" s="39" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="30" t="inlineStr">
+      <c r="D53" s="47">
+        <f>'HOLERITE SET.26'!C30</f>
+        <v/>
+      </c>
+      <c r="E53" s="50" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B50" s="30" t="inlineStr">
+      <c r="B54" s="43" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C50" s="30" t="inlineStr">
+      <c r="C54" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D50" s="34">
-        <f>'HOLERITE SET.26'!C29</f>
-        <v/>
-      </c>
-      <c r="E50" s="39" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="30" t="inlineStr">
+      <c r="D54" s="47">
+        <f>'HOLERITE SET.26'!C31</f>
+        <v/>
+      </c>
+      <c r="E54" s="50" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="43" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B51" s="30" t="inlineStr">
+      <c r="B55" s="43" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C51" s="30" t="inlineStr">
+      <c r="C55" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D51" s="34">
-        <f>'HOLERITE SET.26'!C30</f>
-        <v/>
-      </c>
-      <c r="E51" s="39" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="40" t="inlineStr">
+      <c r="D55" s="47">
+        <f>'HOLERITE SET.26'!C32</f>
+        <v/>
+      </c>
+      <c r="E55" s="50" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="51" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B52" s="40" t="inlineStr">
+      <c r="B56" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C52" s="40" t="inlineStr">
+      <c r="C56" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D52" s="41">
-        <f>'HOLERITE SET.26'!C31</f>
-        <v/>
-      </c>
-      <c r="E52" s="18" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="42" t="inlineStr">
+      <c r="D56" s="52">
+        <f>'HOLERITE SET.26'!C33</f>
+        <v/>
+      </c>
+      <c r="E56" s="18" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="53" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="B53" s="43" t="inlineStr">
+      <c r="B57" s="54" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C53" s="43" t="inlineStr">
+      <c r="C57" s="54" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D53" s="44">
-        <f>'HOLERITE SET.26'!C33</f>
-        <v/>
-      </c>
-      <c r="E53" s="45" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="30" t="inlineStr">
+      <c r="D57" s="55">
+        <f>'HOLERITE SET.26'!C35</f>
+        <v/>
+      </c>
+      <c r="E57" s="56" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B55" s="30" t="inlineStr">
+      <c r="B59" s="43" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C55" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D55" s="34">
+      <c r="C59" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D59" s="47">
         <f>'HOLERITE SET.26'!D6</f>
         <v/>
       </c>
-      <c r="E55" s="39" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="30" t="inlineStr">
+      <c r="E59" s="50" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B56" s="30" t="inlineStr">
+      <c r="B60" s="43" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C56" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D56" s="34">
+      <c r="C60" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D60" s="47">
         <f>'HOLERITE SET.26'!D7</f>
         <v/>
       </c>
-      <c r="E56" s="39" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="30" t="inlineStr">
+      <c r="E60" s="50" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B57" s="30" t="inlineStr">
+      <c r="B61" s="43" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C57" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D57" s="34">
+      <c r="C61" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D61" s="47">
         <f>'HOLERITE SET.26'!D8</f>
         <v/>
       </c>
-      <c r="E57" s="39" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="30" t="inlineStr">
+      <c r="E61" s="50" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B58" s="30" t="inlineStr">
+      <c r="B62" s="43" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C58" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D58" s="34">
+      <c r="C62" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D62" s="47">
         <f>'HOLERITE SET.26'!D11</f>
         <v/>
       </c>
-      <c r="E58" s="39" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="30" t="inlineStr">
+      <c r="E62" s="50" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B59" s="30" t="inlineStr">
+      <c r="B63" s="43" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C59" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D59" s="34">
+      <c r="C63" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D63" s="47">
         <f>'HOLERITE SET.26'!D12</f>
         <v/>
       </c>
-      <c r="E59" s="39" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="30" t="inlineStr">
+      <c r="E63" s="50" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B60" s="30" t="inlineStr">
+      <c r="B64" s="43" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C60" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D60" s="34">
+      <c r="C64" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D64" s="47">
         <f>'HOLERITE SET.26'!D13</f>
         <v/>
       </c>
-      <c r="E60" s="39" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="30" t="inlineStr">
+      <c r="E64" s="50" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B61" s="30" t="inlineStr">
+      <c r="B65" s="43" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C61" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D61" s="34">
+      <c r="C65" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D65" s="47">
         <f>'HOLERITE SET.26'!D14</f>
         <v/>
       </c>
-      <c r="E61" s="39" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="30" t="inlineStr">
+      <c r="E65" s="50" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B62" s="30" t="inlineStr">
-        <is>
-          <t>PRÊMIO COTA GERAL</t>
-        </is>
-      </c>
-      <c r="C62" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D62" s="34">
+      <c r="B66" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 1 — VOLUME</t>
+        </is>
+      </c>
+      <c r="C66" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D66" s="47">
         <f>'HOLERITE SET.26'!D15</f>
         <v/>
       </c>
-      <c r="E62" s="39" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="30" t="inlineStr">
+      <c r="E66" s="50" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B63" s="30" t="inlineStr">
-        <is>
-          <t>PRÊMIO PRÉ-VENCIDOS</t>
-        </is>
-      </c>
-      <c r="C63" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D63" s="34">
+      <c r="B67" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
+        </is>
+      </c>
+      <c r="C67" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D67" s="47">
         <f>'HOLERITE SET.26'!D16</f>
         <v/>
       </c>
-      <c r="E63" s="39" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="30" t="inlineStr">
+      <c r="E67" s="50" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B64" s="30" t="inlineStr">
+      <c r="B68" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
+        </is>
+      </c>
+      <c r="C68" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D68" s="47">
+        <f>'HOLERITE SET.26'!D17</f>
+        <v/>
+      </c>
+      <c r="E68" s="50" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="43" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B69" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
+        </is>
+      </c>
+      <c r="C69" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D69" s="47">
+        <f>'HOLERITE SET.26'!D18</f>
+        <v/>
+      </c>
+      <c r="E69" s="50" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="43" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B70" s="43" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C64" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D64" s="34">
-        <f>'HOLERITE SET.26'!D17</f>
-        <v/>
-      </c>
-      <c r="E64" s="39" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="30" t="inlineStr">
+      <c r="C70" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D70" s="47">
+        <f>'HOLERITE SET.26'!D19</f>
+        <v/>
+      </c>
+      <c r="E70" s="50" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B65" s="30" t="inlineStr">
+      <c r="B71" s="43" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C65" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D65" s="34">
-        <f>'HOLERITE SET.26'!D18</f>
-        <v/>
-      </c>
-      <c r="E65" s="39" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="30" t="inlineStr">
+      <c r="C71" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D71" s="47">
+        <f>'HOLERITE SET.26'!D20</f>
+        <v/>
+      </c>
+      <c r="E71" s="50" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B66" s="30" t="inlineStr">
+      <c r="B72" s="43" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C66" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D66" s="34">
-        <f>'HOLERITE SET.26'!D19</f>
-        <v/>
-      </c>
-      <c r="E66" s="39" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+      <c r="C72" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D72" s="47">
+        <f>'HOLERITE SET.26'!D21</f>
+        <v/>
+      </c>
+      <c r="E72" s="50" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B67" s="30" t="inlineStr">
+      <c r="B73" s="43" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C67" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D67" s="34">
-        <f>'HOLERITE SET.26'!D20</f>
-        <v/>
-      </c>
-      <c r="E67" s="39" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
+      <c r="C73" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D73" s="47">
+        <f>'HOLERITE SET.26'!D22</f>
+        <v/>
+      </c>
+      <c r="E73" s="50" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B68" s="30" t="inlineStr">
+      <c r="B74" s="43" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D68" s="34">
-        <f>'HOLERITE SET.26'!D21</f>
-        <v/>
-      </c>
-      <c r="E68" s="39" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="40" t="inlineStr">
+      <c r="C74" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D74" s="47">
+        <f>'HOLERITE SET.26'!D23</f>
+        <v/>
+      </c>
+      <c r="E74" s="50" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="51" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B69" s="40" t="inlineStr">
+      <c r="B75" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C69" s="40" t="inlineStr">
+      <c r="C75" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D69" s="41">
-        <f>'HOLERITE SET.26'!D22</f>
-        <v/>
-      </c>
-      <c r="E69" s="18" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
+      <c r="D75" s="52">
+        <f>'HOLERITE SET.26'!D24</f>
+        <v/>
+      </c>
+      <c r="E75" s="18" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B70" s="30" t="inlineStr">
+      <c r="B76" s="43" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C70" s="30" t="inlineStr">
+      <c r="C76" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D70" s="34">
-        <f>'HOLERITE SET.26'!D24</f>
-        <v/>
-      </c>
-      <c r="E70" s="39" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="30" t="inlineStr">
+      <c r="D76" s="47">
+        <f>'HOLERITE SET.26'!D26</f>
+        <v/>
+      </c>
+      <c r="E76" s="50" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B71" s="30" t="inlineStr">
+      <c r="B77" s="43" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C71" s="30" t="inlineStr">
+      <c r="C77" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D71" s="34">
-        <f>'HOLERITE SET.26'!D25</f>
-        <v/>
-      </c>
-      <c r="E71" s="39" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="30" t="inlineStr">
+      <c r="D77" s="47">
+        <f>'HOLERITE SET.26'!D27</f>
+        <v/>
+      </c>
+      <c r="E77" s="50" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B72" s="30" t="inlineStr">
+      <c r="B78" s="43" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C72" s="30" t="inlineStr">
+      <c r="C78" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D72" s="34">
-        <f>'HOLERITE SET.26'!D26</f>
-        <v/>
-      </c>
-      <c r="E72" s="39" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="30" t="inlineStr">
+      <c r="D78" s="47">
+        <f>'HOLERITE SET.26'!D28</f>
+        <v/>
+      </c>
+      <c r="E78" s="50" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B73" s="30" t="inlineStr">
+      <c r="B79" s="43" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C73" s="30" t="inlineStr">
+      <c r="C79" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D73" s="34">
-        <f>'HOLERITE SET.26'!D27</f>
-        <v/>
-      </c>
-      <c r="E73" s="39" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
+      <c r="D79" s="47">
+        <f>'HOLERITE SET.26'!D29</f>
+        <v/>
+      </c>
+      <c r="E79" s="50" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B74" s="30" t="inlineStr">
+      <c r="B80" s="43" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C74" s="30" t="inlineStr">
+      <c r="C80" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D74" s="34">
-        <f>'HOLERITE SET.26'!D28</f>
-        <v/>
-      </c>
-      <c r="E74" s="39" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
+      <c r="D80" s="47">
+        <f>'HOLERITE SET.26'!D30</f>
+        <v/>
+      </c>
+      <c r="E80" s="50" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B75" s="30" t="inlineStr">
+      <c r="B81" s="43" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C75" s="30" t="inlineStr">
+      <c r="C81" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D75" s="34">
-        <f>'HOLERITE SET.26'!D29</f>
-        <v/>
-      </c>
-      <c r="E75" s="39" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
+      <c r="D81" s="47">
+        <f>'HOLERITE SET.26'!D31</f>
+        <v/>
+      </c>
+      <c r="E81" s="50" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="43" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B76" s="30" t="inlineStr">
+      <c r="B82" s="43" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C76" s="30" t="inlineStr">
+      <c r="C82" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D76" s="34">
-        <f>'HOLERITE SET.26'!D30</f>
-        <v/>
-      </c>
-      <c r="E76" s="39" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="40" t="inlineStr">
+      <c r="D82" s="47">
+        <f>'HOLERITE SET.26'!D32</f>
+        <v/>
+      </c>
+      <c r="E82" s="50" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="51" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B77" s="40" t="inlineStr">
+      <c r="B83" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C77" s="40" t="inlineStr">
+      <c r="C83" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D77" s="41">
-        <f>'HOLERITE SET.26'!D31</f>
-        <v/>
-      </c>
-      <c r="E77" s="18" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="42" t="inlineStr">
+      <c r="D83" s="52">
+        <f>'HOLERITE SET.26'!D33</f>
+        <v/>
+      </c>
+      <c r="E83" s="18" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="53" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B78" s="43" t="inlineStr">
+      <c r="B84" s="54" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C78" s="43" t="inlineStr">
+      <c r="C84" s="54" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D78" s="44">
-        <f>'HOLERITE SET.26'!D33</f>
-        <v/>
-      </c>
-      <c r="E78" s="45" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="30" t="inlineStr">
+      <c r="D84" s="55">
+        <f>'HOLERITE SET.26'!D35</f>
+        <v/>
+      </c>
+      <c r="E84" s="56" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B80" s="30" t="inlineStr">
+      <c r="B86" s="43" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C80" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D80" s="34">
+      <c r="C86" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D86" s="47">
         <f>'HOLERITE SET.26'!E6</f>
         <v/>
       </c>
-      <c r="E80" s="39" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="30" t="inlineStr">
+      <c r="E86" s="50" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B81" s="30" t="inlineStr">
+      <c r="B87" s="43" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C81" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D81" s="34">
+      <c r="C87" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D87" s="47">
         <f>'HOLERITE SET.26'!E7</f>
         <v/>
       </c>
-      <c r="E81" s="39" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="30" t="inlineStr">
+      <c r="E87" s="50" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B82" s="30" t="inlineStr">
+      <c r="B88" s="43" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C82" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D82" s="34">
+      <c r="C88" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D88" s="47">
         <f>'HOLERITE SET.26'!E8</f>
         <v/>
       </c>
-      <c r="E82" s="39" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="30" t="inlineStr">
+      <c r="E88" s="50" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B83" s="30" t="inlineStr">
+      <c r="B89" s="43" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C83" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D83" s="34">
+      <c r="C89" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D89" s="47">
         <f>'HOLERITE SET.26'!E11</f>
         <v/>
       </c>
-      <c r="E83" s="39" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="30" t="inlineStr">
+      <c r="E89" s="50" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B84" s="30" t="inlineStr">
+      <c r="B90" s="43" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C84" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D84" s="34">
+      <c r="C90" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D90" s="47">
         <f>'HOLERITE SET.26'!E12</f>
         <v/>
       </c>
-      <c r="E84" s="39" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="30" t="inlineStr">
+      <c r="E90" s="50" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B85" s="30" t="inlineStr">
+      <c r="B91" s="43" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C85" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D85" s="34">
+      <c r="C91" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D91" s="47">
         <f>'HOLERITE SET.26'!E13</f>
         <v/>
       </c>
-      <c r="E85" s="39" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="30" t="inlineStr">
+      <c r="E91" s="50" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B86" s="30" t="inlineStr">
+      <c r="B92" s="43" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C86" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D86" s="34">
+      <c r="C92" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D92" s="47">
         <f>'HOLERITE SET.26'!E14</f>
         <v/>
       </c>
-      <c r="E86" s="39" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="30" t="inlineStr">
+      <c r="E92" s="50" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B87" s="30" t="inlineStr">
-        <is>
-          <t>PRÊMIO COTA GERAL</t>
-        </is>
-      </c>
-      <c r="C87" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D87" s="34">
+      <c r="B93" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 1 — VOLUME</t>
+        </is>
+      </c>
+      <c r="C93" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D93" s="47">
         <f>'HOLERITE SET.26'!E15</f>
         <v/>
       </c>
-      <c r="E87" s="39" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="30" t="inlineStr">
+      <c r="E93" s="50" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B88" s="30" t="inlineStr">
-        <is>
-          <t>PRÊMIO PRÉ-VENCIDOS</t>
-        </is>
-      </c>
-      <c r="C88" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D88" s="34">
+      <c r="B94" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
+        </is>
+      </c>
+      <c r="C94" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D94" s="47">
         <f>'HOLERITE SET.26'!E16</f>
         <v/>
       </c>
-      <c r="E88" s="39" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="30" t="inlineStr">
+      <c r="E94" s="50" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B89" s="30" t="inlineStr">
+      <c r="B95" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
+        </is>
+      </c>
+      <c r="C95" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D95" s="47">
+        <f>'HOLERITE SET.26'!E17</f>
+        <v/>
+      </c>
+      <c r="E95" s="50" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="43" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B96" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
+        </is>
+      </c>
+      <c r="C96" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D96" s="47">
+        <f>'HOLERITE SET.26'!E18</f>
+        <v/>
+      </c>
+      <c r="E96" s="50" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="43" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B97" s="43" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C89" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D89" s="34">
-        <f>'HOLERITE SET.26'!E17</f>
-        <v/>
-      </c>
-      <c r="E89" s="39" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="30" t="inlineStr">
+      <c r="C97" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D97" s="47">
+        <f>'HOLERITE SET.26'!E19</f>
+        <v/>
+      </c>
+      <c r="E97" s="50" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B90" s="30" t="inlineStr">
+      <c r="B98" s="43" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C90" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D90" s="34">
-        <f>'HOLERITE SET.26'!E18</f>
-        <v/>
-      </c>
-      <c r="E90" s="39" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="30" t="inlineStr">
+      <c r="C98" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D98" s="47">
+        <f>'HOLERITE SET.26'!E20</f>
+        <v/>
+      </c>
+      <c r="E98" s="50" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B91" s="30" t="inlineStr">
+      <c r="B99" s="43" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C91" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D91" s="34">
-        <f>'HOLERITE SET.26'!E19</f>
-        <v/>
-      </c>
-      <c r="E91" s="39" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="30" t="inlineStr">
+      <c r="C99" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D99" s="47">
+        <f>'HOLERITE SET.26'!E21</f>
+        <v/>
+      </c>
+      <c r="E99" s="50" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B92" s="30" t="inlineStr">
+      <c r="B100" s="43" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C92" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D92" s="34">
-        <f>'HOLERITE SET.26'!E20</f>
-        <v/>
-      </c>
-      <c r="E92" s="39" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="30" t="inlineStr">
+      <c r="C100" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D100" s="47">
+        <f>'HOLERITE SET.26'!E22</f>
+        <v/>
+      </c>
+      <c r="E100" s="50" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B93" s="30" t="inlineStr">
+      <c r="B101" s="43" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C93" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D93" s="34">
-        <f>'HOLERITE SET.26'!E21</f>
-        <v/>
-      </c>
-      <c r="E93" s="39" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="40" t="inlineStr">
+      <c r="C101" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D101" s="47">
+        <f>'HOLERITE SET.26'!E23</f>
+        <v/>
+      </c>
+      <c r="E101" s="50" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="51" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B94" s="40" t="inlineStr">
+      <c r="B102" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C94" s="40" t="inlineStr">
+      <c r="C102" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D94" s="41">
-        <f>'HOLERITE SET.26'!E22</f>
-        <v/>
-      </c>
-      <c r="E94" s="18" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="30" t="inlineStr">
+      <c r="D102" s="52">
+        <f>'HOLERITE SET.26'!E24</f>
+        <v/>
+      </c>
+      <c r="E102" s="18" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B95" s="30" t="inlineStr">
+      <c r="B103" s="43" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C95" s="30" t="inlineStr">
+      <c r="C103" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D95" s="34">
-        <f>'HOLERITE SET.26'!E24</f>
-        <v/>
-      </c>
-      <c r="E95" s="39" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="30" t="inlineStr">
+      <c r="D103" s="47">
+        <f>'HOLERITE SET.26'!E26</f>
+        <v/>
+      </c>
+      <c r="E103" s="50" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B96" s="30" t="inlineStr">
+      <c r="B104" s="43" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C96" s="30" t="inlineStr">
+      <c r="C104" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D96" s="34">
-        <f>'HOLERITE SET.26'!E25</f>
-        <v/>
-      </c>
-      <c r="E96" s="39" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="30" t="inlineStr">
+      <c r="D104" s="47">
+        <f>'HOLERITE SET.26'!E27</f>
+        <v/>
+      </c>
+      <c r="E104" s="50" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B97" s="30" t="inlineStr">
+      <c r="B105" s="43" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C97" s="30" t="inlineStr">
+      <c r="C105" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D97" s="34">
-        <f>'HOLERITE SET.26'!E26</f>
-        <v/>
-      </c>
-      <c r="E97" s="39" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="30" t="inlineStr">
+      <c r="D105" s="47">
+        <f>'HOLERITE SET.26'!E28</f>
+        <v/>
+      </c>
+      <c r="E105" s="50" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B98" s="30" t="inlineStr">
+      <c r="B106" s="43" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C98" s="30" t="inlineStr">
+      <c r="C106" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D98" s="34">
-        <f>'HOLERITE SET.26'!E27</f>
-        <v/>
-      </c>
-      <c r="E98" s="39" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="30" t="inlineStr">
+      <c r="D106" s="47">
+        <f>'HOLERITE SET.26'!E29</f>
+        <v/>
+      </c>
+      <c r="E106" s="50" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B99" s="30" t="inlineStr">
+      <c r="B107" s="43" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C99" s="30" t="inlineStr">
+      <c r="C107" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D99" s="34">
-        <f>'HOLERITE SET.26'!E28</f>
-        <v/>
-      </c>
-      <c r="E99" s="39" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="30" t="inlineStr">
+      <c r="D107" s="47">
+        <f>'HOLERITE SET.26'!E30</f>
+        <v/>
+      </c>
+      <c r="E107" s="50" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B100" s="30" t="inlineStr">
+      <c r="B108" s="43" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C100" s="30" t="inlineStr">
+      <c r="C108" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D100" s="34">
-        <f>'HOLERITE SET.26'!E29</f>
-        <v/>
-      </c>
-      <c r="E100" s="39" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="30" t="inlineStr">
+      <c r="D108" s="47">
+        <f>'HOLERITE SET.26'!E31</f>
+        <v/>
+      </c>
+      <c r="E108" s="50" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="43" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B101" s="30" t="inlineStr">
+      <c r="B109" s="43" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C101" s="30" t="inlineStr">
+      <c r="C109" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D101" s="34">
-        <f>'HOLERITE SET.26'!E30</f>
-        <v/>
-      </c>
-      <c r="E101" s="39" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="40" t="inlineStr">
+      <c r="D109" s="47">
+        <f>'HOLERITE SET.26'!E32</f>
+        <v/>
+      </c>
+      <c r="E109" s="50" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="51" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B102" s="40" t="inlineStr">
+      <c r="B110" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C102" s="40" t="inlineStr">
+      <c r="C110" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D102" s="41">
-        <f>'HOLERITE SET.26'!E31</f>
-        <v/>
-      </c>
-      <c r="E102" s="18" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="42" t="inlineStr">
+      <c r="D110" s="52">
+        <f>'HOLERITE SET.26'!E33</f>
+        <v/>
+      </c>
+      <c r="E110" s="18" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="53" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B103" s="43" t="inlineStr">
+      <c r="B111" s="54" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C103" s="43" t="inlineStr">
+      <c r="C111" s="54" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D103" s="44">
-        <f>'HOLERITE SET.26'!E33</f>
-        <v/>
-      </c>
-      <c r="E103" s="45" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="30" t="inlineStr">
+      <c r="D111" s="55">
+        <f>'HOLERITE SET.26'!E35</f>
+        <v/>
+      </c>
+      <c r="E111" s="56" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B105" s="30" t="inlineStr">
+      <c r="B113" s="43" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C105" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D105" s="34">
+      <c r="C113" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D113" s="47">
         <f>'HOLERITE SET.26'!F6</f>
         <v/>
       </c>
-      <c r="E105" s="39" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="30" t="inlineStr">
+      <c r="E113" s="50" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B106" s="30" t="inlineStr">
+      <c r="B114" s="43" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C106" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D106" s="34">
+      <c r="C114" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D114" s="47">
         <f>'HOLERITE SET.26'!F7</f>
         <v/>
       </c>
-      <c r="E106" s="39" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="30" t="inlineStr">
+      <c r="E114" s="50" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B107" s="30" t="inlineStr">
+      <c r="B115" s="43" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C107" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D107" s="34">
+      <c r="C115" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D115" s="47">
         <f>'HOLERITE SET.26'!F8</f>
         <v/>
       </c>
-      <c r="E107" s="39" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="30" t="inlineStr">
+      <c r="E115" s="50" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B108" s="30" t="inlineStr">
+      <c r="B116" s="43" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C108" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D108" s="34">
+      <c r="C116" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D116" s="47">
         <f>'HOLERITE SET.26'!F11</f>
         <v/>
       </c>
-      <c r="E108" s="39" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="30" t="inlineStr">
+      <c r="E116" s="50" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B109" s="30" t="inlineStr">
+      <c r="B117" s="43" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C109" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D109" s="34">
+      <c r="C117" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D117" s="47">
         <f>'HOLERITE SET.26'!F12</f>
         <v/>
       </c>
-      <c r="E109" s="39" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="30" t="inlineStr">
+      <c r="E117" s="50" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B110" s="30" t="inlineStr">
+      <c r="B118" s="43" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C110" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D110" s="34">
+      <c r="C118" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D118" s="47">
         <f>'HOLERITE SET.26'!F13</f>
         <v/>
       </c>
-      <c r="E110" s="39" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="30" t="inlineStr">
+      <c r="E118" s="50" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B111" s="30" t="inlineStr">
+      <c r="B119" s="43" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C111" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D111" s="34">
+      <c r="C119" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D119" s="47">
         <f>'HOLERITE SET.26'!F14</f>
         <v/>
       </c>
-      <c r="E111" s="39" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="30" t="inlineStr">
+      <c r="E119" s="50" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B112" s="30" t="inlineStr">
-        <is>
-          <t>PRÊMIO COTA GERAL</t>
-        </is>
-      </c>
-      <c r="C112" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D112" s="34">
+      <c r="B120" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 1 — VOLUME</t>
+        </is>
+      </c>
+      <c r="C120" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D120" s="47">
         <f>'HOLERITE SET.26'!F15</f>
         <v/>
       </c>
-      <c r="E112" s="39" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="30" t="inlineStr">
+      <c r="E120" s="50" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B113" s="30" t="inlineStr">
-        <is>
-          <t>PRÊMIO PRÉ-VENCIDOS</t>
-        </is>
-      </c>
-      <c r="C113" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D113" s="34">
+      <c r="B121" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
+        </is>
+      </c>
+      <c r="C121" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D121" s="47">
         <f>'HOLERITE SET.26'!F16</f>
         <v/>
       </c>
-      <c r="E113" s="39" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="30" t="inlineStr">
+      <c r="E121" s="50" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B114" s="30" t="inlineStr">
+      <c r="B122" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
+        </is>
+      </c>
+      <c r="C122" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D122" s="47">
+        <f>'HOLERITE SET.26'!F17</f>
+        <v/>
+      </c>
+      <c r="E122" s="50" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="43" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B123" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
+        </is>
+      </c>
+      <c r="C123" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D123" s="47">
+        <f>'HOLERITE SET.26'!F18</f>
+        <v/>
+      </c>
+      <c r="E123" s="50" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="43" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B124" s="43" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C114" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D114" s="34">
-        <f>'HOLERITE SET.26'!F17</f>
-        <v/>
-      </c>
-      <c r="E114" s="39" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="30" t="inlineStr">
+      <c r="C124" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D124" s="47">
+        <f>'HOLERITE SET.26'!F19</f>
+        <v/>
+      </c>
+      <c r="E124" s="50" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B115" s="30" t="inlineStr">
+      <c r="B125" s="43" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C115" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D115" s="34">
-        <f>'HOLERITE SET.26'!F18</f>
-        <v/>
-      </c>
-      <c r="E115" s="39" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="30" t="inlineStr">
+      <c r="C125" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D125" s="47">
+        <f>'HOLERITE SET.26'!F20</f>
+        <v/>
+      </c>
+      <c r="E125" s="50" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B116" s="30" t="inlineStr">
+      <c r="B126" s="43" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C116" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D116" s="34">
-        <f>'HOLERITE SET.26'!F19</f>
-        <v/>
-      </c>
-      <c r="E116" s="39" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="30" t="inlineStr">
+      <c r="C126" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D126" s="47">
+        <f>'HOLERITE SET.26'!F21</f>
+        <v/>
+      </c>
+      <c r="E126" s="50" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B117" s="30" t="inlineStr">
+      <c r="B127" s="43" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C117" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D117" s="34">
-        <f>'HOLERITE SET.26'!F20</f>
-        <v/>
-      </c>
-      <c r="E117" s="39" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="30" t="inlineStr">
+      <c r="C127" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D127" s="47">
+        <f>'HOLERITE SET.26'!F22</f>
+        <v/>
+      </c>
+      <c r="E127" s="50" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B118" s="30" t="inlineStr">
+      <c r="B128" s="43" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C118" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D118" s="34">
-        <f>'HOLERITE SET.26'!F21</f>
-        <v/>
-      </c>
-      <c r="E118" s="39" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="40" t="inlineStr">
+      <c r="C128" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D128" s="47">
+        <f>'HOLERITE SET.26'!F23</f>
+        <v/>
+      </c>
+      <c r="E128" s="50" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="51" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B119" s="40" t="inlineStr">
+      <c r="B129" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C119" s="40" t="inlineStr">
+      <c r="C129" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D119" s="41">
-        <f>'HOLERITE SET.26'!F22</f>
-        <v/>
-      </c>
-      <c r="E119" s="18" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="30" t="inlineStr">
+      <c r="D129" s="52">
+        <f>'HOLERITE SET.26'!F24</f>
+        <v/>
+      </c>
+      <c r="E129" s="18" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B120" s="30" t="inlineStr">
+      <c r="B130" s="43" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C120" s="30" t="inlineStr">
+      <c r="C130" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D120" s="34">
-        <f>'HOLERITE SET.26'!F24</f>
-        <v/>
-      </c>
-      <c r="E120" s="39" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="30" t="inlineStr">
+      <c r="D130" s="47">
+        <f>'HOLERITE SET.26'!F26</f>
+        <v/>
+      </c>
+      <c r="E130" s="50" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B121" s="30" t="inlineStr">
+      <c r="B131" s="43" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C121" s="30" t="inlineStr">
+      <c r="C131" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D121" s="34">
-        <f>'HOLERITE SET.26'!F25</f>
-        <v/>
-      </c>
-      <c r="E121" s="39" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="30" t="inlineStr">
+      <c r="D131" s="47">
+        <f>'HOLERITE SET.26'!F27</f>
+        <v/>
+      </c>
+      <c r="E131" s="50" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B122" s="30" t="inlineStr">
+      <c r="B132" s="43" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C122" s="30" t="inlineStr">
+      <c r="C132" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D122" s="34">
-        <f>'HOLERITE SET.26'!F26</f>
-        <v/>
-      </c>
-      <c r="E122" s="39" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="30" t="inlineStr">
+      <c r="D132" s="47">
+        <f>'HOLERITE SET.26'!F28</f>
+        <v/>
+      </c>
+      <c r="E132" s="50" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B123" s="30" t="inlineStr">
+      <c r="B133" s="43" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C123" s="30" t="inlineStr">
+      <c r="C133" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D123" s="34">
-        <f>'HOLERITE SET.26'!F27</f>
-        <v/>
-      </c>
-      <c r="E123" s="39" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="30" t="inlineStr">
+      <c r="D133" s="47">
+        <f>'HOLERITE SET.26'!F29</f>
+        <v/>
+      </c>
+      <c r="E133" s="50" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B124" s="30" t="inlineStr">
+      <c r="B134" s="43" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C124" s="30" t="inlineStr">
+      <c r="C134" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D124" s="34">
-        <f>'HOLERITE SET.26'!F28</f>
-        <v/>
-      </c>
-      <c r="E124" s="39" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="30" t="inlineStr">
+      <c r="D134" s="47">
+        <f>'HOLERITE SET.26'!F30</f>
+        <v/>
+      </c>
+      <c r="E134" s="50" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B125" s="30" t="inlineStr">
+      <c r="B135" s="43" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C125" s="30" t="inlineStr">
+      <c r="C135" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D125" s="34">
-        <f>'HOLERITE SET.26'!F29</f>
-        <v/>
-      </c>
-      <c r="E125" s="39" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="30" t="inlineStr">
+      <c r="D135" s="47">
+        <f>'HOLERITE SET.26'!F31</f>
+        <v/>
+      </c>
+      <c r="E135" s="50" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="43" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B126" s="30" t="inlineStr">
+      <c r="B136" s="43" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C126" s="30" t="inlineStr">
+      <c r="C136" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D126" s="34">
-        <f>'HOLERITE SET.26'!F30</f>
-        <v/>
-      </c>
-      <c r="E126" s="39" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="40" t="inlineStr">
+      <c r="D136" s="47">
+        <f>'HOLERITE SET.26'!F32</f>
+        <v/>
+      </c>
+      <c r="E136" s="50" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="51" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B127" s="40" t="inlineStr">
+      <c r="B137" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C127" s="40" t="inlineStr">
+      <c r="C137" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D127" s="41">
-        <f>'HOLERITE SET.26'!F31</f>
-        <v/>
-      </c>
-      <c r="E127" s="18" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="42" t="inlineStr">
+      <c r="D137" s="52">
+        <f>'HOLERITE SET.26'!F33</f>
+        <v/>
+      </c>
+      <c r="E137" s="18" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="53" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="B128" s="43" t="inlineStr">
+      <c r="B138" s="54" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C128" s="43" t="inlineStr">
+      <c r="C138" s="54" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D128" s="44">
-        <f>'HOLERITE SET.26'!F33</f>
-        <v/>
-      </c>
-      <c r="E128" s="45" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="30" t="inlineStr">
+      <c r="D138" s="55">
+        <f>'HOLERITE SET.26'!F35</f>
+        <v/>
+      </c>
+      <c r="E138" s="56" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B130" s="30" t="inlineStr">
+      <c r="B140" s="43" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C130" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D130" s="34">
+      <c r="C140" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D140" s="47">
         <f>'HOLERITE SET.26'!G6</f>
         <v/>
       </c>
-      <c r="E130" s="39" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="30" t="inlineStr">
+      <c r="E140" s="50" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B131" s="30" t="inlineStr">
+      <c r="B141" s="43" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C131" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D131" s="34">
+      <c r="C141" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D141" s="47">
         <f>'HOLERITE SET.26'!G7</f>
         <v/>
       </c>
-      <c r="E131" s="39" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="30" t="inlineStr">
+      <c r="E141" s="50" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B132" s="30" t="inlineStr">
+      <c r="B142" s="43" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C132" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D132" s="34">
+      <c r="C142" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D142" s="47">
         <f>'HOLERITE SET.26'!G8</f>
         <v/>
       </c>
-      <c r="E132" s="39" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="30" t="inlineStr">
+      <c r="E142" s="50" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B133" s="30" t="inlineStr">
+      <c r="B143" s="43" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C133" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D133" s="34">
+      <c r="C143" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D143" s="47">
         <f>'HOLERITE SET.26'!G11</f>
         <v/>
       </c>
-      <c r="E133" s="39" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="30" t="inlineStr">
+      <c r="E143" s="50" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B134" s="30" t="inlineStr">
+      <c r="B144" s="43" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C134" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D134" s="34">
+      <c r="C144" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D144" s="47">
         <f>'HOLERITE SET.26'!G12</f>
         <v/>
       </c>
-      <c r="E134" s="39" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="30" t="inlineStr">
+      <c r="E144" s="50" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B135" s="30" t="inlineStr">
+      <c r="B145" s="43" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C135" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D135" s="34">
+      <c r="C145" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D145" s="47">
         <f>'HOLERITE SET.26'!G13</f>
         <v/>
       </c>
-      <c r="E135" s="39" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="30" t="inlineStr">
+      <c r="E145" s="50" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B136" s="30" t="inlineStr">
+      <c r="B146" s="43" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C136" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D136" s="34">
+      <c r="C146" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D146" s="47">
         <f>'HOLERITE SET.26'!G14</f>
         <v/>
       </c>
-      <c r="E136" s="39" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="30" t="inlineStr">
+      <c r="E146" s="50" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B137" s="30" t="inlineStr">
-        <is>
-          <t>PRÊMIO COTA GERAL</t>
-        </is>
-      </c>
-      <c r="C137" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D137" s="34">
+      <c r="B147" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 1 — VOLUME</t>
+        </is>
+      </c>
+      <c r="C147" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D147" s="47">
         <f>'HOLERITE SET.26'!G15</f>
         <v/>
       </c>
-      <c r="E137" s="39" t="n"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="30" t="inlineStr">
+      <c r="E147" s="50" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B138" s="30" t="inlineStr">
-        <is>
-          <t>PRÊMIO PRÉ-VENCIDOS</t>
-        </is>
-      </c>
-      <c r="C138" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D138" s="34">
+      <c r="B148" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
+        </is>
+      </c>
+      <c r="C148" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D148" s="47">
         <f>'HOLERITE SET.26'!G16</f>
         <v/>
       </c>
-      <c r="E138" s="39" t="n"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="30" t="inlineStr">
+      <c r="E148" s="50" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B139" s="30" t="inlineStr">
+      <c r="B149" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
+        </is>
+      </c>
+      <c r="C149" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D149" s="47">
+        <f>'HOLERITE SET.26'!G17</f>
+        <v/>
+      </c>
+      <c r="E149" s="50" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="43" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B150" s="43" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
+        </is>
+      </c>
+      <c r="C150" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D150" s="47">
+        <f>'HOLERITE SET.26'!G18</f>
+        <v/>
+      </c>
+      <c r="E150" s="50" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="43" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B151" s="43" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C139" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D139" s="34">
-        <f>'HOLERITE SET.26'!G17</f>
-        <v/>
-      </c>
-      <c r="E139" s="39" t="n"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="30" t="inlineStr">
+      <c r="C151" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D151" s="47">
+        <f>'HOLERITE SET.26'!G19</f>
+        <v/>
+      </c>
+      <c r="E151" s="50" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B140" s="30" t="inlineStr">
+      <c r="B152" s="43" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C140" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D140" s="34">
-        <f>'HOLERITE SET.26'!G18</f>
-        <v/>
-      </c>
-      <c r="E140" s="39" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="30" t="inlineStr">
+      <c r="C152" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D152" s="47">
+        <f>'HOLERITE SET.26'!G20</f>
+        <v/>
+      </c>
+      <c r="E152" s="50" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B141" s="30" t="inlineStr">
+      <c r="B153" s="43" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C141" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D141" s="34">
-        <f>'HOLERITE SET.26'!G19</f>
-        <v/>
-      </c>
-      <c r="E141" s="39" t="n"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="30" t="inlineStr">
+      <c r="C153" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D153" s="47">
+        <f>'HOLERITE SET.26'!G21</f>
+        <v/>
+      </c>
+      <c r="E153" s="50" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B142" s="30" t="inlineStr">
+      <c r="B154" s="43" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C142" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D142" s="34">
-        <f>'HOLERITE SET.26'!G20</f>
-        <v/>
-      </c>
-      <c r="E142" s="39" t="n"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="30" t="inlineStr">
+      <c r="C154" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D154" s="47">
+        <f>'HOLERITE SET.26'!G22</f>
+        <v/>
+      </c>
+      <c r="E154" s="50" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B143" s="30" t="inlineStr">
+      <c r="B155" s="43" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C143" s="30" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D143" s="34">
-        <f>'HOLERITE SET.26'!G21</f>
-        <v/>
-      </c>
-      <c r="E143" s="39" t="n"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="40" t="inlineStr">
+      <c r="C155" s="43" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D155" s="47">
+        <f>'HOLERITE SET.26'!G23</f>
+        <v/>
+      </c>
+      <c r="E155" s="50" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="51" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B144" s="40" t="inlineStr">
+      <c r="B156" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C144" s="40" t="inlineStr">
+      <c r="C156" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D144" s="41">
-        <f>'HOLERITE SET.26'!G22</f>
-        <v/>
-      </c>
-      <c r="E144" s="18" t="n"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="30" t="inlineStr">
+      <c r="D156" s="52">
+        <f>'HOLERITE SET.26'!G24</f>
+        <v/>
+      </c>
+      <c r="E156" s="18" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B145" s="30" t="inlineStr">
+      <c r="B157" s="43" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C145" s="30" t="inlineStr">
+      <c r="C157" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D145" s="34">
-        <f>'HOLERITE SET.26'!G24</f>
-        <v/>
-      </c>
-      <c r="E145" s="39" t="n"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="30" t="inlineStr">
+      <c r="D157" s="47">
+        <f>'HOLERITE SET.26'!G26</f>
+        <v/>
+      </c>
+      <c r="E157" s="50" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B146" s="30" t="inlineStr">
+      <c r="B158" s="43" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C146" s="30" t="inlineStr">
+      <c r="C158" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D146" s="34">
-        <f>'HOLERITE SET.26'!G25</f>
-        <v/>
-      </c>
-      <c r="E146" s="39" t="n"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="30" t="inlineStr">
+      <c r="D158" s="47">
+        <f>'HOLERITE SET.26'!G27</f>
+        <v/>
+      </c>
+      <c r="E158" s="50" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B147" s="30" t="inlineStr">
+      <c r="B159" s="43" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C147" s="30" t="inlineStr">
+      <c r="C159" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D147" s="34">
-        <f>'HOLERITE SET.26'!G26</f>
-        <v/>
-      </c>
-      <c r="E147" s="39" t="n"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="30" t="inlineStr">
+      <c r="D159" s="47">
+        <f>'HOLERITE SET.26'!G28</f>
+        <v/>
+      </c>
+      <c r="E159" s="50" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B148" s="30" t="inlineStr">
+      <c r="B160" s="43" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C148" s="30" t="inlineStr">
+      <c r="C160" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D148" s="34">
-        <f>'HOLERITE SET.26'!G27</f>
-        <v/>
-      </c>
-      <c r="E148" s="39" t="n"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="30" t="inlineStr">
+      <c r="D160" s="47">
+        <f>'HOLERITE SET.26'!G29</f>
+        <v/>
+      </c>
+      <c r="E160" s="50" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B149" s="30" t="inlineStr">
+      <c r="B161" s="43" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C149" s="30" t="inlineStr">
+      <c r="C161" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D149" s="34">
-        <f>'HOLERITE SET.26'!G28</f>
-        <v/>
-      </c>
-      <c r="E149" s="39" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="30" t="inlineStr">
+      <c r="D161" s="47">
+        <f>'HOLERITE SET.26'!G30</f>
+        <v/>
+      </c>
+      <c r="E161" s="50" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B150" s="30" t="inlineStr">
+      <c r="B162" s="43" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C150" s="30" t="inlineStr">
+      <c r="C162" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D150" s="34">
-        <f>'HOLERITE SET.26'!G29</f>
-        <v/>
-      </c>
-      <c r="E150" s="39" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="30" t="inlineStr">
+      <c r="D162" s="47">
+        <f>'HOLERITE SET.26'!G31</f>
+        <v/>
+      </c>
+      <c r="E162" s="50" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="43" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B151" s="30" t="inlineStr">
+      <c r="B163" s="43" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C151" s="30" t="inlineStr">
+      <c r="C163" s="43" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D151" s="34">
-        <f>'HOLERITE SET.26'!G30</f>
-        <v/>
-      </c>
-      <c r="E151" s="39" t="n"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="40" t="inlineStr">
+      <c r="D163" s="47">
+        <f>'HOLERITE SET.26'!G32</f>
+        <v/>
+      </c>
+      <c r="E163" s="50" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="51" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B152" s="40" t="inlineStr">
+      <c r="B164" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C152" s="40" t="inlineStr">
+      <c r="C164" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D152" s="41">
-        <f>'HOLERITE SET.26'!G31</f>
-        <v/>
-      </c>
-      <c r="E152" s="18" t="n"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="42" t="inlineStr">
+      <c r="D164" s="52">
+        <f>'HOLERITE SET.26'!G33</f>
+        <v/>
+      </c>
+      <c r="E164" s="18" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="53" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="B153" s="43" t="inlineStr">
+      <c r="B165" s="54" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C153" s="43" t="inlineStr">
+      <c r="C165" s="54" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D153" s="44">
-        <f>'HOLERITE SET.26'!G33</f>
-        <v/>
-      </c>
-      <c r="E153" s="45" t="n"/>
+      <c r="D165" s="55">
+        <f>'HOLERITE SET.26'!G35</f>
+        <v/>
+      </c>
+      <c r="E165" s="56" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E153"/>
+  <autoFilter ref="A4:E165"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -6178,13 +7302,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6208,12 +7332,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="46" t="inlineStr">
+      <c r="B4" s="57" t="inlineStr">
         <is>
           <t>Escolha o colaborador:</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
+      <c r="C4" s="58" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
@@ -6230,369 +7354,391 @@
           <t>PROVENTOS</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n"/>
-      <c r="D6" s="29" t="n"/>
+      <c r="C6" s="42" t="n"/>
+      <c r="D6" s="42" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>Salário base</t>
         </is>
       </c>
-      <c r="C7" s="34">
+      <c r="C7" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="43" t="inlineStr">
         <is>
           <t>Adicional noturno</t>
         </is>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$7:$G$7,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="43" t="inlineStr">
         <is>
           <t>Horas extras</t>
         </is>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$8:$G$8,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="43" t="inlineStr">
         <is>
           <t>Comissão sobre vendas</t>
         </is>
       </c>
-      <c r="C10" s="34">
+      <c r="C10" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$11:$G$11,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="43" t="inlineStr">
         <is>
           <t>Repouso remunerado / DSR</t>
         </is>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$12:$G$12,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="30" t="inlineStr">
+      <c r="B12" s="43" t="inlineStr">
         <is>
           <t>Auxílio gerência</t>
         </is>
       </c>
-      <c r="C12" s="34">
+      <c r="C12" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$13:$G$13,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="43" t="inlineStr">
         <is>
           <t>Adicional prêmio meta caixa</t>
         </is>
       </c>
-      <c r="C13" s="34">
+      <c r="C13" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$14:$G$14,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="30" t="inlineStr">
-        <is>
-          <t>Prêmio cota geral</t>
-        </is>
-      </c>
-      <c r="C14" s="34">
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>Prêmio meta 1 — volume</t>
+        </is>
+      </c>
+      <c r="C14" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$15:$G$15,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="30" t="inlineStr">
-        <is>
-          <t>Prêmio pré-vencidos</t>
-        </is>
-      </c>
-      <c r="C15" s="34">
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>Prêmio meta 2 — produtos foco</t>
+        </is>
+      </c>
+      <c r="C15" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$16:$G$16,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>Prêmio meta 3 — pré-vencidos</t>
+        </is>
+      </c>
+      <c r="C16" s="47">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$17:$G$17,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="43" t="inlineStr">
+        <is>
+          <t>Prêmio meta 4 — perfumaria</t>
+        </is>
+      </c>
+      <c r="C17" s="47">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$18:$G$18,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="43" t="inlineStr">
         <is>
           <t>Férias</t>
         </is>
       </c>
-      <c r="C16" s="34">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$17:$G$17,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="30" t="inlineStr">
+      <c r="C18" s="47">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$19:$G$19,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="43" t="inlineStr">
         <is>
           <t>1/3 constitucional de férias</t>
         </is>
       </c>
-      <c r="C17" s="34">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$18:$G$18,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="30" t="inlineStr">
+      <c r="C19" s="47">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$20:$G$20,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="43" t="inlineStr">
         <is>
           <t>Incentivo aplicações</t>
         </is>
       </c>
-      <c r="C18" s="34">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$19:$G$19,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="30" t="inlineStr">
+      <c r="C20" s="47">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$21:$G$21,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="43" t="inlineStr">
         <is>
           <t>Incentivo vitaminas</t>
         </is>
       </c>
-      <c r="C19" s="34">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$20:$G$20,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="30" t="inlineStr">
+      <c r="C21" s="47">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$22:$G$22,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="43" t="inlineStr">
         <is>
           <t>Outros incentivos</t>
         </is>
       </c>
-      <c r="C20" s="34">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$21:$G$21,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="19" t="inlineStr">
+      <c r="C22" s="47">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$23:$G$23,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C21" s="41">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$22:$G$22,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="B22" s="3" t="inlineStr">
+      <c r="C23" s="52">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$24:$G$24,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="19" customHeight="1">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>DESCONTOS</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n"/>
-      <c r="D22" s="29" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="30" t="inlineStr">
+      <c r="C24" s="42" t="n"/>
+      <c r="D24" s="42" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="43" t="inlineStr">
         <is>
           <t>Adiantamento salarial / vales</t>
         </is>
       </c>
-      <c r="C23" s="34">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$24:$G$24,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="30" t="inlineStr">
+      <c r="C25" s="47">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$26:$G$26,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="43" t="inlineStr">
         <is>
           <t>Adiantamento de incentivos e aplicações</t>
         </is>
       </c>
-      <c r="C24" s="34">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$25:$G$25,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="30" t="inlineStr">
+      <c r="C26" s="47">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$27:$G$27,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="43" t="inlineStr">
         <is>
           <t>Convênio</t>
         </is>
       </c>
-      <c r="C25" s="34">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$26:$G$26,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="30" t="inlineStr">
+      <c r="C27" s="47">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$28:$G$28,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="43" t="inlineStr">
         <is>
           <t>Faltas / atrasos</t>
         </is>
       </c>
-      <c r="C26" s="34">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$27:$G$27,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="30" t="inlineStr">
+      <c r="C28" s="47">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$29:$G$29,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="43" t="inlineStr">
         <is>
           <t>Vale transporte 6%</t>
         </is>
       </c>
-      <c r="C27" s="34">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$28:$G$28,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="30" t="inlineStr">
+      <c r="C29" s="47">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$30:$G$30,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="43" t="inlineStr">
         <is>
           <t>INSS</t>
         </is>
       </c>
-      <c r="C28" s="34">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$29:$G$29,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="30" t="inlineStr">
+      <c r="C30" s="47">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$31:$G$31,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="43" t="inlineStr">
         <is>
           <t>IRRF</t>
         </is>
       </c>
-      <c r="C29" s="34">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$30:$G$30,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="19" t="inlineStr">
+      <c r="C31" s="47">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$32:$G$32,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C30" s="41">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$31:$G$31,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="B31" s="3" t="inlineStr">
+      <c r="C32" s="52">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$33:$G$33,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>LÍQUIDO</t>
         </is>
       </c>
-      <c r="C31" s="29" t="n"/>
-      <c r="D31" s="29" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="B32" s="48" t="inlineStr">
+      <c r="C33" s="42" t="n"/>
+      <c r="D33" s="42" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="B34" s="59" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER EM 05/10/2026</t>
         </is>
       </c>
-      <c r="C32" s="49">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$33:$G$33,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="50" t="inlineStr">
+      <c r="C34" s="60">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$35:$G$35,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="27" t="inlineStr">
         <is>
           <t>Vendas do colaborador no mês (InovaFarma):</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="30" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="43" t="inlineStr">
         <is>
           <t>Venda bruta</t>
         </is>
       </c>
-      <c r="C35" s="34">
+      <c r="C37" s="47">
         <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$C$5:$C$10,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="30" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="43" t="inlineStr">
         <is>
           <t>Descontos concedidos</t>
         </is>
       </c>
-      <c r="C36" s="34">
+      <c r="C38" s="47">
         <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$D$5:$D$10,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="30" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="43" t="inlineStr">
         <is>
           <t>Venda líquida</t>
         </is>
       </c>
-      <c r="C37" s="34">
+      <c r="C39" s="47">
         <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$E$5:$E$10,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="30" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="43" t="inlineStr">
         <is>
           <t>Comissão apurada</t>
         </is>
       </c>
-      <c r="C38" s="34">
+      <c r="C40" s="47">
         <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$F$5:$F$10,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="30" t="inlineStr">
+    <row r="41">
+      <c r="B41" s="43" t="inlineStr">
         <is>
           <t>Total de incentivos</t>
         </is>
       </c>
-      <c r="C39" s="34">
+      <c r="C41" s="47">
         <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$J$5:$J$10,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
         <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="22" t="inlineStr">
-        <is>
-          <t>A comissão apurada acima é a do sistema. O que entra na folha é a linha "Comissão sobre vendas".</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="22" t="inlineStr">
-        <is>
-          <t>Os valores de INSS e IRRF são calculados pela contabilidade e só aparecem depois de preenchidos na aba HOLERITE SET.26.</t>
-        </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>A comissão apurada acima é a do sistema. O que entra na folha é a linha "Comissão sobre vendas".</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>Os valores de INSS e IRRF são calculados pela contabilidade e só aparecem depois de preenchidos na aba HOLERITE SET.26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="22" t="inlineStr">
         <is>
           <t>Para mandar para o colaborador: selecione o nome acima e imprima esta aba em PDF (ou tire um print).</t>
         </is>
@@ -6613,7 +7759,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6700,7 +7846,7 @@
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="43" t="inlineStr">
         <is>
           <t>Registro informativo</t>
         </is>
@@ -6713,23 +7859,23 @@
           <t>dias</t>
         </is>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A5,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F5" s="36" t="n">
+      <c r="F5" s="48" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="20">
         <f>ROUND(C5*F5,2)</f>
         <v/>
       </c>
-      <c r="H5" s="51" t="inlineStr">
+      <c r="H5" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="33" t="inlineStr">
+      <c r="I5" s="46" t="inlineStr">
         <is>
           <t>Voltou das férias (01 a 30/08/2026) — salário integral em setembro.</t>
         </is>
@@ -6741,7 +7887,7 @@
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="43" t="inlineStr">
         <is>
           <t>Feriado trabalhado (dobra)</t>
         </is>
@@ -6754,11 +7900,11 @@
           <t>dias</t>
         </is>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A6,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="48">
         <f>ROUND(E6/PARÂMETROS!$B$19,2)</f>
         <v/>
       </c>
@@ -6766,12 +7912,12 @@
         <f>ROUND(C6*F6,2)</f>
         <v/>
       </c>
-      <c r="H6" s="51" t="inlineStr">
+      <c r="H6" s="61" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="I6" s="33" t="inlineStr">
+      <c r="I6" s="46" t="inlineStr">
         <is>
           <t>Feriados de 07/09 e 08/09/2026 trabalhados, sem folga compensatória — 1 salário-dia a mais por feriado.</t>
         </is>
@@ -6783,7 +7929,7 @@
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
+      <c r="B7" s="43" t="inlineStr">
         <is>
           <t>Registro informativo</t>
         </is>
@@ -6796,163 +7942,163 @@
           <t>dias</t>
         </is>
       </c>
-      <c r="E7" s="34">
+      <c r="E7" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A7,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F7" s="36" t="n">
+      <c r="F7" s="48" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="20">
         <f>ROUND(C7*F7,2)</f>
         <v/>
       </c>
-      <c r="H7" s="51" t="inlineStr">
+      <c r="H7" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I7" s="33" t="inlineStr">
+      <c r="I7" s="46" t="inlineStr">
         <is>
           <t>Férias de 01 a 30/09/2026 — mês inteiro. Salário zerado no holerite; férias e 1/3 vão em recibo próprio.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="52" t="n"/>
-      <c r="B8" s="52" t="n"/>
-      <c r="C8" s="52" t="n"/>
-      <c r="D8" s="52" t="n"/>
-      <c r="E8" s="34">
+      <c r="A8" s="30" t="n"/>
+      <c r="B8" s="30" t="n"/>
+      <c r="C8" s="30" t="n"/>
+      <c r="D8" s="30" t="n"/>
+      <c r="E8" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A8,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F8" s="35" t="n"/>
+      <c r="F8" s="29" t="n"/>
       <c r="G8" s="20">
         <f>ROUND(C8*F8,2)</f>
         <v/>
       </c>
-      <c r="H8" s="52" t="n"/>
-      <c r="I8" s="52" t="n"/>
+      <c r="H8" s="30" t="n"/>
+      <c r="I8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="52" t="n"/>
-      <c r="B9" s="52" t="n"/>
-      <c r="C9" s="52" t="n"/>
-      <c r="D9" s="52" t="n"/>
-      <c r="E9" s="34">
+      <c r="A9" s="30" t="n"/>
+      <c r="B9" s="30" t="n"/>
+      <c r="C9" s="30" t="n"/>
+      <c r="D9" s="30" t="n"/>
+      <c r="E9" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A9,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F9" s="35" t="n"/>
+      <c r="F9" s="29" t="n"/>
       <c r="G9" s="20">
         <f>ROUND(C9*F9,2)</f>
         <v/>
       </c>
-      <c r="H9" s="52" t="n"/>
-      <c r="I9" s="52" t="n"/>
+      <c r="H9" s="30" t="n"/>
+      <c r="I9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="52" t="n"/>
-      <c r="B10" s="52" t="n"/>
-      <c r="C10" s="52" t="n"/>
-      <c r="D10" s="52" t="n"/>
-      <c r="E10" s="34">
+      <c r="A10" s="30" t="n"/>
+      <c r="B10" s="30" t="n"/>
+      <c r="C10" s="30" t="n"/>
+      <c r="D10" s="30" t="n"/>
+      <c r="E10" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A10,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F10" s="35" t="n"/>
+      <c r="F10" s="29" t="n"/>
       <c r="G10" s="20">
         <f>ROUND(C10*F10,2)</f>
         <v/>
       </c>
-      <c r="H10" s="52" t="n"/>
-      <c r="I10" s="52" t="n"/>
+      <c r="H10" s="30" t="n"/>
+      <c r="I10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="52" t="n"/>
-      <c r="B11" s="52" t="n"/>
-      <c r="C11" s="52" t="n"/>
-      <c r="D11" s="52" t="n"/>
-      <c r="E11" s="34">
+      <c r="A11" s="30" t="n"/>
+      <c r="B11" s="30" t="n"/>
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="30" t="n"/>
+      <c r="E11" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A11,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F11" s="35" t="n"/>
+      <c r="F11" s="29" t="n"/>
       <c r="G11" s="20">
         <f>ROUND(C11*F11,2)</f>
         <v/>
       </c>
-      <c r="H11" s="52" t="n"/>
-      <c r="I11" s="52" t="n"/>
+      <c r="H11" s="30" t="n"/>
+      <c r="I11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="52" t="n"/>
-      <c r="B12" s="52" t="n"/>
-      <c r="C12" s="52" t="n"/>
-      <c r="D12" s="52" t="n"/>
-      <c r="E12" s="34">
+      <c r="A12" s="30" t="n"/>
+      <c r="B12" s="30" t="n"/>
+      <c r="C12" s="30" t="n"/>
+      <c r="D12" s="30" t="n"/>
+      <c r="E12" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A12,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F12" s="35" t="n"/>
+      <c r="F12" s="29" t="n"/>
       <c r="G12" s="20">
         <f>ROUND(C12*F12,2)</f>
         <v/>
       </c>
-      <c r="H12" s="52" t="n"/>
-      <c r="I12" s="52" t="n"/>
+      <c r="H12" s="30" t="n"/>
+      <c r="I12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="52" t="n"/>
-      <c r="B13" s="52" t="n"/>
-      <c r="C13" s="52" t="n"/>
-      <c r="D13" s="52" t="n"/>
-      <c r="E13" s="34">
+      <c r="A13" s="30" t="n"/>
+      <c r="B13" s="30" t="n"/>
+      <c r="C13" s="30" t="n"/>
+      <c r="D13" s="30" t="n"/>
+      <c r="E13" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A13,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F13" s="35" t="n"/>
+      <c r="F13" s="29" t="n"/>
       <c r="G13" s="20">
         <f>ROUND(C13*F13,2)</f>
         <v/>
       </c>
-      <c r="H13" s="52" t="n"/>
-      <c r="I13" s="52" t="n"/>
+      <c r="H13" s="30" t="n"/>
+      <c r="I13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="52" t="n"/>
-      <c r="B14" s="52" t="n"/>
-      <c r="C14" s="52" t="n"/>
-      <c r="D14" s="52" t="n"/>
-      <c r="E14" s="34">
+      <c r="A14" s="30" t="n"/>
+      <c r="B14" s="30" t="n"/>
+      <c r="C14" s="30" t="n"/>
+      <c r="D14" s="30" t="n"/>
+      <c r="E14" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A14,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F14" s="35" t="n"/>
+      <c r="F14" s="29" t="n"/>
       <c r="G14" s="20">
         <f>ROUND(C14*F14,2)</f>
         <v/>
       </c>
-      <c r="H14" s="52" t="n"/>
-      <c r="I14" s="52" t="n"/>
+      <c r="H14" s="30" t="n"/>
+      <c r="I14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="52" t="n"/>
-      <c r="B15" s="52" t="n"/>
-      <c r="C15" s="52" t="n"/>
-      <c r="D15" s="52" t="n"/>
-      <c r="E15" s="34">
+      <c r="A15" s="30" t="n"/>
+      <c r="B15" s="30" t="n"/>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="30" t="n"/>
+      <c r="E15" s="47">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A15,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F15" s="35" t="n"/>
+      <c r="F15" s="29" t="n"/>
       <c r="G15" s="20">
         <f>ROUND(C15*F15,2)</f>
         <v/>
       </c>
-      <c r="H15" s="52" t="n"/>
-      <c r="I15" s="52" t="n"/>
+      <c r="H15" s="30" t="n"/>
+      <c r="I15" s="30" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="18" t="n"/>
@@ -7014,7 +8160,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7100,21 +8246,21 @@
           <t>51</t>
         </is>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="29" t="n">
         <v>150</v>
       </c>
       <c r="D5" s="8" t="n"/>
-      <c r="E5" s="53">
+      <c r="E5" s="28">
         <f>C5*D5</f>
         <v/>
       </c>
-      <c r="F5" s="35" t="n">
+      <c r="F5" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="35" t="n">
+      <c r="G5" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="38">
+      <c r="H5" s="36">
         <f>E5+F5+G5</f>
         <v/>
       </c>
@@ -7130,21 +8276,21 @@
           <t>131</t>
         </is>
       </c>
-      <c r="C6" s="35" t="n">
+      <c r="C6" s="29" t="n">
         <v>100</v>
       </c>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="53">
+      <c r="E6" s="28">
         <f>C6*D6</f>
         <v/>
       </c>
-      <c r="F6" s="35" t="n">
+      <c r="F6" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="35" t="n">
+      <c r="G6" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="38">
+      <c r="H6" s="36">
         <f>E6+F6+G6</f>
         <v/>
       </c>

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_CENTRO_pgto_05-10-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_SETEMBRO_2026_CENTRO_pgto_05-10-2026.xlsx
@@ -20,9 +20,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BASE INOVAFARMA SET.26'!$A$4:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'METAS SET.26'!$A$11:$T$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'HOLERITE SET.26'!$A$4:$I$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$165</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'GANHOS DO COLABORADOR'!$A$1:$D$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'HOLERITE SET.26'!$A$4:$I$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$159</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'GANHOS DO COLABORADOR'!$A$1:$D$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'PONTO SET.26'!$A$4:$I$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'FOLGUISTAS'!$A$4:$H$6</definedName>
   </definedNames>
@@ -105,6 +105,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00008000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00000000"/>
       <sz val="8"/>
@@ -118,11 +123,6 @@
     <font>
       <name val="Arial"/>
       <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -240,10 +240,10 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -299,8 +299,9 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -309,25 +310,24 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="15" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="15" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="L11" s="32" t="inlineStr">
         <is>
-          <t>META 2 PROD. FOCO</t>
+          <t>META 2 (INCENTIVO INOVAFARMA)</t>
         </is>
       </c>
       <c r="M11" s="32" t="inlineStr">
@@ -2148,7 +2148,10 @@
         <f>IF(G12&gt;=1.2,J12,IF(G12&gt;=1,I12,IF(G12&gt;=0.8,H12,0)))</f>
         <v/>
       </c>
-      <c r="L12" s="29" t="n"/>
+      <c r="L12" s="36">
+        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$J$5:$J$10,MATCH(A12,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
+        <v/>
+      </c>
       <c r="M12" s="29" t="n"/>
       <c r="N12" s="28" t="n"/>
       <c r="O12" s="35">
@@ -2165,11 +2168,11 @@
         <f>IF(AND(P12="SIM",$C$9="SIM"),IF(Q12="",0,Q12)+50,0)</f>
         <v/>
       </c>
-      <c r="S12" s="36">
+      <c r="S12" s="37">
         <f>ROUND(K12+IF(L12="",0,L12)+O12+R12,2)</f>
         <v/>
       </c>
-      <c r="T12" s="37" t="inlineStr"/>
+      <c r="T12" s="38" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
@@ -2210,7 +2213,10 @@
         <f>IF(G13&gt;=1.2,J13,IF(G13&gt;=1,I13,IF(G13&gt;=0.8,H13,0)))</f>
         <v/>
       </c>
-      <c r="L13" s="29" t="n"/>
+      <c r="L13" s="36">
+        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$J$5:$J$10,MATCH(A13,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
+        <v/>
+      </c>
       <c r="M13" s="29" t="n"/>
       <c r="N13" s="28" t="n"/>
       <c r="O13" s="35">
@@ -2227,11 +2233,11 @@
         <f>IF(AND(P13="SIM",$C$9="SIM"),IF(Q13="",0,Q13)+50,0)</f>
         <v/>
       </c>
-      <c r="S13" s="36">
+      <c r="S13" s="37">
         <f>ROUND(K13+IF(L13="",0,L13)+O13+R13,2)</f>
         <v/>
       </c>
-      <c r="T13" s="37" t="inlineStr">
+      <c r="T13" s="38" t="inlineStr">
         <is>
           <t>Férias de 01 a 30/09: sem dias trabalhados, fica fora da apuração.</t>
         </is>
@@ -2276,7 +2282,10 @@
         <f>IF(G14&gt;=1.2,J14,IF(G14&gt;=1,I14,IF(G14&gt;=0.8,H14,0)))</f>
         <v/>
       </c>
-      <c r="L14" s="29" t="n"/>
+      <c r="L14" s="36">
+        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$J$5:$J$10,MATCH(A14,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
+        <v/>
+      </c>
       <c r="M14" s="29" t="n"/>
       <c r="N14" s="28" t="n">
         <v>1040</v>
@@ -2295,11 +2304,11 @@
         <f>IF(AND(P14="SIM",$C$9="SIM"),IF(Q14="",0,Q14)+50,0)</f>
         <v/>
       </c>
-      <c r="S14" s="36">
+      <c r="S14" s="37">
         <f>ROUND(K14+IF(L14="",0,L14)+O14+R14,2)</f>
         <v/>
       </c>
-      <c r="T14" s="37" t="inlineStr">
+      <c r="T14" s="38" t="inlineStr">
         <is>
           <t>Farmacêutica: na Meta 3 vale a regra própria (equipe + 30%).</t>
         </is>
@@ -2344,7 +2353,10 @@
         <f>IF(G15&gt;=1.2,J15,IF(G15&gt;=1,I15,IF(G15&gt;=0.8,H15,0)))</f>
         <v/>
       </c>
-      <c r="L15" s="29" t="n"/>
+      <c r="L15" s="36">
+        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$J$5:$J$10,MATCH(A15,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
+        <v/>
+      </c>
       <c r="M15" s="29" t="n"/>
       <c r="N15" s="28" t="n"/>
       <c r="O15" s="35">
@@ -2361,11 +2373,11 @@
         <f>IF(AND(P15="SIM",$C$9="SIM"),IF(Q15="",0,Q15)+50,0)</f>
         <v/>
       </c>
-      <c r="S15" s="36">
+      <c r="S15" s="37">
         <f>ROUND(K15+IF(L15="",0,L15)+O15+R15,2)</f>
         <v/>
       </c>
-      <c r="T15" s="37" t="inlineStr"/>
+      <c r="T15" s="38" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
@@ -2406,7 +2418,10 @@
         <f>IF(G16&gt;=1.2,J16,IF(G16&gt;=1,I16,IF(G16&gt;=0.8,H16,0)))</f>
         <v/>
       </c>
-      <c r="L16" s="29" t="n"/>
+      <c r="L16" s="36">
+        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$J$5:$J$10,MATCH(A16,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
+        <v/>
+      </c>
       <c r="M16" s="29" t="n"/>
       <c r="N16" s="28" t="n"/>
       <c r="O16" s="35">
@@ -2423,11 +2438,11 @@
         <f>IF(AND(P16="SIM",$C$9="SIM"),IF(Q16="",0,Q16)+50,0)</f>
         <v/>
       </c>
-      <c r="S16" s="36">
+      <c r="S16" s="37">
         <f>ROUND(K16+IF(L16="",0,L16)+O16+R16,2)</f>
         <v/>
       </c>
-      <c r="T16" s="37" t="inlineStr"/>
+      <c r="T16" s="38" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
@@ -2466,7 +2481,10 @@
         <f>IF(G17&gt;=1.2,J17,IF(G17&gt;=1,I17,IF(G17&gt;=0.8,H17,0)))</f>
         <v/>
       </c>
-      <c r="L17" s="29" t="n"/>
+      <c r="L17" s="36">
+        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$J$5:$J$10,MATCH(A17,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
+        <v/>
+      </c>
       <c r="M17" s="29" t="n"/>
       <c r="N17" s="28" t="n"/>
       <c r="O17" s="35">
@@ -2483,11 +2501,11 @@
         <f>IF(AND(P17="SIM",$C$9="SIM"),IF(Q17="",0,Q17)+50,0)</f>
         <v/>
       </c>
-      <c r="S17" s="36">
+      <c r="S17" s="37">
         <f>ROUND(K17+IF(L17="",0,L17)+O17+R17,2)</f>
         <v/>
       </c>
-      <c r="T17" s="37" t="inlineStr">
+      <c r="T17" s="38" t="inlineStr">
         <is>
           <t>Folguista: meta proporcional aos dias trabalhados — preencher os dias. Prêmio vai para o contas a pagar, fora do holerite.</t>
         </is>
@@ -2535,49 +2553,49 @@
       <c r="T18" s="18" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="38" t="inlineStr">
+      <c r="A20" s="39" t="inlineStr">
         <is>
           <t>COMO PREENCHER (células amarelas):</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="39" t="inlineStr">
+      <c r="A21" s="40" t="inlineStr">
         <is>
           <t>VENDA REALIZADA: total vendido no mês pelo código do vendedor (InovaFarma, venda líquida). DIAS TRAB.: dias efetivamente trabalhados — a meta cai na mesma proporção.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="39" t="inlineStr">
+      <c r="A22" s="40" t="inlineStr">
         <is>
           <t>META 1 — VOLUME: meta = média dos 3 últimos meses + 8%. 80% da meta paga o prêmio de 80%, 100% paga o de 100% e 120% paga o de 120%, conforme a faixa (A 150/250/500 · B 100/150/300 · C e D 50/80/150).</t>
         </is>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="39" t="inlineStr">
-        <is>
-          <t>META 2 — PRODUTOS FOCO: lançar o valor apurado na semana (vitaminas da campanha, packs, injetáveis, coquetel, brinco, kit ressaca). ATENÇÃO: se o incentivo já vier no relatório do InovaFarma (linhas INCENTIVO do holerite), não lançar de novo aqui.</t>
+      <c r="A23" s="40" t="inlineStr">
+        <is>
+          <t>META 2 — PRODUTOS FOCO: é paga pelo campo de incentivo do InovaFarma (R$ 10 por item cadastrado no estoque). A coluna puxa o total de incentivos da aba BASE só para mostrar o ganho completo — no holerite ela entra pelas linhas INCENTIVO, e não numa linha de prêmio, para não pagar duas vezes.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="39" t="inlineStr">
+      <c r="A24" s="40" t="inlineStr">
         <is>
           <t>META 3 — PRÉ-VENCIDOS: escada mensal por vendedor (acima de R$ 1.000 = 100 · R$ 2.000 = 200 · R$ 3.000 = 300). Farmacêuticos têm regra própria: bateu a meta da coluna META PRÉ-V. FARMAC., recebe R$ 150.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="39" t="inlineStr">
+      <c r="A25" s="40" t="inlineStr">
         <is>
           <t>META 4 — PERFUMARIA 130%: meta da LOJA (bloco no topo). Se a loja bater 130% da média ou zerar o estoque, cada vendedora marcada recebe a comissão de perfumaria do mês mais R$ 50 fixos.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="39" t="inlineStr">
+      <c r="A26" s="40" t="inlineStr">
         <is>
           <t>Os prêmios entram sozinhos nas linhas PRÊMIO META 1 a 4 do holerite. Fonte: planilha Metas_Equipe_Set2026_v2.xlsx.</t>
         </is>
@@ -2611,7 +2629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2640,47 +2658,47 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>RUBRICA</t>
         </is>
       </c>
-      <c r="B4" s="41" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="C4" s="41" t="inlineStr">
+      <c r="C4" s="42" t="inlineStr">
         <is>
           <t>ELIANA</t>
         </is>
       </c>
-      <c r="D4" s="41" t="inlineStr">
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="E4" s="41" t="inlineStr">
+      <c r="E4" s="42" t="inlineStr">
         <is>
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="F4" s="41" t="inlineStr">
+      <c r="F4" s="42" t="inlineStr">
         <is>
           <t>THAYANE</t>
         </is>
       </c>
-      <c r="G4" s="41" t="inlineStr">
+      <c r="G4" s="42" t="inlineStr">
         <is>
           <t>PEDRO</t>
         </is>
       </c>
-      <c r="H4" s="41" t="inlineStr">
+      <c r="H4" s="42" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="I4" s="40" t="inlineStr">
+      <c r="I4" s="41" t="inlineStr">
         <is>
           <t>ORIGEM / OBSERVAÇÃO</t>
         </is>
@@ -2692,76 +2710,76 @@
           <t>PROVENTOS</t>
         </is>
       </c>
-      <c r="B5" s="42" t="n"/>
-      <c r="C5" s="42" t="n"/>
-      <c r="D5" s="42" t="n"/>
-      <c r="E5" s="42" t="n"/>
-      <c r="F5" s="42" t="n"/>
-      <c r="G5" s="42" t="n"/>
-      <c r="H5" s="42" t="n"/>
-      <c r="I5" s="42" t="n"/>
+      <c r="B5" s="43" t="n"/>
+      <c r="C5" s="43" t="n"/>
+      <c r="D5" s="43" t="n"/>
+      <c r="E5" s="43" t="n"/>
+      <c r="F5" s="43" t="n"/>
+      <c r="G5" s="43" t="n"/>
+      <c r="H5" s="43" t="n"/>
+      <c r="I5" s="43" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="44" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="B6" s="44" t="n">
+      <c r="B6" s="45" t="n">
         <v>5648.41</v>
       </c>
-      <c r="C6" s="44" t="n">
+      <c r="C6" s="45" t="n">
         <v>1621</v>
       </c>
-      <c r="D6" s="44" t="n">
+      <c r="D6" s="45" t="n">
         <v>1621</v>
       </c>
-      <c r="E6" s="44" t="n">
+      <c r="E6" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="44" t="n">
+      <c r="F6" s="45" t="n">
         <v>1621</v>
       </c>
-      <c r="G6" s="44" t="n">
+      <c r="G6" s="45" t="n">
         <v>1621</v>
       </c>
-      <c r="H6" s="45">
+      <c r="H6" s="46">
         <f>SUM(B6:G6)</f>
         <v/>
       </c>
-      <c r="I6" s="46" t="inlineStr">
+      <c r="I6" s="47" t="inlineStr">
         <is>
           <t>Piso 2026 R$ 1.621,00; gerente conforme ago/2026. CONFERIR admissões, afastamentos e férias do mês.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="B7" s="47">
+      <c r="B7" s="36">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,B$4,'PONTO SET.26'!$H$5:$H$15,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="36">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,C$4,'PONTO SET.26'!$H$5:$H$15,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
-      <c r="D7" s="47">
+      <c r="D7" s="36">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,D$4,'PONTO SET.26'!$H$5:$H$15,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="36">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,E$4,'PONTO SET.26'!$H$5:$H$15,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
-      <c r="F7" s="47">
+      <c r="F7" s="36">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,F$4,'PONTO SET.26'!$H$5:$H$15,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
-      <c r="G7" s="47">
+      <c r="G7" s="36">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,G$4,'PONTO SET.26'!$H$5:$H$15,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
@@ -2769,39 +2787,39 @@
         <f>SUM(B7:G7)</f>
         <v/>
       </c>
-      <c r="I7" s="46" t="inlineStr">
+      <c r="I7" s="47" t="inlineStr">
         <is>
           <t>Somado automaticamente da aba PONTO SET.26 (apontamento de setembro/2026). Para mudar, edite lá.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="44" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="B8" s="47">
+      <c r="B8" s="36">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,B$4,'PONTO SET.26'!$H$5:$H$15,"HORAS EXTRAS")</f>
         <v/>
       </c>
-      <c r="C8" s="47">
+      <c r="C8" s="36">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,C$4,'PONTO SET.26'!$H$5:$H$15,"HORAS EXTRAS")</f>
         <v/>
       </c>
-      <c r="D8" s="47">
+      <c r="D8" s="36">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,D$4,'PONTO SET.26'!$H$5:$H$15,"HORAS EXTRAS")</f>
         <v/>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="36">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,E$4,'PONTO SET.26'!$H$5:$H$15,"HORAS EXTRAS")</f>
         <v/>
       </c>
-      <c r="F8" s="47">
+      <c r="F8" s="36">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,F$4,'PONTO SET.26'!$H$5:$H$15,"HORAS EXTRAS")</f>
         <v/>
       </c>
-      <c r="G8" s="47">
+      <c r="G8" s="36">
         <f>SUMIFS('PONTO SET.26'!$G$5:$G$15,'PONTO SET.26'!$A$5:$A$15,G$4,'PONTO SET.26'!$H$5:$H$15,"HORAS EXTRAS")</f>
         <v/>
       </c>
@@ -2809,52 +2827,52 @@
         <f>SUM(B8:G8)</f>
         <v/>
       </c>
-      <c r="I8" s="46" t="inlineStr">
+      <c r="I8" s="47" t="inlineStr">
         <is>
           <t>Somado automaticamente da aba PONTO SET.26 (apontamento de setembro/2026). Para mudar, edite lá.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="A9" s="44" t="inlineStr">
         <is>
           <t>COMISSÃO PRODUTOS (INOVAFARMA)</t>
         </is>
       </c>
-      <c r="B9" s="47" t="n">
+      <c r="B9" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="47">
+      <c r="C9" s="36">
         <f>ROUND('BASE INOVAFARMA SET.26'!F6*PARÂMETROS!$B$20,2)</f>
         <v/>
       </c>
-      <c r="D9" s="47">
+      <c r="D9" s="36">
         <f>ROUND('BASE INOVAFARMA SET.26'!F7*PARÂMETROS!$B$20,2)</f>
         <v/>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="36">
         <f>ROUND('BASE INOVAFARMA SET.26'!F8*PARÂMETROS!$B$20,2)</f>
         <v/>
       </c>
-      <c r="F9" s="47">
+      <c r="F9" s="36">
         <f>ROUND('BASE INOVAFARMA SET.26'!F9*PARÂMETROS!$B$20,2)</f>
         <v/>
       </c>
-      <c r="G9" s="47" t="n">
+      <c r="G9" s="36" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="20">
         <f>SUM(B9:G9)</f>
         <v/>
       </c>
-      <c r="I9" s="46" t="inlineStr">
+      <c r="I9" s="47" t="inlineStr">
         <is>
           <t>Apurado no InovaFarma (aba BASE INOVAFARMA SET.26). ARIANE e PEDRO não recebe(m) comissão — lançado zero.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="44" t="inlineStr">
         <is>
           <t>COMPLEMENTO / COMISSÃO PDV</t>
         </is>
@@ -2869,7 +2887,7 @@
         <f>SUM(B10:G10)</f>
         <v/>
       </c>
-      <c r="I10" s="46" t="inlineStr">
+      <c r="I10" s="47" t="inlineStr">
         <is>
           <t>PREENCHER: PDV antigos e complementos de comissão acordados, se houver.</t>
         </is>
@@ -2909,14 +2927,14 @@
         <f>SUM(B11:G11)</f>
         <v/>
       </c>
-      <c r="I11" s="46" t="inlineStr">
+      <c r="I11" s="47" t="inlineStr">
         <is>
           <t>Base do DSR junto com as horas extras.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="44" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
@@ -2949,14 +2967,14 @@
         <f>SUM(B12:G12)</f>
         <v/>
       </c>
-      <c r="I12" s="46" t="inlineStr">
+      <c r="I12" s="47" t="inlineStr">
         <is>
           <t>Cálculo: (comissão total + horas extras) × (4 domingos + feriados de 07/09 e 08/09) ÷ 24 dias úteis de setembro/2026.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="A13" s="44" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
@@ -2971,14 +2989,14 @@
         <f>SUM(B13:G13)</f>
         <v/>
       </c>
-      <c r="I13" s="46" t="inlineStr">
+      <c r="I13" s="47" t="inlineStr">
         <is>
           <t>Conforme acordo da loja.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="44" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
@@ -2993,39 +3011,39 @@
         <f>SUM(B14:G14)</f>
         <v/>
       </c>
-      <c r="I14" s="46" t="inlineStr">
+      <c r="I14" s="47" t="inlineStr">
         <is>
           <t>Conforme apuração do caixa.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="43" t="inlineStr">
+      <c r="A15" s="44" t="inlineStr">
         <is>
           <t>PRÊMIO META 1 — VOLUME</t>
         </is>
       </c>
-      <c r="B15" s="47">
+      <c r="B15" s="36">
         <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$17,MATCH(B$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
         <v/>
       </c>
-      <c r="C15" s="47">
+      <c r="C15" s="36">
         <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$17,MATCH(C$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
         <v/>
       </c>
-      <c r="D15" s="47">
+      <c r="D15" s="36">
         <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$17,MATCH(D$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
         <v/>
       </c>
-      <c r="E15" s="47">
+      <c r="E15" s="36">
         <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$17,MATCH(E$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
         <v/>
       </c>
-      <c r="F15" s="47">
+      <c r="F15" s="36">
         <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$17,MATCH(F$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
         <v/>
       </c>
-      <c r="G15" s="47">
+      <c r="G15" s="36">
         <f>IFERROR(INDEX('METAS SET.26'!$K$12:$K$17,MATCH(G$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
         <v/>
       </c>
@@ -3033,136 +3051,118 @@
         <f>SUM(B15:G15)</f>
         <v/>
       </c>
-      <c r="I15" s="46" t="inlineStr">
+      <c r="I15" s="47" t="inlineStr">
         <is>
           <t>Da aba METAS SET.26: venda do mês contra a meta individual (80% / 100% / 120%).</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="43" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
-        </is>
-      </c>
-      <c r="B16" s="47">
-        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$17,MATCH(B$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="C16" s="47">
-        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$17,MATCH(C$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="D16" s="47">
-        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$17,MATCH(D$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="E16" s="47">
-        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$17,MATCH(E$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F16" s="47">
-        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$17,MATCH(F$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="G16" s="47">
-        <f>IFERROR(INDEX('METAS SET.26'!$L$12:$L$17,MATCH(G$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
+        </is>
+      </c>
+      <c r="B16" s="36">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$17,MATCH(B$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="C16" s="36">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$17,MATCH(C$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="D16" s="36">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$17,MATCH(D$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="E16" s="36">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$17,MATCH(E$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F16" s="36">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$17,MATCH(F$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="36">
+        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$17,MATCH(G$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
         <v/>
       </c>
       <c r="H16" s="20">
         <f>SUM(B16:G16)</f>
         <v/>
       </c>
-      <c r="I16" s="46" t="inlineStr">
-        <is>
-          <t>Da aba METAS SET.26: vitaminas, packs, injetáveis, coquetel, brinco e kit ressaca.</t>
+      <c r="I16" s="47" t="inlineStr">
+        <is>
+          <t>Da aba METAS SET.26: escada de pré-vencidos (farmacêuticos com regra própria).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="43" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
-        </is>
-      </c>
-      <c r="B17" s="47">
-        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$17,MATCH(B$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="C17" s="47">
-        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$17,MATCH(C$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="D17" s="47">
-        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$17,MATCH(D$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="E17" s="47">
-        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$17,MATCH(E$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F17" s="47">
-        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$17,MATCH(F$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="G17" s="47">
-        <f>IFERROR(INDEX('METAS SET.26'!$O$12:$O$17,MATCH(G$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+      <c r="A17" s="44" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
+        </is>
+      </c>
+      <c r="B17" s="36">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$17,MATCH(B$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="C17" s="36">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$17,MATCH(C$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="D17" s="36">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$17,MATCH(D$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="E17" s="36">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$17,MATCH(E$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F17" s="36">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$17,MATCH(F$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
+        <v/>
+      </c>
+      <c r="G17" s="36">
+        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$17,MATCH(G$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
         <v/>
       </c>
       <c r="H17" s="20">
         <f>SUM(B17:G17)</f>
         <v/>
       </c>
-      <c r="I17" s="46" t="inlineStr">
-        <is>
-          <t>Da aba METAS SET.26: escada de pré-vencidos (farmacêuticos com regra própria).</t>
+      <c r="I17" s="47" t="inlineStr">
+        <is>
+          <t>Da aba METAS SET.26: se a loja bateu, comissão de perfumaria em dobro + R$ 50 fixos.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="43" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
-        </is>
-      </c>
-      <c r="B18" s="47">
-        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$17,MATCH(B$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="C18" s="47">
-        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$17,MATCH(C$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="D18" s="47">
-        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$17,MATCH(D$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="E18" s="47">
-        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$17,MATCH(E$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="F18" s="47">
-        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$17,MATCH(F$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="G18" s="47">
-        <f>IFERROR(INDEX('METAS SET.26'!$R$12:$R$17,MATCH(G$4,'METAS SET.26'!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>FÉRIAS (DIAS GOZADOS)</t>
+        </is>
+      </c>
+      <c r="B18" s="29" t="n"/>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="29" t="n"/>
+      <c r="G18" s="29" t="n"/>
       <c r="H18" s="20">
         <f>SUM(B18:G18)</f>
         <v/>
       </c>
-      <c r="I18" s="46" t="inlineStr">
-        <is>
-          <t>Da aba METAS SET.26: se a loja bateu, comissão de perfumaria em dobro + R$ 50 fixos.</t>
+      <c r="I18" s="47" t="inlineStr">
+        <is>
+          <t>PREENCHER se houve férias no mês; informar o período.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="43" t="inlineStr">
-        <is>
-          <t>FÉRIAS (DIAS GOZADOS)</t>
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
       <c r="B19" s="29" t="n"/>
@@ -3175,277 +3175,277 @@
         <f>SUM(B19:G19)</f>
         <v/>
       </c>
-      <c r="I19" s="46" t="inlineStr">
-        <is>
-          <t>PREENCHER se houve férias no mês; informar o período.</t>
+      <c r="I19" s="47" t="inlineStr">
+        <is>
+          <t>Calculado pela contabilidade sobre o valor das férias.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="43" t="inlineStr">
-        <is>
-          <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
-        </is>
-      </c>
-      <c r="B20" s="29" t="n"/>
-      <c r="C20" s="29" t="n"/>
-      <c r="D20" s="29" t="n"/>
-      <c r="E20" s="29" t="n"/>
-      <c r="F20" s="29" t="n"/>
-      <c r="G20" s="29" t="n"/>
+      <c r="A20" s="44" t="inlineStr">
+        <is>
+          <t>INCENTIVO APLICAÇÕES</t>
+        </is>
+      </c>
+      <c r="B20" s="36">
+        <f>'BASE INOVAFARMA SET.26'!G5</f>
+        <v/>
+      </c>
+      <c r="C20" s="36">
+        <f>'BASE INOVAFARMA SET.26'!G6</f>
+        <v/>
+      </c>
+      <c r="D20" s="36">
+        <f>'BASE INOVAFARMA SET.26'!G7</f>
+        <v/>
+      </c>
+      <c r="E20" s="36">
+        <f>'BASE INOVAFARMA SET.26'!G8</f>
+        <v/>
+      </c>
+      <c r="F20" s="36">
+        <f>'BASE INOVAFARMA SET.26'!G9</f>
+        <v/>
+      </c>
+      <c r="G20" s="36">
+        <f>'BASE INOVAFARMA SET.26'!G10</f>
+        <v/>
+      </c>
       <c r="H20" s="20">
         <f>SUM(B20:G20)</f>
         <v/>
       </c>
-      <c r="I20" s="46" t="inlineStr">
-        <is>
-          <t>Calculado pela contabilidade sobre o valor das férias.</t>
+      <c r="I20" s="47" t="inlineStr">
+        <is>
+          <t>Incentivo de injetáveis apurado no InovaFarma. As linhas de incentivo incluem a META 2 (produtos foco) do programa de metas.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="43" t="inlineStr">
-        <is>
-          <t>INCENTIVO APLICAÇÕES</t>
-        </is>
-      </c>
-      <c r="B21" s="47">
-        <f>'BASE INOVAFARMA SET.26'!G5</f>
-        <v/>
-      </c>
-      <c r="C21" s="47">
-        <f>'BASE INOVAFARMA SET.26'!G6</f>
-        <v/>
-      </c>
-      <c r="D21" s="47">
-        <f>'BASE INOVAFARMA SET.26'!G7</f>
-        <v/>
-      </c>
-      <c r="E21" s="47">
-        <f>'BASE INOVAFARMA SET.26'!G8</f>
-        <v/>
-      </c>
-      <c r="F21" s="47">
-        <f>'BASE INOVAFARMA SET.26'!G9</f>
-        <v/>
-      </c>
-      <c r="G21" s="47">
-        <f>'BASE INOVAFARMA SET.26'!G10</f>
+      <c r="A21" s="44" t="inlineStr">
+        <is>
+          <t>INCENTIVO VITAMINAS</t>
+        </is>
+      </c>
+      <c r="B21" s="36">
+        <f>'BASE INOVAFARMA SET.26'!H5</f>
+        <v/>
+      </c>
+      <c r="C21" s="36">
+        <f>'BASE INOVAFARMA SET.26'!H6</f>
+        <v/>
+      </c>
+      <c r="D21" s="36">
+        <f>'BASE INOVAFARMA SET.26'!H7</f>
+        <v/>
+      </c>
+      <c r="E21" s="36">
+        <f>'BASE INOVAFARMA SET.26'!H8</f>
+        <v/>
+      </c>
+      <c r="F21" s="36">
+        <f>'BASE INOVAFARMA SET.26'!H9</f>
+        <v/>
+      </c>
+      <c r="G21" s="36">
+        <f>'BASE INOVAFARMA SET.26'!H10</f>
         <v/>
       </c>
       <c r="H21" s="20">
         <f>SUM(B21:G21)</f>
         <v/>
       </c>
-      <c r="I21" s="46" t="inlineStr">
-        <is>
-          <t>Incentivo de injetáveis apurado no InovaFarma.</t>
+      <c r="I21" s="47" t="inlineStr">
+        <is>
+          <t>Grupo APLICAÇÃO E VITAMINAS INCENTIVO no InovaFarma.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="43" t="inlineStr">
-        <is>
-          <t>INCENTIVO VITAMINAS</t>
-        </is>
-      </c>
-      <c r="B22" s="47">
-        <f>'BASE INOVAFARMA SET.26'!H5</f>
-        <v/>
-      </c>
-      <c r="C22" s="47">
-        <f>'BASE INOVAFARMA SET.26'!H6</f>
-        <v/>
-      </c>
-      <c r="D22" s="47">
-        <f>'BASE INOVAFARMA SET.26'!H7</f>
-        <v/>
-      </c>
-      <c r="E22" s="47">
-        <f>'BASE INOVAFARMA SET.26'!H8</f>
-        <v/>
-      </c>
-      <c r="F22" s="47">
-        <f>'BASE INOVAFARMA SET.26'!H9</f>
-        <v/>
-      </c>
-      <c r="G22" s="47">
-        <f>'BASE INOVAFARMA SET.26'!H10</f>
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>OUTROS INCENTIVOS</t>
+        </is>
+      </c>
+      <c r="B22" s="36">
+        <f>'BASE INOVAFARMA SET.26'!I5</f>
+        <v/>
+      </c>
+      <c r="C22" s="36">
+        <f>'BASE INOVAFARMA SET.26'!I6</f>
+        <v/>
+      </c>
+      <c r="D22" s="36">
+        <f>'BASE INOVAFARMA SET.26'!I7</f>
+        <v/>
+      </c>
+      <c r="E22" s="36">
+        <f>'BASE INOVAFARMA SET.26'!I8</f>
+        <v/>
+      </c>
+      <c r="F22" s="36">
+        <f>'BASE INOVAFARMA SET.26'!I9</f>
+        <v/>
+      </c>
+      <c r="G22" s="36">
+        <f>'BASE INOVAFARMA SET.26'!I10</f>
         <v/>
       </c>
       <c r="H22" s="20">
         <f>SUM(B22:G22)</f>
         <v/>
       </c>
-      <c r="I22" s="46" t="inlineStr">
-        <is>
-          <t>Grupo APLICAÇÃO E VITAMINAS INCENTIVO no InovaFarma.</t>
+      <c r="I22" s="47" t="inlineStr">
+        <is>
+          <t>Populares, oficinais e similar normal.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="43" t="inlineStr">
-        <is>
-          <t>OUTROS INCENTIVOS</t>
-        </is>
-      </c>
-      <c r="B23" s="47">
-        <f>'BASE INOVAFARMA SET.26'!I5</f>
-        <v/>
-      </c>
-      <c r="C23" s="47">
-        <f>'BASE INOVAFARMA SET.26'!I6</f>
-        <v/>
-      </c>
-      <c r="D23" s="47">
-        <f>'BASE INOVAFARMA SET.26'!I7</f>
-        <v/>
-      </c>
-      <c r="E23" s="47">
-        <f>'BASE INOVAFARMA SET.26'!I8</f>
-        <v/>
-      </c>
-      <c r="F23" s="47">
-        <f>'BASE INOVAFARMA SET.26'!I9</f>
-        <v/>
-      </c>
-      <c r="G23" s="47">
-        <f>'BASE INOVAFARMA SET.26'!I10</f>
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL DE PROVENTOS</t>
+        </is>
+      </c>
+      <c r="B23" s="20">
+        <f>SUM(B6:B22)-B9-B10</f>
+        <v/>
+      </c>
+      <c r="C23" s="20">
+        <f>SUM(C6:C22)-C9-C10</f>
+        <v/>
+      </c>
+      <c r="D23" s="20">
+        <f>SUM(D6:D22)-D9-D10</f>
+        <v/>
+      </c>
+      <c r="E23" s="20">
+        <f>SUM(E6:E22)-E9-E10</f>
+        <v/>
+      </c>
+      <c r="F23" s="20">
+        <f>SUM(F6:F22)-F9-F10</f>
+        <v/>
+      </c>
+      <c r="G23" s="20">
+        <f>SUM(G6:G22)-G9-G10</f>
         <v/>
       </c>
       <c r="H23" s="20">
         <f>SUM(B23:G23)</f>
         <v/>
       </c>
-      <c r="I23" s="46" t="inlineStr">
-        <is>
-          <t>Populares, oficinais e similar normal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL DE PROVENTOS</t>
-        </is>
-      </c>
-      <c r="B24" s="20">
-        <f>SUM(B6:B23)-B9-B10</f>
-        <v/>
-      </c>
-      <c r="C24" s="20">
-        <f>SUM(C6:C23)-C9-C10</f>
-        <v/>
-      </c>
-      <c r="D24" s="20">
-        <f>SUM(D6:D23)-D9-D10</f>
-        <v/>
-      </c>
-      <c r="E24" s="20">
-        <f>SUM(E6:E23)-E9-E10</f>
-        <v/>
-      </c>
-      <c r="F24" s="20">
-        <f>SUM(F6:F23)-F9-F10</f>
-        <v/>
-      </c>
-      <c r="G24" s="20">
-        <f>SUM(G6:G23)-G9-G10</f>
-        <v/>
-      </c>
-      <c r="H24" s="20">
-        <f>SUM(B24:G24)</f>
-        <v/>
-      </c>
-      <c r="I24" s="46" t="inlineStr">
+      <c r="I23" s="47" t="inlineStr">
         <is>
           <t>Soma das rubricas acima (a linha COMISSÃO TOTAL já engloba a comissão do InovaFarma e o complemento).</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>DESCONTOS  (lançar com sinal negativo)</t>
         </is>
       </c>
-      <c r="B25" s="42" t="n"/>
-      <c r="C25" s="42" t="n"/>
-      <c r="D25" s="42" t="n"/>
-      <c r="E25" s="42" t="n"/>
-      <c r="F25" s="42" t="n"/>
-      <c r="G25" s="42" t="n"/>
-      <c r="H25" s="42" t="n"/>
-      <c r="I25" s="42" t="n"/>
+      <c r="B24" s="43" t="n"/>
+      <c r="C24" s="43" t="n"/>
+      <c r="D24" s="43" t="n"/>
+      <c r="E24" s="43" t="n"/>
+      <c r="F24" s="43" t="n"/>
+      <c r="G24" s="43" t="n"/>
+      <c r="H24" s="43" t="n"/>
+      <c r="I24" s="43" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
+        </is>
+      </c>
+      <c r="B25" s="29" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="29" t="n">
+        <v>-500</v>
+      </c>
+      <c r="E25" s="29" t="n"/>
+      <c r="F25" s="29" t="n"/>
+      <c r="G25" s="29" t="n"/>
+      <c r="H25" s="20">
+        <f>SUM(B25:G25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="47" t="inlineStr">
+        <is>
+          <t>PREENCHER com os vales adiantados durante setembro. GENECIR: adiantamento de R$ 500,00 em 09/09/2026.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="43" t="inlineStr">
-        <is>
-          <t>ADIANTAMENTO SALARIAL / VALES</t>
-        </is>
-      </c>
-      <c r="B26" s="29" t="n"/>
-      <c r="C26" s="29" t="n"/>
-      <c r="D26" s="29" t="n">
-        <v>-500</v>
-      </c>
-      <c r="E26" s="29" t="n"/>
-      <c r="F26" s="29" t="n"/>
-      <c r="G26" s="29" t="n"/>
-      <c r="H26" s="20">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>ADIANT. VALES INCENT. E APLIC.</t>
+        </is>
+      </c>
+      <c r="B26" s="49">
+        <f>-(B20+B21+B22)</f>
+        <v/>
+      </c>
+      <c r="C26" s="49">
+        <f>-(C20+C21+C22)</f>
+        <v/>
+      </c>
+      <c r="D26" s="49">
+        <f>-(D20+D21+D22)</f>
+        <v/>
+      </c>
+      <c r="E26" s="49">
+        <f>-(E20+E21+E22)</f>
+        <v/>
+      </c>
+      <c r="F26" s="49">
+        <f>-(F20+F21+F22)</f>
+        <v/>
+      </c>
+      <c r="G26" s="49">
+        <f>-(G20+G21+G22)</f>
+        <v/>
+      </c>
+      <c r="H26" s="46">
         <f>SUM(B26:G26)</f>
         <v/>
       </c>
-      <c r="I26" s="46" t="inlineStr">
-        <is>
-          <t>PREENCHER com os vales adiantados durante setembro. GENECIR: adiantamento de R$ 500,00 em 09/09/2026.</t>
+      <c r="I26" s="47" t="inlineStr">
+        <is>
+          <t>Estorno dos incentivos já adiantados em dinheiro no mês. AJUSTAR se algum incentivo não foi adiantado.</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="43" t="inlineStr">
-        <is>
-          <t>ADIANT. VALES INCENT. E APLIC.</t>
-        </is>
-      </c>
-      <c r="B27" s="49">
-        <f>-(B21+B22+B23)</f>
-        <v/>
-      </c>
-      <c r="C27" s="49">
-        <f>-(C21+C22+C23)</f>
-        <v/>
-      </c>
-      <c r="D27" s="49">
-        <f>-(D21+D22+D23)</f>
-        <v/>
-      </c>
-      <c r="E27" s="49">
-        <f>-(E21+E22+E23)</f>
-        <v/>
-      </c>
-      <c r="F27" s="49">
-        <f>-(F21+F22+F23)</f>
-        <v/>
-      </c>
-      <c r="G27" s="49">
-        <f>-(G21+G22+G23)</f>
-        <v/>
-      </c>
-      <c r="H27" s="45">
+      <c r="A27" s="44" t="inlineStr">
+        <is>
+          <t>CONVÊNIO</t>
+        </is>
+      </c>
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="29" t="n"/>
+      <c r="G27" s="29" t="n"/>
+      <c r="H27" s="20">
         <f>SUM(B27:G27)</f>
         <v/>
       </c>
-      <c r="I27" s="46" t="inlineStr">
-        <is>
-          <t>Estorno dos incentivos já adiantados em dinheiro no mês. AJUSTAR se algum incentivo não foi adiantado.</t>
+      <c r="I27" s="47" t="inlineStr">
+        <is>
+          <t>PREENCHER conforme o convênio de setembro.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="43" t="inlineStr">
-        <is>
-          <t>CONVÊNIO</t>
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
       <c r="B28" s="29" t="n"/>
@@ -3458,66 +3458,66 @@
         <f>SUM(B28:G28)</f>
         <v/>
       </c>
-      <c r="I28" s="46" t="inlineStr">
-        <is>
-          <t>PREENCHER conforme o convênio de setembro.</t>
+      <c r="I28" s="47" t="inlineStr">
+        <is>
+          <t>PREENCHER conforme o ponto.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="43" t="inlineStr">
-        <is>
-          <t>DESCONTO FALTAS / ATRASOS</t>
-        </is>
-      </c>
-      <c r="B29" s="29" t="n"/>
-      <c r="C29" s="29" t="n"/>
-      <c r="D29" s="29" t="n"/>
-      <c r="E29" s="29" t="n"/>
-      <c r="F29" s="29" t="n"/>
-      <c r="G29" s="29" t="n"/>
-      <c r="H29" s="20">
+      <c r="A29" s="44" t="inlineStr">
+        <is>
+          <t>DESCONTO VALE TRANSPORTE 6%</t>
+        </is>
+      </c>
+      <c r="B29" s="45" t="n"/>
+      <c r="C29" s="45" t="n">
+        <v>-84.29000000000001</v>
+      </c>
+      <c r="D29" s="45" t="n">
+        <v>-84.29000000000001</v>
+      </c>
+      <c r="E29" s="45" t="n"/>
+      <c r="F29" s="45" t="n">
+        <v>-84.29000000000001</v>
+      </c>
+      <c r="G29" s="45" t="n"/>
+      <c r="H29" s="46">
         <f>SUM(B29:G29)</f>
         <v/>
       </c>
-      <c r="I29" s="46" t="inlineStr">
-        <is>
-          <t>PREENCHER conforme o ponto.</t>
+      <c r="I29" s="47" t="inlineStr">
+        <is>
+          <t>Valores praticados em ago/26. 6% sobre R$ 1.621,00 seria R$ 97,26 — CONFERIR a base usada.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="43" t="inlineStr">
-        <is>
-          <t>DESCONTO VALE TRANSPORTE 6%</t>
-        </is>
-      </c>
-      <c r="B30" s="44" t="n"/>
-      <c r="C30" s="44" t="n">
-        <v>-84.29000000000001</v>
-      </c>
-      <c r="D30" s="44" t="n">
-        <v>-84.29000000000001</v>
-      </c>
-      <c r="E30" s="44" t="n"/>
-      <c r="F30" s="44" t="n">
-        <v>-84.29000000000001</v>
-      </c>
-      <c r="G30" s="44" t="n"/>
-      <c r="H30" s="45">
+      <c r="A30" s="44" t="inlineStr">
+        <is>
+          <t>DESCONTO INSS</t>
+        </is>
+      </c>
+      <c r="B30" s="29" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="29" t="n"/>
+      <c r="E30" s="29" t="n"/>
+      <c r="F30" s="29" t="n"/>
+      <c r="G30" s="29" t="n"/>
+      <c r="H30" s="20">
         <f>SUM(B30:G30)</f>
         <v/>
       </c>
-      <c r="I30" s="46" t="inlineStr">
-        <is>
-          <t>Valores praticados em ago/26. 6% sobre R$ 1.621,00 seria R$ 97,26 — CONFERIR a base usada.</t>
+      <c r="I30" s="47" t="inlineStr">
+        <is>
+          <t>A CALCULAR PELA CONTABILIDADE sobre o total de proventos.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="43" t="inlineStr">
-        <is>
-          <t>DESCONTO INSS</t>
+      <c r="A31" s="44" t="inlineStr">
+        <is>
+          <t>DESCONTO IRRF</t>
         </is>
       </c>
       <c r="B31" s="29" t="n"/>
@@ -3530,151 +3530,151 @@
         <f>SUM(B31:G31)</f>
         <v/>
       </c>
-      <c r="I31" s="46" t="inlineStr">
-        <is>
-          <t>A CALCULAR PELA CONTABILIDADE sobre o total de proventos.</t>
+      <c r="I31" s="47" t="inlineStr">
+        <is>
+          <t>A CALCULAR PELA CONTABILIDADE.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="43" t="inlineStr">
-        <is>
-          <t>DESCONTO IRRF</t>
-        </is>
-      </c>
-      <c r="B32" s="29" t="n"/>
-      <c r="C32" s="29" t="n"/>
-      <c r="D32" s="29" t="n"/>
-      <c r="E32" s="29" t="n"/>
-      <c r="F32" s="29" t="n"/>
-      <c r="G32" s="29" t="n"/>
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL DE DESCONTOS</t>
+        </is>
+      </c>
+      <c r="B32" s="20">
+        <f>SUM(B25:B31)</f>
+        <v/>
+      </c>
+      <c r="C32" s="20">
+        <f>SUM(C25:C31)</f>
+        <v/>
+      </c>
+      <c r="D32" s="20">
+        <f>SUM(D25:D31)</f>
+        <v/>
+      </c>
+      <c r="E32" s="20">
+        <f>SUM(E25:E31)</f>
+        <v/>
+      </c>
+      <c r="F32" s="20">
+        <f>SUM(F25:F31)</f>
+        <v/>
+      </c>
+      <c r="G32" s="20">
+        <f>SUM(G25:G31)</f>
+        <v/>
+      </c>
       <c r="H32" s="20">
         <f>SUM(B32:G32)</f>
         <v/>
       </c>
-      <c r="I32" s="46" t="inlineStr">
-        <is>
-          <t>A CALCULAR PELA CONTABILIDADE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL DE DESCONTOS</t>
-        </is>
-      </c>
-      <c r="B33" s="20">
-        <f>SUM(B26:B32)</f>
-        <v/>
-      </c>
-      <c r="C33" s="20">
-        <f>SUM(C26:C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="20">
-        <f>SUM(D26:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="20">
-        <f>SUM(E26:E32)</f>
-        <v/>
-      </c>
-      <c r="F33" s="20">
-        <f>SUM(F26:F32)</f>
-        <v/>
-      </c>
-      <c r="G33" s="20">
-        <f>SUM(G26:G32)</f>
-        <v/>
-      </c>
-      <c r="H33" s="20">
-        <f>SUM(B33:G33)</f>
-        <v/>
-      </c>
-      <c r="I33" s="46" t="inlineStr"/>
-    </row>
-    <row r="34" ht="19" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="I32" s="47" t="inlineStr"/>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>LÍQUIDO</t>
         </is>
       </c>
-      <c r="B34" s="42" t="n"/>
-      <c r="C34" s="42" t="n"/>
-      <c r="D34" s="42" t="n"/>
-      <c r="E34" s="42" t="n"/>
-      <c r="F34" s="42" t="n"/>
-      <c r="G34" s="42" t="n"/>
-      <c r="H34" s="42" t="n"/>
-      <c r="I34" s="42" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="B33" s="43" t="n"/>
+      <c r="C33" s="43" t="n"/>
+      <c r="D33" s="43" t="n"/>
+      <c r="E33" s="43" t="n"/>
+      <c r="F33" s="43" t="n"/>
+      <c r="G33" s="43" t="n"/>
+      <c r="H33" s="43" t="n"/>
+      <c r="I33" s="43" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER (05/10/2026)</t>
         </is>
       </c>
-      <c r="B35" s="36">
-        <f>B24+B33</f>
-        <v/>
-      </c>
-      <c r="C35" s="36">
-        <f>C24+C33</f>
-        <v/>
-      </c>
-      <c r="D35" s="36">
-        <f>D24+D33</f>
-        <v/>
-      </c>
-      <c r="E35" s="36">
-        <f>E24+E33</f>
-        <v/>
-      </c>
-      <c r="F35" s="36">
-        <f>F24+F33</f>
-        <v/>
-      </c>
-      <c r="G35" s="36">
-        <f>G24+G33</f>
-        <v/>
-      </c>
-      <c r="H35" s="36">
-        <f>SUM(B35:G35)</f>
-        <v/>
-      </c>
-      <c r="I35" s="46" t="inlineStr">
+      <c r="B34" s="37">
+        <f>B23+B32</f>
+        <v/>
+      </c>
+      <c r="C34" s="37">
+        <f>C23+C32</f>
+        <v/>
+      </c>
+      <c r="D34" s="37">
+        <f>D23+D32</f>
+        <v/>
+      </c>
+      <c r="E34" s="37">
+        <f>E23+E32</f>
+        <v/>
+      </c>
+      <c r="F34" s="37">
+        <f>F23+F32</f>
+        <v/>
+      </c>
+      <c r="G34" s="37">
+        <f>G23+G32</f>
+        <v/>
+      </c>
+      <c r="H34" s="37">
+        <f>SUM(B34:G34)</f>
+        <v/>
+      </c>
+      <c r="I34" s="47" t="inlineStr">
         <is>
           <t>Total de proventos menos descontos. Só fica definitivo depois do INSS/IRRF da contabilidade.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>INFORMATIVO — PAGO PELA EMPRESA, NÃO ENTRA NO HOLERITE</t>
         </is>
       </c>
-      <c r="B36" s="42" t="n"/>
-      <c r="C36" s="42" t="n"/>
-      <c r="D36" s="42" t="n"/>
-      <c r="E36" s="42" t="n"/>
-      <c r="F36" s="42" t="n"/>
-      <c r="G36" s="42" t="n"/>
-      <c r="H36" s="42" t="n"/>
-      <c r="I36" s="42" t="n"/>
+      <c r="B35" s="43" t="n"/>
+      <c r="C35" s="43" t="n"/>
+      <c r="D35" s="43" t="n"/>
+      <c r="E35" s="43" t="n"/>
+      <c r="F35" s="43" t="n"/>
+      <c r="G35" s="43" t="n"/>
+      <c r="H35" s="43" t="n"/>
+      <c r="I35" s="43" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="44" t="inlineStr">
+        <is>
+          <t>VALE TRANSPORTE (compra out/26)</t>
+        </is>
+      </c>
+      <c r="B36" s="29" t="n"/>
+      <c r="C36" s="29" t="n"/>
+      <c r="D36" s="29" t="n">
+        <v>270</v>
+      </c>
+      <c r="E36" s="29" t="n"/>
+      <c r="F36" s="29" t="n"/>
+      <c r="G36" s="29" t="n"/>
+      <c r="H36" s="20">
+        <f>SUM(B36:G36)</f>
+        <v/>
+      </c>
+      <c r="I36" s="47" t="inlineStr">
+        <is>
+          <t>PREENCHER com as passagens compradas. GENECIR: R$ 270,00 de vale-transporte.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="43" t="inlineStr">
-        <is>
-          <t>VALE TRANSPORTE (compra out/26)</t>
+      <c r="A37" s="44" t="inlineStr">
+        <is>
+          <t>VALE ALIMENTAÇÃO FERIADOS E DOMINGOS</t>
         </is>
       </c>
       <c r="B37" s="29" t="n"/>
       <c r="C37" s="29" t="n"/>
-      <c r="D37" s="29" t="n">
-        <v>270</v>
-      </c>
+      <c r="D37" s="29" t="n"/>
       <c r="E37" s="29" t="n"/>
       <c r="F37" s="29" t="n"/>
       <c r="G37" s="29" t="n"/>
@@ -3682,122 +3682,100 @@
         <f>SUM(B37:G37)</f>
         <v/>
       </c>
-      <c r="I37" s="46" t="inlineStr">
-        <is>
-          <t>PREENCHER com as passagens compradas. GENECIR: R$ 270,00 de vale-transporte.</t>
+      <c r="I37" s="47" t="inlineStr">
+        <is>
+          <t>PREENCHER conforme escala de domingos e feriados.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="43" t="inlineStr">
-        <is>
-          <t>VALE ALIMENTAÇÃO FERIADOS E DOMINGOS</t>
-        </is>
-      </c>
-      <c r="B38" s="29" t="n"/>
-      <c r="C38" s="29" t="n"/>
-      <c r="D38" s="29" t="n"/>
-      <c r="E38" s="29" t="n"/>
-      <c r="F38" s="29" t="n"/>
-      <c r="G38" s="29" t="n"/>
-      <c r="H38" s="20">
+      <c r="A38" s="44" t="inlineStr">
+        <is>
+          <t>FÉRIAS PAGAS À PARTE (CONTAS A PAGAR)</t>
+        </is>
+      </c>
+      <c r="B38" s="45" t="n"/>
+      <c r="C38" s="45" t="n"/>
+      <c r="D38" s="45" t="n"/>
+      <c r="E38" s="45" t="n"/>
+      <c r="F38" s="45" t="n"/>
+      <c r="G38" s="45" t="n"/>
+      <c r="H38" s="46">
         <f>SUM(B38:G38)</f>
         <v/>
       </c>
-      <c r="I38" s="46" t="inlineStr">
-        <is>
-          <t>PREENCHER conforme escala de domingos e feriados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="43" t="inlineStr">
-        <is>
-          <t>FÉRIAS PAGAS À PARTE (CONTAS A PAGAR)</t>
-        </is>
-      </c>
-      <c r="B39" s="44" t="n"/>
-      <c r="C39" s="44" t="n"/>
-      <c r="D39" s="44" t="n"/>
-      <c r="E39" s="44" t="n"/>
-      <c r="F39" s="44" t="n"/>
-      <c r="G39" s="44" t="n"/>
-      <c r="H39" s="45">
-        <f>SUM(B39:G39)</f>
-        <v/>
-      </c>
-      <c r="I39" s="46" t="inlineStr">
+      <c r="I38" s="47" t="inlineStr">
         <is>
           <t>Recibo de férias pago fora do holerite — lembrete para o contas a pagar. RENALDO: férias de 01 a 30/09/2026 — informar o valor do recibo.</t>
         </is>
       </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>LEGENDA</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
-          <t>LEGENDA</t>
-        </is>
-      </c>
-      <c r="B41" s="22" t="inlineStr"/>
+          <t>Célula amarela, texto azul</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="inlineStr">
         <is>
-          <t>Célula amarela, texto azul</t>
+          <t>Célula laranja</t>
         </is>
       </c>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
+          <t>valor repetido de agosto/2026 — CONFERIR se continua válido em setembro.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="inlineStr">
         <is>
-          <t>Célula laranja</t>
+          <t>Texto verde</t>
         </is>
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>valor repetido de agosto/2026 — CONFERIR se continua válido em setembro.</t>
+          <t>valor puxado da aba BASE INOVAFARMA SET.26 (não digitar por cima).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="inlineStr">
         <is>
-          <t>Texto verde</t>
+          <t>Texto preto em célula verde</t>
         </is>
       </c>
       <c r="B44" s="22" t="inlineStr">
         <is>
-          <t>valor puxado da aba BASE INOVAFARMA SET.26 (não digitar por cima).</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="21" t="inlineStr">
-        <is>
-          <t>Texto preto em célula verde</t>
-        </is>
-      </c>
-      <c r="B45" s="22" t="inlineStr">
-        <is>
           <t>resultado de fórmula — não alterar.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I39"/>
+  <autoFilter ref="A4:I38"/>
   <mergeCells count="7">
     <mergeCell ref="B44:I44"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="B42:I42"/>
-    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="B43:I43"/>
     <mergeCell ref="B41:I41"/>
-    <mergeCell ref="B43:I43"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3809,7 +3787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E165"/>
+  <dimension ref="A1:E159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3834,3466 +3812,3334 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>FUNCIONÁRIO</t>
         </is>
       </c>
-      <c r="B4" s="40" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>RUBRICA</t>
         </is>
       </c>
-      <c r="C4" s="40" t="inlineStr">
+      <c r="C4" s="41" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="D4" s="40" t="inlineStr">
+      <c r="D4" s="41" t="inlineStr">
         <is>
           <t>VALOR</t>
         </is>
       </c>
-      <c r="E4" s="40" t="inlineStr">
+      <c r="E4" s="41" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C5" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D5" s="47">
+      <c r="C5" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D5" s="36">
         <f>'HOLERITE SET.26'!B6</f>
         <v/>
       </c>
       <c r="E5" s="50" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="43" t="inlineStr">
+      <c r="A6" s="44" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C6" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D6" s="47">
+      <c r="C6" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D6" s="36">
         <f>'HOLERITE SET.26'!B7</f>
         <v/>
       </c>
       <c r="E6" s="50" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="43" t="inlineStr">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C7" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D7" s="47">
+      <c r="C7" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D7" s="36">
         <f>'HOLERITE SET.26'!B8</f>
         <v/>
       </c>
       <c r="E7" s="50" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="inlineStr">
+      <c r="A8" s="44" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B8" s="43" t="inlineStr">
+      <c r="B8" s="44" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C8" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D8" s="47">
+      <c r="C8" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D8" s="36">
         <f>'HOLERITE SET.26'!B11</f>
         <v/>
       </c>
       <c r="E8" s="50" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="A9" s="44" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B9" s="43" t="inlineStr">
+      <c r="B9" s="44" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C9" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D9" s="47">
+      <c r="C9" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D9" s="36">
         <f>'HOLERITE SET.26'!B12</f>
         <v/>
       </c>
       <c r="E9" s="50" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="44" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B10" s="43" t="inlineStr">
+      <c r="B10" s="44" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C10" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D10" s="47">
+      <c r="C10" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D10" s="36">
         <f>'HOLERITE SET.26'!B13</f>
         <v/>
       </c>
       <c r="E10" s="50" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="44" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B11" s="43" t="inlineStr">
+      <c r="B11" s="44" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C11" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D11" s="47">
+      <c r="C11" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D11" s="36">
         <f>'HOLERITE SET.26'!B14</f>
         <v/>
       </c>
       <c r="E11" s="50" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="44" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B12" s="43" t="inlineStr">
+      <c r="B12" s="44" t="inlineStr">
         <is>
           <t>PRÊMIO META 1 — VOLUME</t>
         </is>
       </c>
-      <c r="C12" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D12" s="47">
+      <c r="C12" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D12" s="36">
         <f>'HOLERITE SET.26'!B15</f>
         <v/>
       </c>
       <c r="E12" s="50" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="A13" s="44" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B13" s="43" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
-        </is>
-      </c>
-      <c r="C13" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D13" s="47">
+      <c r="B13" s="44" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
+        </is>
+      </c>
+      <c r="C13" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D13" s="36">
         <f>'HOLERITE SET.26'!B16</f>
         <v/>
       </c>
       <c r="E13" s="50" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="44" t="inlineStr">
         <is>
           <t>ARIANE</t>
         </is>
       </c>
-      <c r="B14" s="43" t="inlineStr">
+      <c r="B14" s="44" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
+        </is>
+      </c>
+      <c r="C14" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D14" s="36">
+        <f>'HOLERITE SET.26'!B17</f>
+        <v/>
+      </c>
+      <c r="E14" s="50" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="44" t="inlineStr">
+        <is>
+          <t>ARIANE</t>
+        </is>
+      </c>
+      <c r="B15" s="44" t="inlineStr">
+        <is>
+          <t>FÉRIAS</t>
+        </is>
+      </c>
+      <c r="C15" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D15" s="36">
+        <f>'HOLERITE SET.26'!B18</f>
+        <v/>
+      </c>
+      <c r="E15" s="50" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="44" t="inlineStr">
+        <is>
+          <t>ARIANE</t>
+        </is>
+      </c>
+      <c r="B16" s="44" t="inlineStr">
+        <is>
+          <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
+        </is>
+      </c>
+      <c r="C16" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D16" s="36">
+        <f>'HOLERITE SET.26'!B19</f>
+        <v/>
+      </c>
+      <c r="E16" s="50" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="44" t="inlineStr">
+        <is>
+          <t>ARIANE</t>
+        </is>
+      </c>
+      <c r="B17" s="44" t="inlineStr">
+        <is>
+          <t>INCENTIVO APLICAÇÕES</t>
+        </is>
+      </c>
+      <c r="C17" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D17" s="36">
+        <f>'HOLERITE SET.26'!B20</f>
+        <v/>
+      </c>
+      <c r="E17" s="50" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="44" t="inlineStr">
+        <is>
+          <t>ARIANE</t>
+        </is>
+      </c>
+      <c r="B18" s="44" t="inlineStr">
+        <is>
+          <t>INCENTIVO VITAMINAS</t>
+        </is>
+      </c>
+      <c r="C18" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D18" s="36">
+        <f>'HOLERITE SET.26'!B21</f>
+        <v/>
+      </c>
+      <c r="E18" s="50" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="44" t="inlineStr">
+        <is>
+          <t>ARIANE</t>
+        </is>
+      </c>
+      <c r="B19" s="44" t="inlineStr">
+        <is>
+          <t>OUTROS INCENTIVOS</t>
+        </is>
+      </c>
+      <c r="C19" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D19" s="36">
+        <f>'HOLERITE SET.26'!B22</f>
+        <v/>
+      </c>
+      <c r="E19" s="50" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="51" t="inlineStr">
+        <is>
+          <t>ARIANE</t>
+        </is>
+      </c>
+      <c r="B20" s="51" t="inlineStr">
+        <is>
+          <t>TOTAL DE PROVENTOS</t>
+        </is>
+      </c>
+      <c r="C20" s="51" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="D20" s="52">
+        <f>'HOLERITE SET.26'!B23</f>
+        <v/>
+      </c>
+      <c r="E20" s="18" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="44" t="inlineStr">
+        <is>
+          <t>ARIANE</t>
+        </is>
+      </c>
+      <c r="B21" s="44" t="inlineStr">
+        <is>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
+        </is>
+      </c>
+      <c r="C21" s="44" t="inlineStr">
+        <is>
+          <t>Desconto</t>
+        </is>
+      </c>
+      <c r="D21" s="36">
+        <f>'HOLERITE SET.26'!B25</f>
+        <v/>
+      </c>
+      <c r="E21" s="50" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="44" t="inlineStr">
+        <is>
+          <t>ARIANE</t>
+        </is>
+      </c>
+      <c r="B22" s="44" t="inlineStr">
+        <is>
+          <t>ADIANT. VALES INCENT. E APLIC.</t>
+        </is>
+      </c>
+      <c r="C22" s="44" t="inlineStr">
+        <is>
+          <t>Desconto</t>
+        </is>
+      </c>
+      <c r="D22" s="36">
+        <f>'HOLERITE SET.26'!B26</f>
+        <v/>
+      </c>
+      <c r="E22" s="50" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="44" t="inlineStr">
+        <is>
+          <t>ARIANE</t>
+        </is>
+      </c>
+      <c r="B23" s="44" t="inlineStr">
+        <is>
+          <t>CONVÊNIO</t>
+        </is>
+      </c>
+      <c r="C23" s="44" t="inlineStr">
+        <is>
+          <t>Desconto</t>
+        </is>
+      </c>
+      <c r="D23" s="36">
+        <f>'HOLERITE SET.26'!B27</f>
+        <v/>
+      </c>
+      <c r="E23" s="50" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="44" t="inlineStr">
+        <is>
+          <t>ARIANE</t>
+        </is>
+      </c>
+      <c r="B24" s="44" t="inlineStr">
+        <is>
+          <t>DESCONTO FALTAS / ATRASOS</t>
+        </is>
+      </c>
+      <c r="C24" s="44" t="inlineStr">
+        <is>
+          <t>Desconto</t>
+        </is>
+      </c>
+      <c r="D24" s="36">
+        <f>'HOLERITE SET.26'!B28</f>
+        <v/>
+      </c>
+      <c r="E24" s="50" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="44" t="inlineStr">
+        <is>
+          <t>ARIANE</t>
+        </is>
+      </c>
+      <c r="B25" s="44" t="inlineStr">
+        <is>
+          <t>DESCONTO VALE TRANSPORTE 6%</t>
+        </is>
+      </c>
+      <c r="C25" s="44" t="inlineStr">
+        <is>
+          <t>Desconto</t>
+        </is>
+      </c>
+      <c r="D25" s="36">
+        <f>'HOLERITE SET.26'!B29</f>
+        <v/>
+      </c>
+      <c r="E25" s="50" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="44" t="inlineStr">
+        <is>
+          <t>ARIANE</t>
+        </is>
+      </c>
+      <c r="B26" s="44" t="inlineStr">
+        <is>
+          <t>DESCONTO INSS</t>
+        </is>
+      </c>
+      <c r="C26" s="44" t="inlineStr">
+        <is>
+          <t>Desconto</t>
+        </is>
+      </c>
+      <c r="D26" s="36">
+        <f>'HOLERITE SET.26'!B30</f>
+        <v/>
+      </c>
+      <c r="E26" s="50" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="44" t="inlineStr">
+        <is>
+          <t>ARIANE</t>
+        </is>
+      </c>
+      <c r="B27" s="44" t="inlineStr">
+        <is>
+          <t>DESCONTO IRRF</t>
+        </is>
+      </c>
+      <c r="C27" s="44" t="inlineStr">
+        <is>
+          <t>Desconto</t>
+        </is>
+      </c>
+      <c r="D27" s="36">
+        <f>'HOLERITE SET.26'!B31</f>
+        <v/>
+      </c>
+      <c r="E27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="51" t="inlineStr">
+        <is>
+          <t>ARIANE</t>
+        </is>
+      </c>
+      <c r="B28" s="51" t="inlineStr">
+        <is>
+          <t>TOTAL DE DESCONTOS</t>
+        </is>
+      </c>
+      <c r="C28" s="51" t="inlineStr">
+        <is>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="D28" s="52">
+        <f>'HOLERITE SET.26'!B32</f>
+        <v/>
+      </c>
+      <c r="E28" s="18" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="53" t="inlineStr">
+        <is>
+          <t>ARIANE</t>
+        </is>
+      </c>
+      <c r="B29" s="54" t="inlineStr">
+        <is>
+          <t>LÍQUIDO A RECEBER</t>
+        </is>
+      </c>
+      <c r="C29" s="54" t="inlineStr">
+        <is>
+          <t>Líquido</t>
+        </is>
+      </c>
+      <c r="D29" s="55">
+        <f>'HOLERITE SET.26'!B34</f>
+        <v/>
+      </c>
+      <c r="E29" s="56" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B31" s="44" t="inlineStr">
+        <is>
+          <t>SALÁRIO BASE</t>
+        </is>
+      </c>
+      <c r="C31" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D31" s="36">
+        <f>'HOLERITE SET.26'!C6</f>
+        <v/>
+      </c>
+      <c r="E31" s="50" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B32" s="44" t="inlineStr">
+        <is>
+          <t>ADICIONAL NOTURNO</t>
+        </is>
+      </c>
+      <c r="C32" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D32" s="36">
+        <f>'HOLERITE SET.26'!C7</f>
+        <v/>
+      </c>
+      <c r="E32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B33" s="44" t="inlineStr">
+        <is>
+          <t>HORAS EXTRAS</t>
+        </is>
+      </c>
+      <c r="C33" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D33" s="36">
+        <f>'HOLERITE SET.26'!C8</f>
+        <v/>
+      </c>
+      <c r="E33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B34" s="44" t="inlineStr">
+        <is>
+          <t>COMISSÃO SOBRE VENDAS</t>
+        </is>
+      </c>
+      <c r="C34" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D34" s="36">
+        <f>'HOLERITE SET.26'!C11</f>
+        <v/>
+      </c>
+      <c r="E34" s="50" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B35" s="44" t="inlineStr">
+        <is>
+          <t>REPOUSO REMUNERADO / DSR</t>
+        </is>
+      </c>
+      <c r="C35" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D35" s="36">
+        <f>'HOLERITE SET.26'!C12</f>
+        <v/>
+      </c>
+      <c r="E35" s="50" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B36" s="44" t="inlineStr">
+        <is>
+          <t>AUXÍLIO GERÊNCIA</t>
+        </is>
+      </c>
+      <c r="C36" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D36" s="36">
+        <f>'HOLERITE SET.26'!C13</f>
+        <v/>
+      </c>
+      <c r="E36" s="50" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B37" s="44" t="inlineStr">
+        <is>
+          <t>ADICIONAL PRÊMIO META CAIXA</t>
+        </is>
+      </c>
+      <c r="C37" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D37" s="36">
+        <f>'HOLERITE SET.26'!C14</f>
+        <v/>
+      </c>
+      <c r="E37" s="50" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B38" s="44" t="inlineStr">
+        <is>
+          <t>PRÊMIO META 1 — VOLUME</t>
+        </is>
+      </c>
+      <c r="C38" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D38" s="36">
+        <f>'HOLERITE SET.26'!C15</f>
+        <v/>
+      </c>
+      <c r="E38" s="50" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B39" s="44" t="inlineStr">
         <is>
           <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="C14" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D14" s="47">
-        <f>'HOLERITE SET.26'!B17</f>
-        <v/>
-      </c>
-      <c r="E14" s="50" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="43" t="inlineStr">
-        <is>
-          <t>ARIANE</t>
-        </is>
-      </c>
-      <c r="B15" s="43" t="inlineStr">
+      <c r="C39" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D39" s="36">
+        <f>'HOLERITE SET.26'!C16</f>
+        <v/>
+      </c>
+      <c r="E39" s="50" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B40" s="44" t="inlineStr">
         <is>
           <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
         </is>
       </c>
-      <c r="C15" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D15" s="47">
-        <f>'HOLERITE SET.26'!B18</f>
-        <v/>
-      </c>
-      <c r="E15" s="50" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="43" t="inlineStr">
-        <is>
-          <t>ARIANE</t>
-        </is>
-      </c>
-      <c r="B16" s="43" t="inlineStr">
+      <c r="C40" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D40" s="36">
+        <f>'HOLERITE SET.26'!C17</f>
+        <v/>
+      </c>
+      <c r="E40" s="50" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B41" s="44" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C16" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D16" s="47">
-        <f>'HOLERITE SET.26'!B19</f>
-        <v/>
-      </c>
-      <c r="E16" s="50" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="43" t="inlineStr">
-        <is>
-          <t>ARIANE</t>
-        </is>
-      </c>
-      <c r="B17" s="43" t="inlineStr">
+      <c r="C41" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D41" s="36">
+        <f>'HOLERITE SET.26'!C18</f>
+        <v/>
+      </c>
+      <c r="E41" s="50" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B42" s="44" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C17" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D17" s="47">
-        <f>'HOLERITE SET.26'!B20</f>
-        <v/>
-      </c>
-      <c r="E17" s="50" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="43" t="inlineStr">
-        <is>
-          <t>ARIANE</t>
-        </is>
-      </c>
-      <c r="B18" s="43" t="inlineStr">
+      <c r="C42" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D42" s="36">
+        <f>'HOLERITE SET.26'!C19</f>
+        <v/>
+      </c>
+      <c r="E42" s="50" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B43" s="44" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C18" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D18" s="47">
-        <f>'HOLERITE SET.26'!B21</f>
-        <v/>
-      </c>
-      <c r="E18" s="50" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="43" t="inlineStr">
-        <is>
-          <t>ARIANE</t>
-        </is>
-      </c>
-      <c r="B19" s="43" t="inlineStr">
+      <c r="C43" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D43" s="36">
+        <f>'HOLERITE SET.26'!C20</f>
+        <v/>
+      </c>
+      <c r="E43" s="50" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B44" s="44" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C19" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D19" s="47">
-        <f>'HOLERITE SET.26'!B22</f>
-        <v/>
-      </c>
-      <c r="E19" s="50" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="43" t="inlineStr">
-        <is>
-          <t>ARIANE</t>
-        </is>
-      </c>
-      <c r="B20" s="43" t="inlineStr">
+      <c r="C44" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D44" s="36">
+        <f>'HOLERITE SET.26'!C21</f>
+        <v/>
+      </c>
+      <c r="E44" s="50" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B45" s="44" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C20" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D20" s="47">
-        <f>'HOLERITE SET.26'!B23</f>
-        <v/>
-      </c>
-      <c r="E20" s="50" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="51" t="inlineStr">
-        <is>
-          <t>ARIANE</t>
-        </is>
-      </c>
-      <c r="B21" s="51" t="inlineStr">
+      <c r="C45" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D45" s="36">
+        <f>'HOLERITE SET.26'!C22</f>
+        <v/>
+      </c>
+      <c r="E45" s="50" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="51" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B46" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C21" s="51" t="inlineStr">
+      <c r="C46" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D21" s="52">
-        <f>'HOLERITE SET.26'!B24</f>
-        <v/>
-      </c>
-      <c r="E21" s="18" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="43" t="inlineStr">
-        <is>
-          <t>ARIANE</t>
-        </is>
-      </c>
-      <c r="B22" s="43" t="inlineStr">
+      <c r="D46" s="52">
+        <f>'HOLERITE SET.26'!C23</f>
+        <v/>
+      </c>
+      <c r="E46" s="18" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B47" s="44" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C22" s="43" t="inlineStr">
+      <c r="C47" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D22" s="47">
-        <f>'HOLERITE SET.26'!B26</f>
-        <v/>
-      </c>
-      <c r="E22" s="50" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="43" t="inlineStr">
-        <is>
-          <t>ARIANE</t>
-        </is>
-      </c>
-      <c r="B23" s="43" t="inlineStr">
+      <c r="D47" s="36">
+        <f>'HOLERITE SET.26'!C25</f>
+        <v/>
+      </c>
+      <c r="E47" s="50" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B48" s="44" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C23" s="43" t="inlineStr">
+      <c r="C48" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D23" s="47">
-        <f>'HOLERITE SET.26'!B27</f>
-        <v/>
-      </c>
-      <c r="E23" s="50" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="43" t="inlineStr">
-        <is>
-          <t>ARIANE</t>
-        </is>
-      </c>
-      <c r="B24" s="43" t="inlineStr">
+      <c r="D48" s="36">
+        <f>'HOLERITE SET.26'!C26</f>
+        <v/>
+      </c>
+      <c r="E48" s="50" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B49" s="44" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C24" s="43" t="inlineStr">
+      <c r="C49" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D24" s="47">
-        <f>'HOLERITE SET.26'!B28</f>
-        <v/>
-      </c>
-      <c r="E24" s="50" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="43" t="inlineStr">
-        <is>
-          <t>ARIANE</t>
-        </is>
-      </c>
-      <c r="B25" s="43" t="inlineStr">
+      <c r="D49" s="36">
+        <f>'HOLERITE SET.26'!C27</f>
+        <v/>
+      </c>
+      <c r="E49" s="50" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B50" s="44" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C25" s="43" t="inlineStr">
+      <c r="C50" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D25" s="47">
-        <f>'HOLERITE SET.26'!B29</f>
-        <v/>
-      </c>
-      <c r="E25" s="50" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="43" t="inlineStr">
-        <is>
-          <t>ARIANE</t>
-        </is>
-      </c>
-      <c r="B26" s="43" t="inlineStr">
+      <c r="D50" s="36">
+        <f>'HOLERITE SET.26'!C28</f>
+        <v/>
+      </c>
+      <c r="E50" s="50" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B51" s="44" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C26" s="43" t="inlineStr">
+      <c r="C51" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D26" s="47">
-        <f>'HOLERITE SET.26'!B30</f>
-        <v/>
-      </c>
-      <c r="E26" s="50" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="43" t="inlineStr">
-        <is>
-          <t>ARIANE</t>
-        </is>
-      </c>
-      <c r="B27" s="43" t="inlineStr">
+      <c r="D51" s="36">
+        <f>'HOLERITE SET.26'!C29</f>
+        <v/>
+      </c>
+      <c r="E51" s="50" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B52" s="44" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C27" s="43" t="inlineStr">
+      <c r="C52" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D27" s="47">
-        <f>'HOLERITE SET.26'!B31</f>
-        <v/>
-      </c>
-      <c r="E27" s="50" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="43" t="inlineStr">
-        <is>
-          <t>ARIANE</t>
-        </is>
-      </c>
-      <c r="B28" s="43" t="inlineStr">
+      <c r="D52" s="36">
+        <f>'HOLERITE SET.26'!C30</f>
+        <v/>
+      </c>
+      <c r="E52" s="50" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="44" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B53" s="44" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C28" s="43" t="inlineStr">
+      <c r="C53" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D28" s="47">
-        <f>'HOLERITE SET.26'!B32</f>
-        <v/>
-      </c>
-      <c r="E28" s="50" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="51" t="inlineStr">
-        <is>
-          <t>ARIANE</t>
-        </is>
-      </c>
-      <c r="B29" s="51" t="inlineStr">
+      <c r="D53" s="36">
+        <f>'HOLERITE SET.26'!C31</f>
+        <v/>
+      </c>
+      <c r="E53" s="50" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="51" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B54" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C29" s="51" t="inlineStr">
+      <c r="C54" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D29" s="52">
-        <f>'HOLERITE SET.26'!B33</f>
-        <v/>
-      </c>
-      <c r="E29" s="18" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="53" t="inlineStr">
-        <is>
-          <t>ARIANE</t>
-        </is>
-      </c>
-      <c r="B30" s="54" t="inlineStr">
+      <c r="D54" s="52">
+        <f>'HOLERITE SET.26'!C32</f>
+        <v/>
+      </c>
+      <c r="E54" s="18" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="53" t="inlineStr">
+        <is>
+          <t>ELIANA</t>
+        </is>
+      </c>
+      <c r="B55" s="54" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C30" s="54" t="inlineStr">
+      <c r="C55" s="54" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D30" s="55">
-        <f>'HOLERITE SET.26'!B35</f>
-        <v/>
-      </c>
-      <c r="E30" s="56" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B32" s="43" t="inlineStr">
+      <c r="D55" s="55">
+        <f>'HOLERITE SET.26'!C34</f>
+        <v/>
+      </c>
+      <c r="E55" s="56" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B57" s="44" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C32" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D32" s="47">
-        <f>'HOLERITE SET.26'!C6</f>
-        <v/>
-      </c>
-      <c r="E32" s="50" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B33" s="43" t="inlineStr">
+      <c r="C57" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D57" s="36">
+        <f>'HOLERITE SET.26'!D6</f>
+        <v/>
+      </c>
+      <c r="E57" s="50" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B58" s="44" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C33" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D33" s="47">
-        <f>'HOLERITE SET.26'!C7</f>
-        <v/>
-      </c>
-      <c r="E33" s="50" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B34" s="43" t="inlineStr">
+      <c r="C58" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D58" s="36">
+        <f>'HOLERITE SET.26'!D7</f>
+        <v/>
+      </c>
+      <c r="E58" s="50" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B59" s="44" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C34" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D34" s="47">
-        <f>'HOLERITE SET.26'!C8</f>
-        <v/>
-      </c>
-      <c r="E34" s="50" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B35" s="43" t="inlineStr">
+      <c r="C59" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D59" s="36">
+        <f>'HOLERITE SET.26'!D8</f>
+        <v/>
+      </c>
+      <c r="E59" s="50" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B60" s="44" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C35" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D35" s="47">
-        <f>'HOLERITE SET.26'!C11</f>
-        <v/>
-      </c>
-      <c r="E35" s="50" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B36" s="43" t="inlineStr">
+      <c r="C60" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D60" s="36">
+        <f>'HOLERITE SET.26'!D11</f>
+        <v/>
+      </c>
+      <c r="E60" s="50" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B61" s="44" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C36" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D36" s="47">
-        <f>'HOLERITE SET.26'!C12</f>
-        <v/>
-      </c>
-      <c r="E36" s="50" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B37" s="43" t="inlineStr">
+      <c r="C61" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D61" s="36">
+        <f>'HOLERITE SET.26'!D12</f>
+        <v/>
+      </c>
+      <c r="E61" s="50" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B62" s="44" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C37" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D37" s="47">
-        <f>'HOLERITE SET.26'!C13</f>
-        <v/>
-      </c>
-      <c r="E37" s="50" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B38" s="43" t="inlineStr">
+      <c r="C62" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D62" s="36">
+        <f>'HOLERITE SET.26'!D13</f>
+        <v/>
+      </c>
+      <c r="E62" s="50" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B63" s="44" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C38" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D38" s="47">
-        <f>'HOLERITE SET.26'!C14</f>
-        <v/>
-      </c>
-      <c r="E38" s="50" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B39" s="43" t="inlineStr">
+      <c r="C63" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D63" s="36">
+        <f>'HOLERITE SET.26'!D14</f>
+        <v/>
+      </c>
+      <c r="E63" s="50" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B64" s="44" t="inlineStr">
         <is>
           <t>PRÊMIO META 1 — VOLUME</t>
         </is>
       </c>
-      <c r="C39" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D39" s="47">
-        <f>'HOLERITE SET.26'!C15</f>
-        <v/>
-      </c>
-      <c r="E39" s="50" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B40" s="43" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
-        </is>
-      </c>
-      <c r="C40" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D40" s="47">
-        <f>'HOLERITE SET.26'!C16</f>
-        <v/>
-      </c>
-      <c r="E40" s="50" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B41" s="43" t="inlineStr">
+      <c r="C64" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D64" s="36">
+        <f>'HOLERITE SET.26'!D15</f>
+        <v/>
+      </c>
+      <c r="E64" s="50" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B65" s="44" t="inlineStr">
         <is>
           <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="C41" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D41" s="47">
-        <f>'HOLERITE SET.26'!C17</f>
-        <v/>
-      </c>
-      <c r="E41" s="50" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B42" s="43" t="inlineStr">
+      <c r="C65" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D65" s="36">
+        <f>'HOLERITE SET.26'!D16</f>
+        <v/>
+      </c>
+      <c r="E65" s="50" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B66" s="44" t="inlineStr">
         <is>
           <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
         </is>
       </c>
-      <c r="C42" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D42" s="47">
-        <f>'HOLERITE SET.26'!C18</f>
-        <v/>
-      </c>
-      <c r="E42" s="50" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B43" s="43" t="inlineStr">
+      <c r="C66" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D66" s="36">
+        <f>'HOLERITE SET.26'!D17</f>
+        <v/>
+      </c>
+      <c r="E66" s="50" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B67" s="44" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C43" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D43" s="47">
-        <f>'HOLERITE SET.26'!C19</f>
-        <v/>
-      </c>
-      <c r="E43" s="50" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B44" s="43" t="inlineStr">
+      <c r="C67" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D67" s="36">
+        <f>'HOLERITE SET.26'!D18</f>
+        <v/>
+      </c>
+      <c r="E67" s="50" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B68" s="44" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C44" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D44" s="47">
-        <f>'HOLERITE SET.26'!C20</f>
-        <v/>
-      </c>
-      <c r="E44" s="50" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B45" s="43" t="inlineStr">
+      <c r="C68" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D68" s="36">
+        <f>'HOLERITE SET.26'!D19</f>
+        <v/>
+      </c>
+      <c r="E68" s="50" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B69" s="44" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C45" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D45" s="47">
-        <f>'HOLERITE SET.26'!C21</f>
-        <v/>
-      </c>
-      <c r="E45" s="50" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B46" s="43" t="inlineStr">
+      <c r="C69" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D69" s="36">
+        <f>'HOLERITE SET.26'!D20</f>
+        <v/>
+      </c>
+      <c r="E69" s="50" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B70" s="44" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C46" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D46" s="47">
-        <f>'HOLERITE SET.26'!C22</f>
-        <v/>
-      </c>
-      <c r="E46" s="50" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B47" s="43" t="inlineStr">
+      <c r="C70" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D70" s="36">
+        <f>'HOLERITE SET.26'!D21</f>
+        <v/>
+      </c>
+      <c r="E70" s="50" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B71" s="44" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C47" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D47" s="47">
-        <f>'HOLERITE SET.26'!C23</f>
-        <v/>
-      </c>
-      <c r="E47" s="50" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="51" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B48" s="51" t="inlineStr">
+      <c r="C71" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D71" s="36">
+        <f>'HOLERITE SET.26'!D22</f>
+        <v/>
+      </c>
+      <c r="E71" s="50" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="51" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B72" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C48" s="51" t="inlineStr">
+      <c r="C72" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D48" s="52">
-        <f>'HOLERITE SET.26'!C24</f>
-        <v/>
-      </c>
-      <c r="E48" s="18" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B49" s="43" t="inlineStr">
+      <c r="D72" s="52">
+        <f>'HOLERITE SET.26'!D23</f>
+        <v/>
+      </c>
+      <c r="E72" s="18" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B73" s="44" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C49" s="43" t="inlineStr">
+      <c r="C73" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D49" s="47">
-        <f>'HOLERITE SET.26'!C26</f>
-        <v/>
-      </c>
-      <c r="E49" s="50" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B50" s="43" t="inlineStr">
+      <c r="D73" s="36">
+        <f>'HOLERITE SET.26'!D25</f>
+        <v/>
+      </c>
+      <c r="E73" s="50" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B74" s="44" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C50" s="43" t="inlineStr">
+      <c r="C74" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D50" s="47">
-        <f>'HOLERITE SET.26'!C27</f>
-        <v/>
-      </c>
-      <c r="E50" s="50" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B51" s="43" t="inlineStr">
+      <c r="D74" s="36">
+        <f>'HOLERITE SET.26'!D26</f>
+        <v/>
+      </c>
+      <c r="E74" s="50" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B75" s="44" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C51" s="43" t="inlineStr">
+      <c r="C75" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D51" s="47">
-        <f>'HOLERITE SET.26'!C28</f>
-        <v/>
-      </c>
-      <c r="E51" s="50" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B52" s="43" t="inlineStr">
+      <c r="D75" s="36">
+        <f>'HOLERITE SET.26'!D27</f>
+        <v/>
+      </c>
+      <c r="E75" s="50" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B76" s="44" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C52" s="43" t="inlineStr">
+      <c r="C76" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D52" s="47">
-        <f>'HOLERITE SET.26'!C29</f>
-        <v/>
-      </c>
-      <c r="E52" s="50" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B53" s="43" t="inlineStr">
+      <c r="D76" s="36">
+        <f>'HOLERITE SET.26'!D28</f>
+        <v/>
+      </c>
+      <c r="E76" s="50" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B77" s="44" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C53" s="43" t="inlineStr">
+      <c r="C77" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D53" s="47">
-        <f>'HOLERITE SET.26'!C30</f>
-        <v/>
-      </c>
-      <c r="E53" s="50" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B54" s="43" t="inlineStr">
+      <c r="D77" s="36">
+        <f>'HOLERITE SET.26'!D29</f>
+        <v/>
+      </c>
+      <c r="E77" s="50" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B78" s="44" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C54" s="43" t="inlineStr">
+      <c r="C78" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D54" s="47">
-        <f>'HOLERITE SET.26'!C31</f>
-        <v/>
-      </c>
-      <c r="E54" s="50" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="43" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B55" s="43" t="inlineStr">
+      <c r="D78" s="36">
+        <f>'HOLERITE SET.26'!D30</f>
+        <v/>
+      </c>
+      <c r="E78" s="50" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="44" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B79" s="44" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C55" s="43" t="inlineStr">
+      <c r="C79" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D55" s="47">
-        <f>'HOLERITE SET.26'!C32</f>
-        <v/>
-      </c>
-      <c r="E55" s="50" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="51" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B56" s="51" t="inlineStr">
+      <c r="D79" s="36">
+        <f>'HOLERITE SET.26'!D31</f>
+        <v/>
+      </c>
+      <c r="E79" s="50" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="51" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B80" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C56" s="51" t="inlineStr">
+      <c r="C80" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D56" s="52">
-        <f>'HOLERITE SET.26'!C33</f>
-        <v/>
-      </c>
-      <c r="E56" s="18" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="53" t="inlineStr">
-        <is>
-          <t>ELIANA</t>
-        </is>
-      </c>
-      <c r="B57" s="54" t="inlineStr">
+      <c r="D80" s="52">
+        <f>'HOLERITE SET.26'!D32</f>
+        <v/>
+      </c>
+      <c r="E80" s="18" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="53" t="inlineStr">
+        <is>
+          <t>GENECIR</t>
+        </is>
+      </c>
+      <c r="B81" s="54" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C57" s="54" t="inlineStr">
+      <c r="C81" s="54" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D57" s="55">
-        <f>'HOLERITE SET.26'!C35</f>
-        <v/>
-      </c>
-      <c r="E57" s="56" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B59" s="43" t="inlineStr">
+      <c r="D81" s="55">
+        <f>'HOLERITE SET.26'!D34</f>
+        <v/>
+      </c>
+      <c r="E81" s="56" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B83" s="44" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C59" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D59" s="47">
-        <f>'HOLERITE SET.26'!D6</f>
-        <v/>
-      </c>
-      <c r="E59" s="50" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B60" s="43" t="inlineStr">
+      <c r="C83" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D83" s="36">
+        <f>'HOLERITE SET.26'!E6</f>
+        <v/>
+      </c>
+      <c r="E83" s="50" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B84" s="44" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C60" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D60" s="47">
-        <f>'HOLERITE SET.26'!D7</f>
-        <v/>
-      </c>
-      <c r="E60" s="50" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B61" s="43" t="inlineStr">
+      <c r="C84" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D84" s="36">
+        <f>'HOLERITE SET.26'!E7</f>
+        <v/>
+      </c>
+      <c r="E84" s="50" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B85" s="44" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C61" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D61" s="47">
-        <f>'HOLERITE SET.26'!D8</f>
-        <v/>
-      </c>
-      <c r="E61" s="50" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B62" s="43" t="inlineStr">
+      <c r="C85" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D85" s="36">
+        <f>'HOLERITE SET.26'!E8</f>
+        <v/>
+      </c>
+      <c r="E85" s="50" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B86" s="44" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C62" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D62" s="47">
-        <f>'HOLERITE SET.26'!D11</f>
-        <v/>
-      </c>
-      <c r="E62" s="50" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B63" s="43" t="inlineStr">
+      <c r="C86" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D86" s="36">
+        <f>'HOLERITE SET.26'!E11</f>
+        <v/>
+      </c>
+      <c r="E86" s="50" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B87" s="44" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C63" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D63" s="47">
-        <f>'HOLERITE SET.26'!D12</f>
-        <v/>
-      </c>
-      <c r="E63" s="50" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B64" s="43" t="inlineStr">
+      <c r="C87" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D87" s="36">
+        <f>'HOLERITE SET.26'!E12</f>
+        <v/>
+      </c>
+      <c r="E87" s="50" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B88" s="44" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C64" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D64" s="47">
-        <f>'HOLERITE SET.26'!D13</f>
-        <v/>
-      </c>
-      <c r="E64" s="50" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B65" s="43" t="inlineStr">
+      <c r="C88" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D88" s="36">
+        <f>'HOLERITE SET.26'!E13</f>
+        <v/>
+      </c>
+      <c r="E88" s="50" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B89" s="44" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C65" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D65" s="47">
-        <f>'HOLERITE SET.26'!D14</f>
-        <v/>
-      </c>
-      <c r="E65" s="50" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B66" s="43" t="inlineStr">
+      <c r="C89" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D89" s="36">
+        <f>'HOLERITE SET.26'!E14</f>
+        <v/>
+      </c>
+      <c r="E89" s="50" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B90" s="44" t="inlineStr">
         <is>
           <t>PRÊMIO META 1 — VOLUME</t>
         </is>
       </c>
-      <c r="C66" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D66" s="47">
-        <f>'HOLERITE SET.26'!D15</f>
-        <v/>
-      </c>
-      <c r="E66" s="50" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B67" s="43" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
-        </is>
-      </c>
-      <c r="C67" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D67" s="47">
-        <f>'HOLERITE SET.26'!D16</f>
-        <v/>
-      </c>
-      <c r="E67" s="50" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B68" s="43" t="inlineStr">
+      <c r="C90" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D90" s="36">
+        <f>'HOLERITE SET.26'!E15</f>
+        <v/>
+      </c>
+      <c r="E90" s="50" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B91" s="44" t="inlineStr">
         <is>
           <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="C68" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D68" s="47">
-        <f>'HOLERITE SET.26'!D17</f>
-        <v/>
-      </c>
-      <c r="E68" s="50" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B69" s="43" t="inlineStr">
+      <c r="C91" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D91" s="36">
+        <f>'HOLERITE SET.26'!E16</f>
+        <v/>
+      </c>
+      <c r="E91" s="50" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B92" s="44" t="inlineStr">
         <is>
           <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
         </is>
       </c>
-      <c r="C69" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D69" s="47">
-        <f>'HOLERITE SET.26'!D18</f>
-        <v/>
-      </c>
-      <c r="E69" s="50" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B70" s="43" t="inlineStr">
+      <c r="C92" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D92" s="36">
+        <f>'HOLERITE SET.26'!E17</f>
+        <v/>
+      </c>
+      <c r="E92" s="50" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B93" s="44" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C70" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D70" s="47">
-        <f>'HOLERITE SET.26'!D19</f>
-        <v/>
-      </c>
-      <c r="E70" s="50" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B71" s="43" t="inlineStr">
+      <c r="C93" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D93" s="36">
+        <f>'HOLERITE SET.26'!E18</f>
+        <v/>
+      </c>
+      <c r="E93" s="50" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B94" s="44" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C71" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D71" s="47">
-        <f>'HOLERITE SET.26'!D20</f>
-        <v/>
-      </c>
-      <c r="E71" s="50" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B72" s="43" t="inlineStr">
+      <c r="C94" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D94" s="36">
+        <f>'HOLERITE SET.26'!E19</f>
+        <v/>
+      </c>
+      <c r="E94" s="50" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B95" s="44" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C72" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D72" s="47">
-        <f>'HOLERITE SET.26'!D21</f>
-        <v/>
-      </c>
-      <c r="E72" s="50" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B73" s="43" t="inlineStr">
+      <c r="C95" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D95" s="36">
+        <f>'HOLERITE SET.26'!E20</f>
+        <v/>
+      </c>
+      <c r="E95" s="50" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B96" s="44" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C73" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D73" s="47">
-        <f>'HOLERITE SET.26'!D22</f>
-        <v/>
-      </c>
-      <c r="E73" s="50" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B74" s="43" t="inlineStr">
+      <c r="C96" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D96" s="36">
+        <f>'HOLERITE SET.26'!E21</f>
+        <v/>
+      </c>
+      <c r="E96" s="50" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B97" s="44" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C74" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D74" s="47">
-        <f>'HOLERITE SET.26'!D23</f>
-        <v/>
-      </c>
-      <c r="E74" s="50" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="51" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B75" s="51" t="inlineStr">
+      <c r="C97" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D97" s="36">
+        <f>'HOLERITE SET.26'!E22</f>
+        <v/>
+      </c>
+      <c r="E97" s="50" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="51" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B98" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C75" s="51" t="inlineStr">
+      <c r="C98" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D75" s="52">
-        <f>'HOLERITE SET.26'!D24</f>
-        <v/>
-      </c>
-      <c r="E75" s="18" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B76" s="43" t="inlineStr">
+      <c r="D98" s="52">
+        <f>'HOLERITE SET.26'!E23</f>
+        <v/>
+      </c>
+      <c r="E98" s="18" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B99" s="44" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C76" s="43" t="inlineStr">
+      <c r="C99" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D76" s="47">
-        <f>'HOLERITE SET.26'!D26</f>
-        <v/>
-      </c>
-      <c r="E76" s="50" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B77" s="43" t="inlineStr">
+      <c r="D99" s="36">
+        <f>'HOLERITE SET.26'!E25</f>
+        <v/>
+      </c>
+      <c r="E99" s="50" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B100" s="44" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C77" s="43" t="inlineStr">
+      <c r="C100" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D77" s="47">
-        <f>'HOLERITE SET.26'!D27</f>
-        <v/>
-      </c>
-      <c r="E77" s="50" t="n"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B78" s="43" t="inlineStr">
+      <c r="D100" s="36">
+        <f>'HOLERITE SET.26'!E26</f>
+        <v/>
+      </c>
+      <c r="E100" s="50" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B101" s="44" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C78" s="43" t="inlineStr">
+      <c r="C101" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D78" s="47">
-        <f>'HOLERITE SET.26'!D28</f>
-        <v/>
-      </c>
-      <c r="E78" s="50" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B79" s="43" t="inlineStr">
+      <c r="D101" s="36">
+        <f>'HOLERITE SET.26'!E27</f>
+        <v/>
+      </c>
+      <c r="E101" s="50" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B102" s="44" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C79" s="43" t="inlineStr">
+      <c r="C102" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D79" s="47">
-        <f>'HOLERITE SET.26'!D29</f>
-        <v/>
-      </c>
-      <c r="E79" s="50" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B80" s="43" t="inlineStr">
+      <c r="D102" s="36">
+        <f>'HOLERITE SET.26'!E28</f>
+        <v/>
+      </c>
+      <c r="E102" s="50" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B103" s="44" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C80" s="43" t="inlineStr">
+      <c r="C103" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D80" s="47">
-        <f>'HOLERITE SET.26'!D30</f>
-        <v/>
-      </c>
-      <c r="E80" s="50" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B81" s="43" t="inlineStr">
+      <c r="D103" s="36">
+        <f>'HOLERITE SET.26'!E29</f>
+        <v/>
+      </c>
+      <c r="E103" s="50" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B104" s="44" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C81" s="43" t="inlineStr">
+      <c r="C104" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D81" s="47">
-        <f>'HOLERITE SET.26'!D31</f>
-        <v/>
-      </c>
-      <c r="E81" s="50" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="43" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B82" s="43" t="inlineStr">
+      <c r="D104" s="36">
+        <f>'HOLERITE SET.26'!E30</f>
+        <v/>
+      </c>
+      <c r="E104" s="50" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="44" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B105" s="44" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C82" s="43" t="inlineStr">
+      <c r="C105" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D82" s="47">
-        <f>'HOLERITE SET.26'!D32</f>
-        <v/>
-      </c>
-      <c r="E82" s="50" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="51" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B83" s="51" t="inlineStr">
+      <c r="D105" s="36">
+        <f>'HOLERITE SET.26'!E31</f>
+        <v/>
+      </c>
+      <c r="E105" s="50" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="51" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B106" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C83" s="51" t="inlineStr">
+      <c r="C106" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D83" s="52">
-        <f>'HOLERITE SET.26'!D33</f>
-        <v/>
-      </c>
-      <c r="E83" s="18" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="53" t="inlineStr">
-        <is>
-          <t>GENECIR</t>
-        </is>
-      </c>
-      <c r="B84" s="54" t="inlineStr">
+      <c r="D106" s="52">
+        <f>'HOLERITE SET.26'!E32</f>
+        <v/>
+      </c>
+      <c r="E106" s="18" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="53" t="inlineStr">
+        <is>
+          <t>RENALDO</t>
+        </is>
+      </c>
+      <c r="B107" s="54" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C84" s="54" t="inlineStr">
+      <c r="C107" s="54" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D84" s="55">
-        <f>'HOLERITE SET.26'!D35</f>
-        <v/>
-      </c>
-      <c r="E84" s="56" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B86" s="43" t="inlineStr">
+      <c r="D107" s="55">
+        <f>'HOLERITE SET.26'!E34</f>
+        <v/>
+      </c>
+      <c r="E107" s="56" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B109" s="44" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C86" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D86" s="47">
-        <f>'HOLERITE SET.26'!E6</f>
-        <v/>
-      </c>
-      <c r="E86" s="50" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B87" s="43" t="inlineStr">
+      <c r="C109" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D109" s="36">
+        <f>'HOLERITE SET.26'!F6</f>
+        <v/>
+      </c>
+      <c r="E109" s="50" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B110" s="44" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C87" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D87" s="47">
-        <f>'HOLERITE SET.26'!E7</f>
-        <v/>
-      </c>
-      <c r="E87" s="50" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B88" s="43" t="inlineStr">
+      <c r="C110" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D110" s="36">
+        <f>'HOLERITE SET.26'!F7</f>
+        <v/>
+      </c>
+      <c r="E110" s="50" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B111" s="44" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C88" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D88" s="47">
-        <f>'HOLERITE SET.26'!E8</f>
-        <v/>
-      </c>
-      <c r="E88" s="50" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B89" s="43" t="inlineStr">
+      <c r="C111" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D111" s="36">
+        <f>'HOLERITE SET.26'!F8</f>
+        <v/>
+      </c>
+      <c r="E111" s="50" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B112" s="44" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C89" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D89" s="47">
-        <f>'HOLERITE SET.26'!E11</f>
-        <v/>
-      </c>
-      <c r="E89" s="50" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B90" s="43" t="inlineStr">
+      <c r="C112" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D112" s="36">
+        <f>'HOLERITE SET.26'!F11</f>
+        <v/>
+      </c>
+      <c r="E112" s="50" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B113" s="44" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C90" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D90" s="47">
-        <f>'HOLERITE SET.26'!E12</f>
-        <v/>
-      </c>
-      <c r="E90" s="50" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B91" s="43" t="inlineStr">
+      <c r="C113" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D113" s="36">
+        <f>'HOLERITE SET.26'!F12</f>
+        <v/>
+      </c>
+      <c r="E113" s="50" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B114" s="44" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C91" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D91" s="47">
-        <f>'HOLERITE SET.26'!E13</f>
-        <v/>
-      </c>
-      <c r="E91" s="50" t="n"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B92" s="43" t="inlineStr">
+      <c r="C114" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D114" s="36">
+        <f>'HOLERITE SET.26'!F13</f>
+        <v/>
+      </c>
+      <c r="E114" s="50" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B115" s="44" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C92" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D92" s="47">
-        <f>'HOLERITE SET.26'!E14</f>
-        <v/>
-      </c>
-      <c r="E92" s="50" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B93" s="43" t="inlineStr">
+      <c r="C115" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D115" s="36">
+        <f>'HOLERITE SET.26'!F14</f>
+        <v/>
+      </c>
+      <c r="E115" s="50" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B116" s="44" t="inlineStr">
         <is>
           <t>PRÊMIO META 1 — VOLUME</t>
         </is>
       </c>
-      <c r="C93" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D93" s="47">
-        <f>'HOLERITE SET.26'!E15</f>
-        <v/>
-      </c>
-      <c r="E93" s="50" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B94" s="43" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
-        </is>
-      </c>
-      <c r="C94" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D94" s="47">
-        <f>'HOLERITE SET.26'!E16</f>
-        <v/>
-      </c>
-      <c r="E94" s="50" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B95" s="43" t="inlineStr">
+      <c r="C116" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D116" s="36">
+        <f>'HOLERITE SET.26'!F15</f>
+        <v/>
+      </c>
+      <c r="E116" s="50" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B117" s="44" t="inlineStr">
         <is>
           <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="C95" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D95" s="47">
-        <f>'HOLERITE SET.26'!E17</f>
-        <v/>
-      </c>
-      <c r="E95" s="50" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B96" s="43" t="inlineStr">
+      <c r="C117" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D117" s="36">
+        <f>'HOLERITE SET.26'!F16</f>
+        <v/>
+      </c>
+      <c r="E117" s="50" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B118" s="44" t="inlineStr">
         <is>
           <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
         </is>
       </c>
-      <c r="C96" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D96" s="47">
-        <f>'HOLERITE SET.26'!E18</f>
-        <v/>
-      </c>
-      <c r="E96" s="50" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B97" s="43" t="inlineStr">
+      <c r="C118" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D118" s="36">
+        <f>'HOLERITE SET.26'!F17</f>
+        <v/>
+      </c>
+      <c r="E118" s="50" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B119" s="44" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C97" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D97" s="47">
-        <f>'HOLERITE SET.26'!E19</f>
-        <v/>
-      </c>
-      <c r="E97" s="50" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B98" s="43" t="inlineStr">
+      <c r="C119" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D119" s="36">
+        <f>'HOLERITE SET.26'!F18</f>
+        <v/>
+      </c>
+      <c r="E119" s="50" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B120" s="44" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C98" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D98" s="47">
-        <f>'HOLERITE SET.26'!E20</f>
-        <v/>
-      </c>
-      <c r="E98" s="50" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B99" s="43" t="inlineStr">
+      <c r="C120" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D120" s="36">
+        <f>'HOLERITE SET.26'!F19</f>
+        <v/>
+      </c>
+      <c r="E120" s="50" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B121" s="44" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C99" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D99" s="47">
-        <f>'HOLERITE SET.26'!E21</f>
-        <v/>
-      </c>
-      <c r="E99" s="50" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B100" s="43" t="inlineStr">
+      <c r="C121" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D121" s="36">
+        <f>'HOLERITE SET.26'!F20</f>
+        <v/>
+      </c>
+      <c r="E121" s="50" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B122" s="44" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C100" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D100" s="47">
-        <f>'HOLERITE SET.26'!E22</f>
-        <v/>
-      </c>
-      <c r="E100" s="50" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B101" s="43" t="inlineStr">
+      <c r="C122" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D122" s="36">
+        <f>'HOLERITE SET.26'!F21</f>
+        <v/>
+      </c>
+      <c r="E122" s="50" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B123" s="44" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C101" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D101" s="47">
-        <f>'HOLERITE SET.26'!E23</f>
-        <v/>
-      </c>
-      <c r="E101" s="50" t="n"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="51" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B102" s="51" t="inlineStr">
+      <c r="C123" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D123" s="36">
+        <f>'HOLERITE SET.26'!F22</f>
+        <v/>
+      </c>
+      <c r="E123" s="50" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="51" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B124" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C102" s="51" t="inlineStr">
+      <c r="C124" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D102" s="52">
-        <f>'HOLERITE SET.26'!E24</f>
-        <v/>
-      </c>
-      <c r="E102" s="18" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B103" s="43" t="inlineStr">
+      <c r="D124" s="52">
+        <f>'HOLERITE SET.26'!F23</f>
+        <v/>
+      </c>
+      <c r="E124" s="18" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B125" s="44" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C103" s="43" t="inlineStr">
+      <c r="C125" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D103" s="47">
-        <f>'HOLERITE SET.26'!E26</f>
-        <v/>
-      </c>
-      <c r="E103" s="50" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B104" s="43" t="inlineStr">
+      <c r="D125" s="36">
+        <f>'HOLERITE SET.26'!F25</f>
+        <v/>
+      </c>
+      <c r="E125" s="50" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B126" s="44" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C104" s="43" t="inlineStr">
+      <c r="C126" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D104" s="47">
-        <f>'HOLERITE SET.26'!E27</f>
-        <v/>
-      </c>
-      <c r="E104" s="50" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B105" s="43" t="inlineStr">
+      <c r="D126" s="36">
+        <f>'HOLERITE SET.26'!F26</f>
+        <v/>
+      </c>
+      <c r="E126" s="50" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B127" s="44" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C105" s="43" t="inlineStr">
+      <c r="C127" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D105" s="47">
-        <f>'HOLERITE SET.26'!E28</f>
-        <v/>
-      </c>
-      <c r="E105" s="50" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B106" s="43" t="inlineStr">
+      <c r="D127" s="36">
+        <f>'HOLERITE SET.26'!F27</f>
+        <v/>
+      </c>
+      <c r="E127" s="50" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B128" s="44" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C106" s="43" t="inlineStr">
+      <c r="C128" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D106" s="47">
-        <f>'HOLERITE SET.26'!E29</f>
-        <v/>
-      </c>
-      <c r="E106" s="50" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B107" s="43" t="inlineStr">
+      <c r="D128" s="36">
+        <f>'HOLERITE SET.26'!F28</f>
+        <v/>
+      </c>
+      <c r="E128" s="50" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B129" s="44" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C107" s="43" t="inlineStr">
+      <c r="C129" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D107" s="47">
-        <f>'HOLERITE SET.26'!E30</f>
-        <v/>
-      </c>
-      <c r="E107" s="50" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B108" s="43" t="inlineStr">
+      <c r="D129" s="36">
+        <f>'HOLERITE SET.26'!F29</f>
+        <v/>
+      </c>
+      <c r="E129" s="50" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B130" s="44" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C108" s="43" t="inlineStr">
+      <c r="C130" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D108" s="47">
-        <f>'HOLERITE SET.26'!E31</f>
-        <v/>
-      </c>
-      <c r="E108" s="50" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="43" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B109" s="43" t="inlineStr">
+      <c r="D130" s="36">
+        <f>'HOLERITE SET.26'!F30</f>
+        <v/>
+      </c>
+      <c r="E130" s="50" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="44" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B131" s="44" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C109" s="43" t="inlineStr">
+      <c r="C131" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D109" s="47">
-        <f>'HOLERITE SET.26'!E32</f>
-        <v/>
-      </c>
-      <c r="E109" s="50" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="51" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B110" s="51" t="inlineStr">
+      <c r="D131" s="36">
+        <f>'HOLERITE SET.26'!F31</f>
+        <v/>
+      </c>
+      <c r="E131" s="50" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="51" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B132" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C110" s="51" t="inlineStr">
+      <c r="C132" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D110" s="52">
-        <f>'HOLERITE SET.26'!E33</f>
-        <v/>
-      </c>
-      <c r="E110" s="18" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="53" t="inlineStr">
-        <is>
-          <t>RENALDO</t>
-        </is>
-      </c>
-      <c r="B111" s="54" t="inlineStr">
+      <c r="D132" s="52">
+        <f>'HOLERITE SET.26'!F32</f>
+        <v/>
+      </c>
+      <c r="E132" s="18" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="53" t="inlineStr">
+        <is>
+          <t>THAYANE</t>
+        </is>
+      </c>
+      <c r="B133" s="54" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C111" s="54" t="inlineStr">
+      <c r="C133" s="54" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D111" s="55">
-        <f>'HOLERITE SET.26'!E35</f>
-        <v/>
-      </c>
-      <c r="E111" s="56" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B113" s="43" t="inlineStr">
+      <c r="D133" s="55">
+        <f>'HOLERITE SET.26'!F34</f>
+        <v/>
+      </c>
+      <c r="E133" s="56" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B135" s="44" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C113" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D113" s="47">
-        <f>'HOLERITE SET.26'!F6</f>
-        <v/>
-      </c>
-      <c r="E113" s="50" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B114" s="43" t="inlineStr">
+      <c r="C135" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D135" s="36">
+        <f>'HOLERITE SET.26'!G6</f>
+        <v/>
+      </c>
+      <c r="E135" s="50" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B136" s="44" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C114" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D114" s="47">
-        <f>'HOLERITE SET.26'!F7</f>
-        <v/>
-      </c>
-      <c r="E114" s="50" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B115" s="43" t="inlineStr">
+      <c r="C136" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D136" s="36">
+        <f>'HOLERITE SET.26'!G7</f>
+        <v/>
+      </c>
+      <c r="E136" s="50" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B137" s="44" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C115" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D115" s="47">
-        <f>'HOLERITE SET.26'!F8</f>
-        <v/>
-      </c>
-      <c r="E115" s="50" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B116" s="43" t="inlineStr">
+      <c r="C137" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D137" s="36">
+        <f>'HOLERITE SET.26'!G8</f>
+        <v/>
+      </c>
+      <c r="E137" s="50" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B138" s="44" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C116" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D116" s="47">
-        <f>'HOLERITE SET.26'!F11</f>
-        <v/>
-      </c>
-      <c r="E116" s="50" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B117" s="43" t="inlineStr">
+      <c r="C138" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D138" s="36">
+        <f>'HOLERITE SET.26'!G11</f>
+        <v/>
+      </c>
+      <c r="E138" s="50" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B139" s="44" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C117" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D117" s="47">
-        <f>'HOLERITE SET.26'!F12</f>
-        <v/>
-      </c>
-      <c r="E117" s="50" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B118" s="43" t="inlineStr">
+      <c r="C139" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D139" s="36">
+        <f>'HOLERITE SET.26'!G12</f>
+        <v/>
+      </c>
+      <c r="E139" s="50" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B140" s="44" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C118" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D118" s="47">
-        <f>'HOLERITE SET.26'!F13</f>
-        <v/>
-      </c>
-      <c r="E118" s="50" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B119" s="43" t="inlineStr">
+      <c r="C140" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D140" s="36">
+        <f>'HOLERITE SET.26'!G13</f>
+        <v/>
+      </c>
+      <c r="E140" s="50" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B141" s="44" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C119" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D119" s="47">
-        <f>'HOLERITE SET.26'!F14</f>
-        <v/>
-      </c>
-      <c r="E119" s="50" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B120" s="43" t="inlineStr">
+      <c r="C141" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D141" s="36">
+        <f>'HOLERITE SET.26'!G14</f>
+        <v/>
+      </c>
+      <c r="E141" s="50" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B142" s="44" t="inlineStr">
         <is>
           <t>PRÊMIO META 1 — VOLUME</t>
         </is>
       </c>
-      <c r="C120" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D120" s="47">
-        <f>'HOLERITE SET.26'!F15</f>
-        <v/>
-      </c>
-      <c r="E120" s="50" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B121" s="43" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
-        </is>
-      </c>
-      <c r="C121" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D121" s="47">
-        <f>'HOLERITE SET.26'!F16</f>
-        <v/>
-      </c>
-      <c r="E121" s="50" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B122" s="43" t="inlineStr">
+      <c r="C142" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D142" s="36">
+        <f>'HOLERITE SET.26'!G15</f>
+        <v/>
+      </c>
+      <c r="E142" s="50" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B143" s="44" t="inlineStr">
         <is>
           <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="C122" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D122" s="47">
-        <f>'HOLERITE SET.26'!F17</f>
-        <v/>
-      </c>
-      <c r="E122" s="50" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B123" s="43" t="inlineStr">
+      <c r="C143" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D143" s="36">
+        <f>'HOLERITE SET.26'!G16</f>
+        <v/>
+      </c>
+      <c r="E143" s="50" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B144" s="44" t="inlineStr">
         <is>
           <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
         </is>
       </c>
-      <c r="C123" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D123" s="47">
-        <f>'HOLERITE SET.26'!F18</f>
-        <v/>
-      </c>
-      <c r="E123" s="50" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B124" s="43" t="inlineStr">
+      <c r="C144" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D144" s="36">
+        <f>'HOLERITE SET.26'!G17</f>
+        <v/>
+      </c>
+      <c r="E144" s="50" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B145" s="44" t="inlineStr">
         <is>
           <t>FÉRIAS</t>
         </is>
       </c>
-      <c r="C124" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D124" s="47">
-        <f>'HOLERITE SET.26'!F19</f>
-        <v/>
-      </c>
-      <c r="E124" s="50" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B125" s="43" t="inlineStr">
+      <c r="C145" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D145" s="36">
+        <f>'HOLERITE SET.26'!G18</f>
+        <v/>
+      </c>
+      <c r="E145" s="50" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B146" s="44" t="inlineStr">
         <is>
           <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
         </is>
       </c>
-      <c r="C125" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D125" s="47">
-        <f>'HOLERITE SET.26'!F20</f>
-        <v/>
-      </c>
-      <c r="E125" s="50" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B126" s="43" t="inlineStr">
+      <c r="C146" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D146" s="36">
+        <f>'HOLERITE SET.26'!G19</f>
+        <v/>
+      </c>
+      <c r="E146" s="50" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B147" s="44" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C126" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D126" s="47">
-        <f>'HOLERITE SET.26'!F21</f>
-        <v/>
-      </c>
-      <c r="E126" s="50" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B127" s="43" t="inlineStr">
+      <c r="C147" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D147" s="36">
+        <f>'HOLERITE SET.26'!G20</f>
+        <v/>
+      </c>
+      <c r="E147" s="50" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B148" s="44" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C127" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D127" s="47">
-        <f>'HOLERITE SET.26'!F22</f>
-        <v/>
-      </c>
-      <c r="E127" s="50" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B128" s="43" t="inlineStr">
+      <c r="C148" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D148" s="36">
+        <f>'HOLERITE SET.26'!G21</f>
+        <v/>
+      </c>
+      <c r="E148" s="50" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B149" s="44" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C128" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D128" s="47">
-        <f>'HOLERITE SET.26'!F23</f>
-        <v/>
-      </c>
-      <c r="E128" s="50" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="51" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B129" s="51" t="inlineStr">
+      <c r="C149" s="44" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D149" s="36">
+        <f>'HOLERITE SET.26'!G22</f>
+        <v/>
+      </c>
+      <c r="E149" s="50" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="51" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B150" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C129" s="51" t="inlineStr">
+      <c r="C150" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D129" s="52">
-        <f>'HOLERITE SET.26'!F24</f>
-        <v/>
-      </c>
-      <c r="E129" s="18" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B130" s="43" t="inlineStr">
+      <c r="D150" s="52">
+        <f>'HOLERITE SET.26'!G23</f>
+        <v/>
+      </c>
+      <c r="E150" s="18" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B151" s="44" t="inlineStr">
         <is>
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="C130" s="43" t="inlineStr">
+      <c r="C151" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D130" s="47">
-        <f>'HOLERITE SET.26'!F26</f>
-        <v/>
-      </c>
-      <c r="E130" s="50" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B131" s="43" t="inlineStr">
+      <c r="D151" s="36">
+        <f>'HOLERITE SET.26'!G25</f>
+        <v/>
+      </c>
+      <c r="E151" s="50" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B152" s="44" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C131" s="43" t="inlineStr">
+      <c r="C152" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D131" s="47">
-        <f>'HOLERITE SET.26'!F27</f>
-        <v/>
-      </c>
-      <c r="E131" s="50" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B132" s="43" t="inlineStr">
+      <c r="D152" s="36">
+        <f>'HOLERITE SET.26'!G26</f>
+        <v/>
+      </c>
+      <c r="E152" s="50" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B153" s="44" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C132" s="43" t="inlineStr">
+      <c r="C153" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D132" s="47">
-        <f>'HOLERITE SET.26'!F28</f>
-        <v/>
-      </c>
-      <c r="E132" s="50" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B133" s="43" t="inlineStr">
+      <c r="D153" s="36">
+        <f>'HOLERITE SET.26'!G27</f>
+        <v/>
+      </c>
+      <c r="E153" s="50" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B154" s="44" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C133" s="43" t="inlineStr">
+      <c r="C154" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D133" s="47">
-        <f>'HOLERITE SET.26'!F29</f>
-        <v/>
-      </c>
-      <c r="E133" s="50" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B134" s="43" t="inlineStr">
+      <c r="D154" s="36">
+        <f>'HOLERITE SET.26'!G28</f>
+        <v/>
+      </c>
+      <c r="E154" s="50" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B155" s="44" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C134" s="43" t="inlineStr">
+      <c r="C155" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D134" s="47">
-        <f>'HOLERITE SET.26'!F30</f>
-        <v/>
-      </c>
-      <c r="E134" s="50" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B135" s="43" t="inlineStr">
+      <c r="D155" s="36">
+        <f>'HOLERITE SET.26'!G29</f>
+        <v/>
+      </c>
+      <c r="E155" s="50" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B156" s="44" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C135" s="43" t="inlineStr">
+      <c r="C156" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D135" s="47">
-        <f>'HOLERITE SET.26'!F31</f>
-        <v/>
-      </c>
-      <c r="E135" s="50" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="43" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B136" s="43" t="inlineStr">
+      <c r="D156" s="36">
+        <f>'HOLERITE SET.26'!G30</f>
+        <v/>
+      </c>
+      <c r="E156" s="50" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="44" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B157" s="44" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C136" s="43" t="inlineStr">
+      <c r="C157" s="44" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D136" s="47">
-        <f>'HOLERITE SET.26'!F32</f>
-        <v/>
-      </c>
-      <c r="E136" s="50" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="51" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B137" s="51" t="inlineStr">
+      <c r="D157" s="36">
+        <f>'HOLERITE SET.26'!G31</f>
+        <v/>
+      </c>
+      <c r="E157" s="50" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="51" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B158" s="51" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C137" s="51" t="inlineStr">
+      <c r="C158" s="51" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D137" s="52">
-        <f>'HOLERITE SET.26'!F33</f>
-        <v/>
-      </c>
-      <c r="E137" s="18" t="n"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="53" t="inlineStr">
-        <is>
-          <t>THAYANE</t>
-        </is>
-      </c>
-      <c r="B138" s="54" t="inlineStr">
+      <c r="D158" s="52">
+        <f>'HOLERITE SET.26'!G32</f>
+        <v/>
+      </c>
+      <c r="E158" s="18" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="53" t="inlineStr">
+        <is>
+          <t>PEDRO</t>
+        </is>
+      </c>
+      <c r="B159" s="54" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C138" s="54" t="inlineStr">
+      <c r="C159" s="54" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D138" s="55">
-        <f>'HOLERITE SET.26'!F35</f>
-        <v/>
-      </c>
-      <c r="E138" s="56" t="n"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B140" s="43" t="inlineStr">
-        <is>
-          <t>SALÁRIO BASE</t>
-        </is>
-      </c>
-      <c r="C140" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D140" s="47">
-        <f>'HOLERITE SET.26'!G6</f>
-        <v/>
-      </c>
-      <c r="E140" s="50" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B141" s="43" t="inlineStr">
-        <is>
-          <t>ADICIONAL NOTURNO</t>
-        </is>
-      </c>
-      <c r="C141" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D141" s="47">
-        <f>'HOLERITE SET.26'!G7</f>
-        <v/>
-      </c>
-      <c r="E141" s="50" t="n"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B142" s="43" t="inlineStr">
-        <is>
-          <t>HORAS EXTRAS</t>
-        </is>
-      </c>
-      <c r="C142" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D142" s="47">
-        <f>'HOLERITE SET.26'!G8</f>
-        <v/>
-      </c>
-      <c r="E142" s="50" t="n"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B143" s="43" t="inlineStr">
-        <is>
-          <t>COMISSÃO SOBRE VENDAS</t>
-        </is>
-      </c>
-      <c r="C143" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D143" s="47">
-        <f>'HOLERITE SET.26'!G11</f>
-        <v/>
-      </c>
-      <c r="E143" s="50" t="n"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B144" s="43" t="inlineStr">
-        <is>
-          <t>REPOUSO REMUNERADO / DSR</t>
-        </is>
-      </c>
-      <c r="C144" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D144" s="47">
-        <f>'HOLERITE SET.26'!G12</f>
-        <v/>
-      </c>
-      <c r="E144" s="50" t="n"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B145" s="43" t="inlineStr">
-        <is>
-          <t>AUXÍLIO GERÊNCIA</t>
-        </is>
-      </c>
-      <c r="C145" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D145" s="47">
-        <f>'HOLERITE SET.26'!G13</f>
-        <v/>
-      </c>
-      <c r="E145" s="50" t="n"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B146" s="43" t="inlineStr">
-        <is>
-          <t>ADICIONAL PRÊMIO META CAIXA</t>
-        </is>
-      </c>
-      <c r="C146" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D146" s="47">
-        <f>'HOLERITE SET.26'!G14</f>
-        <v/>
-      </c>
-      <c r="E146" s="50" t="n"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B147" s="43" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 1 — VOLUME</t>
-        </is>
-      </c>
-      <c r="C147" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D147" s="47">
-        <f>'HOLERITE SET.26'!G15</f>
-        <v/>
-      </c>
-      <c r="E147" s="50" t="n"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B148" s="43" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 2 — PRODUTOS FOCO</t>
-        </is>
-      </c>
-      <c r="C148" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D148" s="47">
-        <f>'HOLERITE SET.26'!G16</f>
-        <v/>
-      </c>
-      <c r="E148" s="50" t="n"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B149" s="43" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 3 — PRÉ-VENCIDOS</t>
-        </is>
-      </c>
-      <c r="C149" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D149" s="47">
-        <f>'HOLERITE SET.26'!G17</f>
-        <v/>
-      </c>
-      <c r="E149" s="50" t="n"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B150" s="43" t="inlineStr">
-        <is>
-          <t>PRÊMIO META 4 — PERFUMARIA 130%</t>
-        </is>
-      </c>
-      <c r="C150" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D150" s="47">
-        <f>'HOLERITE SET.26'!G18</f>
-        <v/>
-      </c>
-      <c r="E150" s="50" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B151" s="43" t="inlineStr">
-        <is>
-          <t>FÉRIAS</t>
-        </is>
-      </c>
-      <c r="C151" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D151" s="47">
-        <f>'HOLERITE SET.26'!G19</f>
-        <v/>
-      </c>
-      <c r="E151" s="50" t="n"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B152" s="43" t="inlineStr">
-        <is>
-          <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
-        </is>
-      </c>
-      <c r="C152" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D152" s="47">
-        <f>'HOLERITE SET.26'!G20</f>
-        <v/>
-      </c>
-      <c r="E152" s="50" t="n"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B153" s="43" t="inlineStr">
-        <is>
-          <t>INCENTIVO APLICAÇÕES</t>
-        </is>
-      </c>
-      <c r="C153" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D153" s="47">
-        <f>'HOLERITE SET.26'!G21</f>
-        <v/>
-      </c>
-      <c r="E153" s="50" t="n"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B154" s="43" t="inlineStr">
-        <is>
-          <t>INCENTIVO VITAMINAS</t>
-        </is>
-      </c>
-      <c r="C154" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D154" s="47">
-        <f>'HOLERITE SET.26'!G22</f>
-        <v/>
-      </c>
-      <c r="E154" s="50" t="n"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B155" s="43" t="inlineStr">
-        <is>
-          <t>OUTROS INCENTIVOS</t>
-        </is>
-      </c>
-      <c r="C155" s="43" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D155" s="47">
-        <f>'HOLERITE SET.26'!G23</f>
-        <v/>
-      </c>
-      <c r="E155" s="50" t="n"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="51" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B156" s="51" t="inlineStr">
-        <is>
-          <t>TOTAL DE PROVENTOS</t>
-        </is>
-      </c>
-      <c r="C156" s="51" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="D156" s="52">
-        <f>'HOLERITE SET.26'!G24</f>
-        <v/>
-      </c>
-      <c r="E156" s="18" t="n"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B157" s="43" t="inlineStr">
-        <is>
-          <t>ADIANTAMENTO SALARIAL / VALES</t>
-        </is>
-      </c>
-      <c r="C157" s="43" t="inlineStr">
-        <is>
-          <t>Desconto</t>
-        </is>
-      </c>
-      <c r="D157" s="47">
-        <f>'HOLERITE SET.26'!G26</f>
-        <v/>
-      </c>
-      <c r="E157" s="50" t="n"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B158" s="43" t="inlineStr">
-        <is>
-          <t>ADIANT. VALES INCENT. E APLIC.</t>
-        </is>
-      </c>
-      <c r="C158" s="43" t="inlineStr">
-        <is>
-          <t>Desconto</t>
-        </is>
-      </c>
-      <c r="D158" s="47">
-        <f>'HOLERITE SET.26'!G27</f>
-        <v/>
-      </c>
-      <c r="E158" s="50" t="n"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B159" s="43" t="inlineStr">
-        <is>
-          <t>CONVÊNIO</t>
-        </is>
-      </c>
-      <c r="C159" s="43" t="inlineStr">
-        <is>
-          <t>Desconto</t>
-        </is>
-      </c>
-      <c r="D159" s="47">
-        <f>'HOLERITE SET.26'!G28</f>
-        <v/>
-      </c>
-      <c r="E159" s="50" t="n"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B160" s="43" t="inlineStr">
-        <is>
-          <t>DESCONTO FALTAS / ATRASOS</t>
-        </is>
-      </c>
-      <c r="C160" s="43" t="inlineStr">
-        <is>
-          <t>Desconto</t>
-        </is>
-      </c>
-      <c r="D160" s="47">
-        <f>'HOLERITE SET.26'!G29</f>
-        <v/>
-      </c>
-      <c r="E160" s="50" t="n"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B161" s="43" t="inlineStr">
-        <is>
-          <t>DESCONTO VALE TRANSPORTE 6%</t>
-        </is>
-      </c>
-      <c r="C161" s="43" t="inlineStr">
-        <is>
-          <t>Desconto</t>
-        </is>
-      </c>
-      <c r="D161" s="47">
-        <f>'HOLERITE SET.26'!G30</f>
-        <v/>
-      </c>
-      <c r="E161" s="50" t="n"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B162" s="43" t="inlineStr">
-        <is>
-          <t>DESCONTO INSS</t>
-        </is>
-      </c>
-      <c r="C162" s="43" t="inlineStr">
-        <is>
-          <t>Desconto</t>
-        </is>
-      </c>
-      <c r="D162" s="47">
-        <f>'HOLERITE SET.26'!G31</f>
-        <v/>
-      </c>
-      <c r="E162" s="50" t="n"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="43" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B163" s="43" t="inlineStr">
-        <is>
-          <t>DESCONTO IRRF</t>
-        </is>
-      </c>
-      <c r="C163" s="43" t="inlineStr">
-        <is>
-          <t>Desconto</t>
-        </is>
-      </c>
-      <c r="D163" s="47">
-        <f>'HOLERITE SET.26'!G32</f>
-        <v/>
-      </c>
-      <c r="E163" s="50" t="n"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="51" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B164" s="51" t="inlineStr">
-        <is>
-          <t>TOTAL DE DESCONTOS</t>
-        </is>
-      </c>
-      <c r="C164" s="51" t="inlineStr">
-        <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="D164" s="52">
-        <f>'HOLERITE SET.26'!G33</f>
-        <v/>
-      </c>
-      <c r="E164" s="18" t="n"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="53" t="inlineStr">
-        <is>
-          <t>PEDRO</t>
-        </is>
-      </c>
-      <c r="B165" s="54" t="inlineStr">
-        <is>
-          <t>LÍQUIDO A RECEBER</t>
-        </is>
-      </c>
-      <c r="C165" s="54" t="inlineStr">
-        <is>
-          <t>Líquido</t>
-        </is>
-      </c>
-      <c r="D165" s="55">
-        <f>'HOLERITE SET.26'!G35</f>
-        <v/>
-      </c>
-      <c r="E165" s="56" t="n"/>
+      <c r="D159" s="55">
+        <f>'HOLERITE SET.26'!G34</f>
+        <v/>
+      </c>
+      <c r="E159" s="56" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:E165"/>
+  <autoFilter ref="A4:E159"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
@@ -7308,7 +7154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -7354,391 +7200,380 @@
           <t>PROVENTOS</t>
         </is>
       </c>
-      <c r="C6" s="42" t="n"/>
-      <c r="D6" s="42" t="n"/>
+      <c r="C6" s="43" t="n"/>
+      <c r="D6" s="43" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>Salário base</t>
         </is>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="43" t="inlineStr">
+      <c r="B8" s="44" t="inlineStr">
         <is>
           <t>Adicional noturno</t>
         </is>
       </c>
-      <c r="C8" s="47">
+      <c r="C8" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$7:$G$7,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="43" t="inlineStr">
+      <c r="B9" s="44" t="inlineStr">
         <is>
           <t>Horas extras</t>
         </is>
       </c>
-      <c r="C9" s="47">
+      <c r="C9" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$8:$G$8,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="43" t="inlineStr">
+      <c r="B10" s="44" t="inlineStr">
         <is>
           <t>Comissão sobre vendas</t>
         </is>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$11:$G$11,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="43" t="inlineStr">
+      <c r="B11" s="44" t="inlineStr">
         <is>
           <t>Repouso remunerado / DSR</t>
         </is>
       </c>
-      <c r="C11" s="47">
+      <c r="C11" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$12:$G$12,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="43" t="inlineStr">
+      <c r="B12" s="44" t="inlineStr">
         <is>
           <t>Auxílio gerência</t>
         </is>
       </c>
-      <c r="C12" s="47">
+      <c r="C12" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$13:$G$13,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="43" t="inlineStr">
+      <c r="B13" s="44" t="inlineStr">
         <is>
           <t>Adicional prêmio meta caixa</t>
         </is>
       </c>
-      <c r="C13" s="47">
+      <c r="C13" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$14:$G$14,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="43" t="inlineStr">
+      <c r="B14" s="44" t="inlineStr">
         <is>
           <t>Prêmio meta 1 — volume</t>
         </is>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$15:$G$15,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="43" t="inlineStr">
-        <is>
-          <t>Prêmio meta 2 — produtos foco</t>
-        </is>
-      </c>
-      <c r="C15" s="47">
+      <c r="B15" s="44" t="inlineStr">
+        <is>
+          <t>Prêmio meta 3 — pré-vencidos</t>
+        </is>
+      </c>
+      <c r="C15" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$16:$G$16,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="43" t="inlineStr">
-        <is>
-          <t>Prêmio meta 3 — pré-vencidos</t>
-        </is>
-      </c>
-      <c r="C16" s="47">
+      <c r="B16" s="44" t="inlineStr">
+        <is>
+          <t>Prêmio meta 4 — perfumaria</t>
+        </is>
+      </c>
+      <c r="C16" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$17:$G$17,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="43" t="inlineStr">
-        <is>
-          <t>Prêmio meta 4 — perfumaria</t>
-        </is>
-      </c>
-      <c r="C17" s="47">
+      <c r="B17" s="44" t="inlineStr">
+        <is>
+          <t>Férias</t>
+        </is>
+      </c>
+      <c r="C17" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$18:$G$18,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="43" t="inlineStr">
-        <is>
-          <t>Férias</t>
-        </is>
-      </c>
-      <c r="C18" s="47">
+      <c r="B18" s="44" t="inlineStr">
+        <is>
+          <t>1/3 constitucional de férias</t>
+        </is>
+      </c>
+      <c r="C18" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$19:$G$19,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="43" t="inlineStr">
-        <is>
-          <t>1/3 constitucional de férias</t>
-        </is>
-      </c>
-      <c r="C19" s="47">
+      <c r="B19" s="44" t="inlineStr">
+        <is>
+          <t>Incentivo aplicações</t>
+        </is>
+      </c>
+      <c r="C19" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$20:$G$20,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="43" t="inlineStr">
-        <is>
-          <t>Incentivo aplicações</t>
-        </is>
-      </c>
-      <c r="C20" s="47">
+      <c r="B20" s="44" t="inlineStr">
+        <is>
+          <t>Incentivo vitaminas</t>
+        </is>
+      </c>
+      <c r="C20" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$21:$G$21,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="43" t="inlineStr">
-        <is>
-          <t>Incentivo vitaminas</t>
-        </is>
-      </c>
-      <c r="C21" s="47">
+      <c r="B21" s="44" t="inlineStr">
+        <is>
+          <t>Outros incentivos</t>
+        </is>
+      </c>
+      <c r="C21" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$22:$G$22,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="43" t="inlineStr">
-        <is>
-          <t>Outros incentivos</t>
-        </is>
-      </c>
-      <c r="C22" s="47">
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL DE PROVENTOS</t>
+        </is>
+      </c>
+      <c r="C22" s="52">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$23:$G$23,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL DE PROVENTOS</t>
-        </is>
-      </c>
-      <c r="C23" s="52">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$24:$G$24,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" ht="19" customHeight="1">
-      <c r="B24" s="3" t="inlineStr">
+    <row r="23" ht="19" customHeight="1">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>DESCONTOS</t>
         </is>
       </c>
-      <c r="C24" s="42" t="n"/>
-      <c r="D24" s="42" t="n"/>
+      <c r="C23" s="43" t="n"/>
+      <c r="D23" s="43" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="44" t="inlineStr">
+        <is>
+          <t>Adiantamento salarial / vales</t>
+        </is>
+      </c>
+      <c r="C24" s="36">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$25:$G$25,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="B25" s="43" t="inlineStr">
-        <is>
-          <t>Adiantamento salarial / vales</t>
-        </is>
-      </c>
-      <c r="C25" s="47">
+      <c r="B25" s="44" t="inlineStr">
+        <is>
+          <t>Adiantamento de incentivos e aplicações</t>
+        </is>
+      </c>
+      <c r="C25" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$26:$G$26,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="43" t="inlineStr">
-        <is>
-          <t>Adiantamento de incentivos e aplicações</t>
-        </is>
-      </c>
-      <c r="C26" s="47">
+      <c r="B26" s="44" t="inlineStr">
+        <is>
+          <t>Convênio</t>
+        </is>
+      </c>
+      <c r="C26" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$27:$G$27,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="43" t="inlineStr">
-        <is>
-          <t>Convênio</t>
-        </is>
-      </c>
-      <c r="C27" s="47">
+      <c r="B27" s="44" t="inlineStr">
+        <is>
+          <t>Faltas / atrasos</t>
+        </is>
+      </c>
+      <c r="C27" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$28:$G$28,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="43" t="inlineStr">
-        <is>
-          <t>Faltas / atrasos</t>
-        </is>
-      </c>
-      <c r="C28" s="47">
+      <c r="B28" s="44" t="inlineStr">
+        <is>
+          <t>Vale transporte 6%</t>
+        </is>
+      </c>
+      <c r="C28" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$29:$G$29,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="43" t="inlineStr">
-        <is>
-          <t>Vale transporte 6%</t>
-        </is>
-      </c>
-      <c r="C29" s="47">
+      <c r="B29" s="44" t="inlineStr">
+        <is>
+          <t>INSS</t>
+        </is>
+      </c>
+      <c r="C29" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$30:$G$30,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="43" t="inlineStr">
-        <is>
-          <t>INSS</t>
-        </is>
-      </c>
-      <c r="C30" s="47">
+      <c r="B30" s="44" t="inlineStr">
+        <is>
+          <t>IRRF</t>
+        </is>
+      </c>
+      <c r="C30" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$31:$G$31,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="43" t="inlineStr">
-        <is>
-          <t>IRRF</t>
-        </is>
-      </c>
-      <c r="C31" s="47">
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL DE DESCONTOS</t>
+        </is>
+      </c>
+      <c r="C31" s="52">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$32:$G$32,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>TOTAL DE DESCONTOS</t>
-        </is>
-      </c>
-      <c r="C32" s="52">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$33:$G$33,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="B33" s="3" t="inlineStr">
+    <row r="32" ht="19" customHeight="1">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>LÍQUIDO</t>
         </is>
       </c>
-      <c r="C33" s="42" t="n"/>
-      <c r="D33" s="42" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="B34" s="59" t="inlineStr">
+      <c r="C32" s="43" t="n"/>
+      <c r="D32" s="43" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="B33" s="59" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER EM 05/10/2026</t>
         </is>
       </c>
-      <c r="C34" s="60">
-        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$35:$G$35,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
-        <v/>
+      <c r="C33" s="60">
+        <f>IFERROR(INDEX('HOLERITE SET.26'!$B$34:$G$34,1,MATCH($C$4,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="27" t="inlineStr">
+        <is>
+          <t>Vendas do colaborador no mês (InovaFarma):</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="27" t="inlineStr">
-        <is>
-          <t>Vendas do colaborador no mês (InovaFarma):</t>
-        </is>
+      <c r="B36" s="44" t="inlineStr">
+        <is>
+          <t>Venda bruta</t>
+        </is>
+      </c>
+      <c r="C36" s="36">
+        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$C$5:$C$10,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
+        <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="43" t="inlineStr">
-        <is>
-          <t>Venda bruta</t>
-        </is>
-      </c>
-      <c r="C37" s="47">
-        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$C$5:$C$10,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
+      <c r="B37" s="44" t="inlineStr">
+        <is>
+          <t>Descontos concedidos</t>
+        </is>
+      </c>
+      <c r="C37" s="36">
+        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$D$5:$D$10,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="43" t="inlineStr">
-        <is>
-          <t>Descontos concedidos</t>
-        </is>
-      </c>
-      <c r="C38" s="47">
-        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$D$5:$D$10,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
+      <c r="B38" s="44" t="inlineStr">
+        <is>
+          <t>Venda líquida</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$E$5:$E$10,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="43" t="inlineStr">
-        <is>
-          <t>Venda líquida</t>
-        </is>
-      </c>
-      <c r="C39" s="47">
-        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$E$5:$E$10,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
+      <c r="B39" s="44" t="inlineStr">
+        <is>
+          <t>Comissão apurada</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$F$5:$F$10,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="43" t="inlineStr">
-        <is>
-          <t>Comissão apurada</t>
-        </is>
-      </c>
-      <c r="C40" s="47">
-        <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$F$5:$F$10,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="43" t="inlineStr">
+      <c r="B40" s="44" t="inlineStr">
         <is>
           <t>Total de incentivos</t>
         </is>
       </c>
-      <c r="C41" s="47">
+      <c r="C40" s="36">
         <f>IFERROR(INDEX('BASE INOVAFARMA SET.26'!$J$5:$J$10,MATCH($C$4,'BASE INOVAFARMA SET.26'!$B$5:$B$10,0)),0)</f>
         <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>A comissão apurada acima é a do sistema. O que entra na folha é a linha "Comissão sobre vendas".</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>A comissão apurada acima é a do sistema. O que entra na folha é a linha "Comissão sobre vendas".</t>
+          <t>Os valores de INSS e IRRF são calculados pela contabilidade e só aparecem depois de preenchidos na aba HOLERITE SET.26.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="22" t="inlineStr">
-        <is>
-          <t>Os valores de INSS e IRRF são calculados pela contabilidade e só aparecem depois de preenchidos na aba HOLERITE SET.26.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="22" t="inlineStr">
         <is>
           <t>Para mandar para o colaborador: selecione o nome acima e imprima esta aba em PDF (ou tire um print).</t>
         </is>
@@ -7846,7 +7681,7 @@
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>Registro informativo</t>
         </is>
@@ -7859,7 +7694,7 @@
           <t>dias</t>
         </is>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A5,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
@@ -7875,7 +7710,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="46" t="inlineStr">
+      <c r="I5" s="47" t="inlineStr">
         <is>
           <t>Voltou das férias (01 a 30/08/2026) — salário integral em setembro.</t>
         </is>
@@ -7887,7 +7722,7 @@
           <t>GENECIR</t>
         </is>
       </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>Feriado trabalhado (dobra)</t>
         </is>
@@ -7900,7 +7735,7 @@
           <t>dias</t>
         </is>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A6,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
@@ -7917,7 +7752,7 @@
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="I6" s="46" t="inlineStr">
+      <c r="I6" s="47" t="inlineStr">
         <is>
           <t>Feriados de 07/09 e 08/09/2026 trabalhados, sem folga compensatória — 1 salário-dia a mais por feriado.</t>
         </is>
@@ -7929,7 +7764,7 @@
           <t>RENALDO</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="44" t="inlineStr">
         <is>
           <t>Registro informativo</t>
         </is>
@@ -7942,7 +7777,7 @@
           <t>dias</t>
         </is>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A7,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
@@ -7958,7 +7793,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I7" s="46" t="inlineStr">
+      <c r="I7" s="47" t="inlineStr">
         <is>
           <t>Férias de 01 a 30/09/2026 — mês inteiro. Salário zerado no holerite; férias e 1/3 vão em recibo próprio.</t>
         </is>
@@ -7969,7 +7804,7 @@
       <c r="B8" s="30" t="n"/>
       <c r="C8" s="30" t="n"/>
       <c r="D8" s="30" t="n"/>
-      <c r="E8" s="47">
+      <c r="E8" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A8,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
@@ -7986,7 +7821,7 @@
       <c r="B9" s="30" t="n"/>
       <c r="C9" s="30" t="n"/>
       <c r="D9" s="30" t="n"/>
-      <c r="E9" s="47">
+      <c r="E9" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A9,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
@@ -8003,7 +7838,7 @@
       <c r="B10" s="30" t="n"/>
       <c r="C10" s="30" t="n"/>
       <c r="D10" s="30" t="n"/>
-      <c r="E10" s="47">
+      <c r="E10" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A10,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
@@ -8020,7 +7855,7 @@
       <c r="B11" s="30" t="n"/>
       <c r="C11" s="30" t="n"/>
       <c r="D11" s="30" t="n"/>
-      <c r="E11" s="47">
+      <c r="E11" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A11,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
@@ -8037,7 +7872,7 @@
       <c r="B12" s="30" t="n"/>
       <c r="C12" s="30" t="n"/>
       <c r="D12" s="30" t="n"/>
-      <c r="E12" s="47">
+      <c r="E12" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A12,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
@@ -8054,7 +7889,7 @@
       <c r="B13" s="30" t="n"/>
       <c r="C13" s="30" t="n"/>
       <c r="D13" s="30" t="n"/>
-      <c r="E13" s="47">
+      <c r="E13" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A13,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
@@ -8071,7 +7906,7 @@
       <c r="B14" s="30" t="n"/>
       <c r="C14" s="30" t="n"/>
       <c r="D14" s="30" t="n"/>
-      <c r="E14" s="47">
+      <c r="E14" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A14,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
@@ -8088,7 +7923,7 @@
       <c r="B15" s="30" t="n"/>
       <c r="C15" s="30" t="n"/>
       <c r="D15" s="30" t="n"/>
-      <c r="E15" s="47">
+      <c r="E15" s="36">
         <f>IFERROR(INDEX('HOLERITE SET.26'!$B$6:$G$6,1,MATCH(A15,'HOLERITE SET.26'!$B$4:$G$4,0)),0)</f>
         <v/>
       </c>
@@ -8260,7 +8095,7 @@
       <c r="G5" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="36">
+      <c r="H5" s="37">
         <f>E5+F5+G5</f>
         <v/>
       </c>
@@ -8290,7 +8125,7 @@
       <c r="G6" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="36">
+      <c r="H6" s="37">
         <f>E6+F6+G6</f>
         <v/>
       </c>
